--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="329">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -900,6 +900,9 @@
     <t xml:space="preserve">Paid so far</t>
   </si>
   <si>
+    <t xml:space="preserve">Log ID</t>
+  </si>
+  <si>
     <t xml:space="preserve">28/09/2026</t>
   </si>
   <si>
@@ -982,6 +985,33 @@
   </si>
   <si>
     <t xml:space="preserve">Dinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvfx8jx3909u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvfx90yw8xl4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvfx9bgghgpi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kimbap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvfusx39nkux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eggs and Sparkling water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvfutaqk8eyk</t>
   </si>
 </sst>
 </file>
@@ -1737,11 +1767,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>53.96</v>
+        <v>80.82</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1167.04</v>
+        <v>1140.18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2031,11 +2061,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>17.96</v>
+        <v>41.87</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3372.04</v>
+        <v>3348.13</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2052,11 +2082,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>970</v>
+        <v>967.05</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
@@ -2136,11 +2166,11 @@
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">SUM(C20:C26)</f>
-        <v>2728.46</v>
+        <v>2755.32</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">SUM(D20:D26)</f>
-        <v>7271.54</v>
+        <v>7244.68</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">SUM(E20:E26)</f>
@@ -2164,7 +2194,7 @@
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2728.46</v>
+        <v>2755.32</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2182,7 +2212,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7271.54</v>
+        <v>7244.68</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2190,12 +2220,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
         <v>46</v>
       </c>
@@ -2203,25 +2233,25 @@
         <v>8034.27</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
         <v>47</v>
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2728.46</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2755.32</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
         <v>48</v>
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">B38-B39</f>
-        <v>5305.81</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5278.95</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
         <v>49</v>
       </c>
@@ -2230,7 +2260,7 @@
         <v>1965.73</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
         <v>50</v>
       </c>
@@ -3325,7 +3355,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
         <v>27</v>
       </c>
@@ -4283,7 +4313,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="42" t="s">
         <v>27</v>
       </c>
@@ -4329,7 +4359,7 @@
         <v>1397.02</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>163</v>
       </c>
@@ -5294,7 +5324,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -5306,6 +5336,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5342,21 +5373,24 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2728.46</v>
+        <v>2755.32</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E5" s="52" t="n">
         <v>667.6</v>
@@ -5374,16 +5408,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C6" s="51" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E6" s="52" t="n">
         <v>281.62</v>
@@ -5392,16 +5426,16 @@
         <v>41</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2728.46</v>
+        <v>2755.32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B7" s="51" t="s">
         <v>11</v>
@@ -5410,7 +5444,7 @@
         <v>34</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E7" s="52" t="n">
         <v>36</v>
@@ -5419,25 +5453,25 @@
         <v>41</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7271.54</v>
+        <v>7244.68</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C8" s="51" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E8" s="52" t="n">
         <v>19</v>
@@ -5448,16 +5482,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="51" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E9" s="52" t="n">
         <v>87.7</v>
@@ -5468,7 +5502,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>13</v>
@@ -5477,7 +5511,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E10" s="52" t="n">
         <v>239.55</v>
@@ -5488,7 +5522,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="51" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>13</v>
@@ -5497,7 +5531,7 @@
         <v>34</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E11" s="52" t="n">
         <v>52.24</v>
@@ -5508,16 +5542,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="51" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C12" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E12" s="52" t="n">
         <v>211.52</v>
@@ -5528,7 +5562,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="51" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B13" s="51" t="s">
         <v>13</v>
@@ -5537,7 +5571,7 @@
         <v>34</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E13" s="52" t="n">
         <v>137.26</v>
@@ -5548,7 +5582,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>13</v>
@@ -5557,7 +5591,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E14" s="52" t="n">
         <v>338.05</v>
@@ -5568,7 +5602,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B15" s="51" t="s">
         <v>13</v>
@@ -5577,7 +5611,7 @@
         <v>34</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E15" s="52" t="n">
         <v>66.78</v>
@@ -5588,7 +5622,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>13</v>
@@ -5597,7 +5631,7 @@
         <v>34</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E16" s="52" t="n">
         <v>300.97</v>
@@ -5608,7 +5642,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>13</v>
@@ -5617,7 +5651,7 @@
         <v>34</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E17" s="52" t="n">
         <v>226.17</v>
@@ -5628,10 +5662,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C18" s="51" t="s">
         <v>38</v>
@@ -5648,16 +5682,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C19" s="51" t="s">
         <v>38</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E19" s="52" t="n">
         <v>32.4</v>
@@ -5668,7 +5702,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B20" s="51" t="s">
         <v>11</v>
@@ -5677,7 +5711,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E20" s="52" t="n">
         <v>3.05</v>
@@ -5688,7 +5722,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B21" s="51" t="s">
         <v>11</v>
@@ -5697,7 +5731,7 @@
         <v>35</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E21" s="52" t="n">
         <v>14.91</v>
@@ -5707,44 +5741,119 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="51"/>
+      <c r="A22" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="E22" s="52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="51"/>
+      <c r="A23" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="E23" s="52" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="51"/>
+      <c r="A24" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="52" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" s="0" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="51"/>
+      <c r="A25" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="E25" s="52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="51"/>
+      <c r="A26" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="E26" s="52" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26" s="0" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="330">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1012,6 +1012,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvfutaqk8eyk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvg586qrpc9q</t>
   </si>
 </sst>
 </file>
@@ -1767,11 +1770,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>80.82</v>
+        <v>86.72</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1140.18</v>
+        <v>1134.28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2082,11 +2085,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>2.95</v>
+        <v>8.85</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>967.05</v>
+        <v>961.15</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
@@ -2166,11 +2169,11 @@
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">SUM(C20:C26)</f>
-        <v>2755.32</v>
+        <v>2761.22</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">SUM(D20:D26)</f>
-        <v>7244.68</v>
+        <v>7238.78</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">SUM(E20:E26)</f>
@@ -2194,7 +2197,7 @@
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2755.32</v>
+        <v>2761.22</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2212,7 +2215,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7244.68</v>
+        <v>7238.78</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2239,7 +2242,7 @@
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2755.32</v>
+        <v>2761.22</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2248,7 +2251,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">B38-B39</f>
-        <v>5278.95</v>
+        <v>5273.05</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5336,7 +5339,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5373,7 +5376,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2755.32</v>
+        <v>2761.22</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>291</v>
@@ -5430,7 +5433,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2755.32</v>
+        <v>2761.22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5457,7 +5460,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7244.68</v>
+        <v>7238.78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5759,7 +5762,7 @@
       <c r="F22" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="0" t="s">
+      <c r="J22" s="1" t="s">
         <v>321</v>
       </c>
     </row>
@@ -5782,7 +5785,7 @@
       <c r="F23" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J23" s="0" t="s">
+      <c r="J23" s="1" t="s">
         <v>322</v>
       </c>
     </row>
@@ -5805,7 +5808,7 @@
       <c r="F24" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J24" s="0" t="s">
+      <c r="J24" s="1" t="s">
         <v>323</v>
       </c>
     </row>
@@ -5828,7 +5831,7 @@
       <c r="F25" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J25" s="0" t="s">
+      <c r="J25" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -5851,17 +5854,32 @@
       <c r="F26" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J26" s="0" t="s">
+      <c r="J26" s="1" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="51"/>
+      <c r="A27" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="E27" s="52" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="332">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1015,6 +1015,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvg586qrpc9q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sushi - Lunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvg90jc7vf95</t>
   </si>
 </sst>
 </file>
@@ -1770,11 +1776,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>86.72</v>
+        <v>95.22</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1134.28</v>
+        <v>1125.78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2064,11 +2070,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>41.87</v>
+        <v>50.37</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3348.13</v>
+        <v>3339.63</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2169,11 +2175,11 @@
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">SUM(C20:C26)</f>
-        <v>2761.22</v>
+        <v>2769.72</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">SUM(D20:D26)</f>
-        <v>7238.78</v>
+        <v>7230.28</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">SUM(E20:E26)</f>
@@ -2197,7 +2203,7 @@
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2761.22</v>
+        <v>2769.72</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2215,7 +2221,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7238.78</v>
+        <v>7230.28</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2242,7 +2248,7 @@
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2761.22</v>
+        <v>2769.72</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2251,7 +2257,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">B38-B39</f>
-        <v>5273.05</v>
+        <v>5264.55</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5376,7 +5382,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2761.22</v>
+        <v>2769.72</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>291</v>
@@ -5433,7 +5439,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2761.22</v>
+        <v>2769.72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5460,7 +5466,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7238.78</v>
+        <v>7230.28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5882,12 +5888,27 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="51"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="51"/>
+      <c r="A28" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="E28" s="52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="334">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1021,6 +1021,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvg90jc7vf95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teddy Beurre House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvga02pv4zdc</t>
   </si>
 </sst>
 </file>
@@ -1776,11 +1782,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>95.22</v>
+        <v>104.09</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1125.78</v>
+        <v>1116.91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2070,11 +2076,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>50.37</v>
+        <v>59.24</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3339.63</v>
+        <v>3330.76</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2175,11 +2181,11 @@
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">SUM(C20:C26)</f>
-        <v>2769.72</v>
+        <v>2778.59</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">SUM(D20:D26)</f>
-        <v>7230.28</v>
+        <v>7221.41</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">SUM(E20:E26)</f>
@@ -2203,7 +2209,7 @@
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2769.72</v>
+        <v>2778.59</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2221,7 +2227,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7230.28</v>
+        <v>7221.41</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2248,7 +2254,7 @@
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2769.72</v>
+        <v>2778.59</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2257,7 +2263,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">B38-B39</f>
-        <v>5264.55</v>
+        <v>5255.68</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5382,7 +5388,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2769.72</v>
+        <v>2778.59</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>291</v>
@@ -5439,7 +5445,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2769.72</v>
+        <v>2778.59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5466,7 +5472,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7230.28</v>
+        <v>7221.41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5911,12 +5917,27 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="51"/>
+      <c r="A29" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B29" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>332</v>
+      </c>
+      <c r="E29" s="52" t="n">
+        <v>8.87</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="336">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1027,6 +1027,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvga02pv4zdc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel Adapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvgm0kk7r7zk</t>
   </si>
 </sst>
 </file>
@@ -1782,11 +1788,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>104.09</v>
+        <v>107.49</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1116.91</v>
+        <v>1113.51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2118,11 +2124,11 @@
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A24)</f>
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">B24-C24</f>
-        <v>1030</v>
+        <v>1026.6</v>
       </c>
       <c r="E24" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B24/$B$3)</f>
@@ -2181,11 +2187,11 @@
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">SUM(C20:C26)</f>
-        <v>2778.59</v>
+        <v>2781.99</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">SUM(D20:D26)</f>
-        <v>7221.41</v>
+        <v>7218.01</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">SUM(E20:E26)</f>
@@ -2209,7 +2215,7 @@
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2778.59</v>
+        <v>2781.99</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2227,7 +2233,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7221.41</v>
+        <v>7218.01</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2254,7 +2260,7 @@
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2778.59</v>
+        <v>2781.99</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2263,7 +2269,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">B38-B39</f>
-        <v>5255.68</v>
+        <v>5252.28</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5388,7 +5394,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2778.59</v>
+        <v>2781.99</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>291</v>
@@ -5445,7 +5451,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2778.59</v>
+        <v>2781.99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5472,7 +5478,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7221.41</v>
+        <v>7218.01</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5940,12 +5946,27 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="51"/>
+      <c r="A30" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="E30" s="52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="338">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1033,6 +1033,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvgm0kk7r7zk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coffee &amp; cafés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvgm1pq2sx7l</t>
   </si>
 </sst>
 </file>
@@ -1788,11 +1794,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>107.49</v>
+        <v>109.47</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1113.51</v>
+        <v>1111.53</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2082,11 +2088,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>59.24</v>
+        <v>61.22</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3330.76</v>
+        <v>3328.78</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2187,11 +2193,11 @@
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">SUM(C20:C26)</f>
-        <v>2781.99</v>
+        <v>2783.97</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">SUM(D20:D26)</f>
-        <v>7218.01</v>
+        <v>7216.03</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">SUM(E20:E26)</f>
@@ -2215,7 +2221,7 @@
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2781.99</v>
+        <v>2783.97</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2233,7 +2239,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7218.01</v>
+        <v>7216.03</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2260,7 +2266,7 @@
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2781.99</v>
+        <v>2783.97</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2269,7 +2275,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">B38-B39</f>
-        <v>5252.28</v>
+        <v>5250.3</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5394,7 +5400,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2781.99</v>
+        <v>2783.97</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>291</v>
@@ -5451,7 +5457,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2781.99</v>
+        <v>2783.97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5478,7 +5484,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7218.01</v>
+        <v>7216.03</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5969,12 +5975,27 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="51"/>
+      <c r="A31" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="E31" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="341">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1039,6 +1039,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvgm1pq2sx7l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvha28vt2umu</t>
   </si>
 </sst>
 </file>
@@ -1794,11 +1803,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>109.47</v>
+        <v>113.73</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1111.53</v>
+        <v>1107.27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2088,11 +2097,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>61.22</v>
+        <v>65.48</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3328.78</v>
+        <v>3324.52</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2193,11 +2202,11 @@
       </c>
       <c r="C27" s="24" t="n">
         <f aca="false">SUM(C20:C26)</f>
-        <v>2783.97</v>
+        <v>2788.23</v>
       </c>
       <c r="D27" s="24" t="n">
         <f aca="false">SUM(D20:D26)</f>
-        <v>7216.03</v>
+        <v>7211.77</v>
       </c>
       <c r="E27" s="25" t="n">
         <f aca="false">SUM(E20:E26)</f>
@@ -2221,7 +2230,7 @@
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2783.97</v>
+        <v>2788.23</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2239,7 +2248,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7216.03</v>
+        <v>7211.77</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2266,7 +2275,7 @@
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2783.97</v>
+        <v>2788.23</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2275,7 +2284,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">B38-B39</f>
-        <v>5250.3</v>
+        <v>5246.04</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5400,7 +5409,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2783.97</v>
+        <v>2788.23</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>291</v>
@@ -5457,7 +5466,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2783.97</v>
+        <v>2788.23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5484,7 +5493,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7216.03</v>
+        <v>7211.77</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5998,12 +6007,27 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="51"/>
+      <c r="A32" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="E32" s="52" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="339">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Ground costs only (accommodation, food, local transport, activities). Korea &amp; Japan appear twice – spend is combined on their first row.</t>
+    <t xml:space="preserve">Ground costs only (accommodation, food, local transport, activities, shopping &amp; misc). Korea &amp; Japan appear twice – spend is combined on their first row.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Budget by category</t>
@@ -141,6 +141,9 @@
     <t xml:space="preserve">Activities</t>
   </si>
   <si>
+    <t xml:space="preserve">Shopping &amp; misc</t>
+  </si>
+  <si>
     <t xml:space="preserve">Insurance &amp; admin</t>
   </si>
   <si>
@@ -219,6 +222,9 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">Shopping &amp; misc (£)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Incheon – Incheon Airport Hotel Seattle</t>
   </si>
   <si>
@@ -981,18 +987,15 @@
     <t xml:space="preserve">eSIM #1 – 50GB, 45 days</t>
   </si>
   <si>
+    <t xml:space="preserve">TMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvfx8jx3909u</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coffee</t>
   </si>
   <si>
-    <t xml:space="preserve">Dinner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMoney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mvfx8jx3909u</t>
-  </si>
-  <si>
     <t xml:space="preserve">mvfx90yw8xl4</t>
   </si>
   <si>
@@ -1039,15 +1042,6 @@
   </si>
   <si>
     <t xml:space="preserve">mvgm1pq2sx7l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mvha28vt2umu</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1718,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
@@ -1795,19 +1789,19 @@
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">SUM(Itinerary!K5:K6)</f>
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">IF(C7=0,0,D7/C7)</f>
-        <v>60.3333333333333</v>
+        <v>65.3333333333333</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>113.73</v>
+        <v>91.51</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1107.27</v>
+        <v>1244.49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1823,11 +1817,11 @@
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">SUM(Itinerary!K7:K11)</f>
-        <v>2766.02</v>
+        <v>2866.02</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">IF(C8=0,0,D8/C8)</f>
-        <v>138.301</v>
+        <v>143.301</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1835,7 +1829,7 @@
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3484</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1851,11 +1845,11 @@
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">SUM(Itinerary!K12:K13)</f>
-        <v>535</v>
+        <v>575</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">IF(C9=0,0,D9/C9)</f>
-        <v>66.875</v>
+        <v>71.875</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Vietnam")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Vietnam",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Vietnam",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1863,7 +1857,7 @@
       </c>
       <c r="G9" s="12" t="n">
         <f aca="false">D9-F9</f>
-        <v>535</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1879,11 +1873,11 @@
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">SUM(Itinerary!K14:K15)</f>
-        <v>700</v>
+        <v>735</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">IF(C10=0,0,D10/C10)</f>
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Taiwan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Taiwan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Taiwan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1891,7 +1885,7 @@
       </c>
       <c r="G10" s="12" t="n">
         <f aca="false">D10-F10</f>
-        <v>700</v>
+        <v>735</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1907,11 +1901,11 @@
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">SUM(Itinerary!K16:K17)</f>
-        <v>696</v>
+        <v>736</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">IF(C11=0,0,D11/C11)</f>
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1919,7 +1913,7 @@
       </c>
       <c r="G11" s="12" t="n">
         <f aca="false">D11-F11</f>
-        <v>696</v>
+        <v>736</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1935,11 +1929,11 @@
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">SUM(Itinerary!K18:K19)</f>
-        <v>1195</v>
+        <v>1245</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">IF(C12=0,0,D12/C12)</f>
-        <v>119.5</v>
+        <v>124.5</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Thailand")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Thailand",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Thailand",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1947,7 +1941,7 @@
       </c>
       <c r="G12" s="12" t="n">
         <f aca="false">D12-F12</f>
-        <v>1195</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1963,11 +1957,11 @@
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">SUM(Itinerary!K20:K20)</f>
-        <v>1040</v>
+        <v>1140</v>
       </c>
       <c r="E13" s="11" t="n">
         <f aca="false">IF(C13=0,0,D13/C13)</f>
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>24</v>
@@ -1987,11 +1981,11 @@
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">SUM(Itinerary!K21:K24)</f>
-        <v>2079</v>
+        <v>2154</v>
       </c>
       <c r="E14" s="11" t="n">
         <f aca="false">IF(C14=0,0,D14/C14)</f>
-        <v>138.6</v>
+        <v>143.6</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>26</v>
@@ -2009,11 +2003,11 @@
       </c>
       <c r="D15" s="16" t="n">
         <f aca="false">SUM(D7:D14)</f>
-        <v>9192.02</v>
+        <v>9647.02</v>
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">IF(C15=0,0,D15/C15)</f>
-        <v>101.011208791209</v>
+        <v>106.011208791209</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -2097,11 +2091,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>65.48</v>
+        <v>43.26</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3324.52</v>
+        <v>3346.74</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2139,11 +2133,11 @@
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A24)</f>
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">B24-C24</f>
-        <v>1026.6</v>
+        <v>1030</v>
       </c>
       <c r="E24" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B24/$B$3)</f>
@@ -2155,127 +2149,142 @@
         <v>38</v>
       </c>
       <c r="B25" s="17" t="n">
+        <f aca="false">Itinerary!O25</f>
+        <v>455</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A25)</f>
+        <v>3.4</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <f aca="false">B25-C25</f>
+        <v>451.6</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <f aca="false">IF($B$3=0,0,B25/$B$3)</f>
+        <v>0.0455</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="17" t="n">
         <f aca="false">'Admin &amp; checklist'!B9</f>
         <v>457.66</v>
       </c>
-      <c r="C25" s="18" t="n">
-        <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A25)</f>
+      <c r="C26" s="18" t="n">
+        <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
         <v>346.66</v>
       </c>
-      <c r="D25" s="18" t="n">
-        <f aca="false">B25-C25</f>
+      <c r="D26" s="18" t="n">
+        <f aca="false">B26-C26</f>
         <v>111</v>
       </c>
-      <c r="E25" s="19" t="n">
-        <f aca="false">IF($B$3=0,0,B25/$B$3)</f>
+      <c r="E26" s="19" t="n">
+        <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
         <v>0.045766</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="21" t="n">
-        <f aca="false">$B$3-SUM(B20:B25)</f>
-        <v>-1356.5</v>
-      </c>
-      <c r="C26" s="22" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="21" t="n">
+        <f aca="false">$B$3-SUM(B20:B26)</f>
+        <v>-1811.5</v>
+      </c>
+      <c r="C27" s="22" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,"Other")</f>
         <v>0</v>
       </c>
-      <c r="D26" s="22" t="n">
-        <f aca="false">B26-C26</f>
-        <v>-1356.5</v>
-      </c>
-      <c r="E26" s="23" t="n">
-        <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
-        <v>-0.13565</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
+      <c r="D27" s="22" t="n">
+        <f aca="false">B27-C27</f>
+        <v>-1811.5</v>
+      </c>
+      <c r="E27" s="23" t="n">
+        <f aca="false">IF($B$3=0,0,B27/$B$3)</f>
+        <v>-0.18115</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="24" t="n">
-        <f aca="false">SUM(B20:B26)</f>
+      <c r="B28" s="24" t="n">
+        <f aca="false">SUM(B20:B27)</f>
         <v>10000</v>
       </c>
-      <c r="C27" s="24" t="n">
-        <f aca="false">SUM(C20:C26)</f>
-        <v>2788.23</v>
-      </c>
-      <c r="D27" s="24" t="n">
-        <f aca="false">SUM(D20:D26)</f>
-        <v>7211.77</v>
-      </c>
-      <c r="E27" s="25" t="n">
-        <f aca="false">SUM(E20:E26)</f>
+      <c r="C28" s="24" t="n">
+        <f aca="false">SUM(C20:C27)</f>
+        <v>2766.01</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <f aca="false">SUM(D20:D27)</f>
+        <v>7233.99</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <f aca="false">SUM(E20:E27)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="str">
-        <f aca="false">IF(B26&lt;0,"⚠ Plan is over budget by "&amp;TEXT(-B26,"£#,##0"),IF(B26&lt;200,"⚠ Buffer below £200","✓ Plan fits the budget with a buffer"))</f>
-        <v>⚠ Plan is over budget by £1,357</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="str">
+        <f aca="false">IF(B27&lt;0,"⚠ Plan is over budget by "&amp;TEXT(-B27,"£#,##0"),IF(B27&lt;200,"⚠ Buffer below £200","✓ Plan fits the budget with a buffer"))</f>
+        <v>⚠ Plan is over budget by £1,812</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B31" s="27" t="n">
-        <f aca="false">Tracker!I4</f>
-        <v>2788.23</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="22" t="n">
-        <f aca="false">Tracker!I5</f>
-        <v>0</v>
+      <c r="B32" s="27" t="n">
+        <f aca="false">Tracker!I4</f>
+        <v>2766.01</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B33" s="22" t="n">
+        <f aca="false">Tracker!I5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7211.77</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+        <v>7233.99</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
         <v>45</v>
       </c>
     </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="B38" s="28" t="n">
-        <v>8034.27</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="27" t="n">
-        <f aca="false">Tracker!I4</f>
-        <v>2788.23</v>
+      <c r="B39" s="28" t="n">
+        <v>8034.27</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2283,8 +2292,8 @@
         <v>48</v>
       </c>
       <c r="B40" s="27" t="n">
-        <f aca="false">B38-B39</f>
-        <v>5246.04</v>
+        <f aca="false">Tracker!I4</f>
+        <v>2766.01</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2292,8 +2301,8 @@
         <v>49</v>
       </c>
       <c r="B41" s="27" t="n">
-        <f aca="false">MAX(0,B3-B38)</f>
-        <v>1965.73</v>
+        <f aca="false">B39-B40</f>
+        <v>5268.26</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2301,8 +2310,17 @@
         <v>50</v>
       </c>
       <c r="B42" s="27" t="n">
-        <f aca="false">MAX(0,SUM(B20:B25)-B38)</f>
-        <v>3322.23</v>
+        <f aca="false">MAX(0,B3-B39)</f>
+        <v>1965.73</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="27" t="n">
+        <f aca="false">MAX(0,SUM(B20:B26)-B39)</f>
+        <v>3777.23</v>
       </c>
     </row>
   </sheetData>
@@ -2321,7 +2339,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
@@ -2335,16 +2353,17 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2352,7 +2371,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>5</v>
@@ -2361,34 +2380,37 @@
         <v>6</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2396,10 +2418,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" s="29" t="n">
         <v>1</v>
@@ -2426,19 +2448,22 @@
         <v>15</v>
       </c>
       <c r="K5" s="12" t="n">
-        <f aca="false">G5+H5+I5+J5</f>
-        <v>66</v>
+        <f aca="false">G5+H5+I5+J5+O5</f>
+        <v>71</v>
       </c>
       <c r="L5" s="12" t="n">
         <f aca="false">IF(D5=0,0,K5/D5)</f>
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M5" s="9" t="str">
         <f aca="false">IF(Hotels!G5="Booked","Yes",IF(Hotels!G5="Staying with friends","N/A – host","No"))</f>
         <v>Yes</v>
       </c>
       <c r="N5" s="31" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="O5" s="30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2446,10 +2471,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="29" t="n">
         <v>2</v>
@@ -2476,19 +2501,22 @@
         <v>60</v>
       </c>
       <c r="K6" s="12" t="n">
-        <f aca="false">G6+H6+I6+J6</f>
-        <v>115</v>
+        <f aca="false">G6+H6+I6+J6+O6</f>
+        <v>125</v>
       </c>
       <c r="L6" s="12" t="n">
         <f aca="false">IF(D6=0,0,K6/D6)</f>
-        <v>57.5</v>
+        <v>62.5</v>
       </c>
       <c r="M6" s="9" t="str">
         <f aca="false">IF(Hotels!G6="Booked","Yes",IF(Hotels!G6="Staying with friends","N/A – host","No"))</f>
         <v>N/A – host</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="O6" s="30" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2496,10 +2524,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" s="29" t="n">
         <v>3</v>
@@ -2526,19 +2554,22 @@
         <v>114</v>
       </c>
       <c r="K7" s="12" t="n">
-        <f aca="false">G7+H7+I7+J7</f>
-        <v>475.79</v>
+        <f aca="false">G7+H7+I7+J7+O7</f>
+        <v>490.79</v>
       </c>
       <c r="L7" s="12" t="n">
         <f aca="false">IF(D7=0,0,K7/D7)</f>
-        <v>158.596666666667</v>
+        <v>163.596666666667</v>
       </c>
       <c r="M7" s="9" t="str">
         <f aca="false">IF(Hotels!G7="Booked","Yes",IF(Hotels!G7="Staying with friends","N/A – host","No"))</f>
         <v>Yes</v>
       </c>
       <c r="N7" s="31" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="O7" s="30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2546,10 +2577,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" s="29" t="n">
         <v>3</v>
@@ -2576,19 +2607,22 @@
         <v>114</v>
       </c>
       <c r="K8" s="12" t="n">
-        <f aca="false">G8+H8+I8+J8</f>
-        <v>413.04</v>
+        <f aca="false">G8+H8+I8+J8+O8</f>
+        <v>428.04</v>
       </c>
       <c r="L8" s="12" t="n">
         <f aca="false">IF(D8=0,0,K8/D8)</f>
-        <v>137.68</v>
+        <v>142.68</v>
       </c>
       <c r="M8" s="9" t="str">
         <f aca="false">IF(Hotels!G8="Booked","Yes",IF(Hotels!G8="Staying with friends","N/A – host","No"))</f>
         <v>Yes</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="O8" s="30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2596,10 +2630,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D9" s="29" t="n">
         <v>5</v>
@@ -2626,19 +2660,22 @@
         <v>190</v>
       </c>
       <c r="K9" s="12" t="n">
-        <f aca="false">G9+H9+I9+J9</f>
-        <v>663.05</v>
+        <f aca="false">G9+H9+I9+J9+O9</f>
+        <v>688.05</v>
       </c>
       <c r="L9" s="12" t="n">
         <f aca="false">IF(D9=0,0,K9/D9)</f>
-        <v>132.61</v>
+        <v>137.61</v>
       </c>
       <c r="M9" s="9" t="str">
         <f aca="false">IF(Hotels!G9="Booked","Yes",IF(Hotels!G9="Staying with friends","N/A – host","No"))</f>
         <v>Yes</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="O9" s="30" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2646,10 +2683,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" s="29" t="n">
         <v>3</v>
@@ -2676,19 +2713,22 @@
         <v>114</v>
       </c>
       <c r="K10" s="12" t="n">
-        <f aca="false">G10+H10+I10+J10</f>
-        <v>425.17</v>
+        <f aca="false">G10+H10+I10+J10+O10</f>
+        <v>440.17</v>
       </c>
       <c r="L10" s="12" t="n">
         <f aca="false">IF(D10=0,0,K10/D10)</f>
-        <v>141.723333333333</v>
+        <v>146.723333333333</v>
       </c>
       <c r="M10" s="9" t="str">
         <f aca="false">IF(Hotels!G10="Booked","Yes",IF(Hotels!G10="Staying with friends","N/A – host","No"))</f>
         <v>Yes</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="O10" s="30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2696,10 +2736,10 @@
         <v>13</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" s="29" t="n">
         <v>6</v>
@@ -2726,19 +2766,22 @@
         <v>348</v>
       </c>
       <c r="K11" s="12" t="n">
-        <f aca="false">G11+H11+I11+J11</f>
-        <v>788.97</v>
+        <f aca="false">G11+H11+I11+J11+O11</f>
+        <v>818.97</v>
       </c>
       <c r="L11" s="12" t="n">
         <f aca="false">IF(D11=0,0,K11/D11)</f>
-        <v>131.495</v>
+        <v>136.495</v>
       </c>
       <c r="M11" s="9" t="str">
         <f aca="false">IF(Hotels!G11="Booked","Yes",IF(Hotels!G11="Staying with friends","N/A – host","No"))</f>
         <v>Yes</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="O11" s="30" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2746,10 +2789,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D12" s="29" t="n">
         <v>3</v>
@@ -2776,19 +2819,22 @@
         <v>45</v>
       </c>
       <c r="K12" s="12" t="n">
-        <f aca="false">G12+H12+I12+J12</f>
-        <v>190</v>
+        <f aca="false">G12+H12+I12+J12+O12</f>
+        <v>205</v>
       </c>
       <c r="L12" s="12" t="n">
         <f aca="false">IF(D12=0,0,K12/D12)</f>
-        <v>63.3333333333333</v>
+        <v>68.3333333333333</v>
       </c>
       <c r="M12" s="9" t="str">
         <f aca="false">IF(Hotels!G12="Booked","Yes",IF(Hotels!G12="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="O12" s="30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2796,10 +2842,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" s="29" t="n">
         <v>5</v>
@@ -2826,19 +2872,22 @@
         <v>135</v>
       </c>
       <c r="K13" s="12" t="n">
-        <f aca="false">G13+H13+I13+J13</f>
-        <v>345</v>
+        <f aca="false">G13+H13+I13+J13+O13</f>
+        <v>370</v>
       </c>
       <c r="L13" s="12" t="n">
         <f aca="false">IF(D13=0,0,K13/D13)</f>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M13" s="9" t="str">
         <f aca="false">IF(Hotels!G13="Booked","Yes",IF(Hotels!G13="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="O13" s="30" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2846,10 +2895,10 @@
         <v>17</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" s="29" t="n">
         <v>4</v>
@@ -2876,19 +2925,22 @@
         <v>190</v>
       </c>
       <c r="K14" s="12" t="n">
-        <f aca="false">G14+H14+I14+J14</f>
-        <v>440</v>
+        <f aca="false">G14+H14+I14+J14+O14</f>
+        <v>460</v>
       </c>
       <c r="L14" s="12" t="n">
         <f aca="false">IF(D14=0,0,K14/D14)</f>
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M14" s="9" t="str">
         <f aca="false">IF(Hotels!G14="Booked","Yes",IF(Hotels!G14="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N14" s="31" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+      <c r="O14" s="30" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2896,10 +2948,10 @@
         <v>17</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D15" s="29" t="n">
         <v>3</v>
@@ -2926,19 +2978,22 @@
         <v>75</v>
       </c>
       <c r="K15" s="12" t="n">
-        <f aca="false">G15+H15+I15+J15</f>
-        <v>260</v>
+        <f aca="false">G15+H15+I15+J15+O15</f>
+        <v>275</v>
       </c>
       <c r="L15" s="12" t="n">
         <f aca="false">IF(D15=0,0,K15/D15)</f>
-        <v>86.6666666666667</v>
+        <v>91.6666666666667</v>
       </c>
       <c r="M15" s="9" t="str">
         <f aca="false">IF(Hotels!G15="Booked","Yes",IF(Hotels!G15="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N15" s="31" t="s">
-        <v>96</v>
+        <v>98</v>
+      </c>
+      <c r="O15" s="30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2946,10 +3001,10 @@
         <v>19</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D16" s="29" t="n">
         <v>3</v>
@@ -2976,19 +3031,22 @@
         <v>66</v>
       </c>
       <c r="K16" s="12" t="n">
-        <f aca="false">G16+H16+I16+J16</f>
-        <v>231</v>
+        <f aca="false">G16+H16+I16+J16+O16</f>
+        <v>246</v>
       </c>
       <c r="L16" s="12" t="n">
         <f aca="false">IF(D16=0,0,K16/D16)</f>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="M16" s="9" t="str">
         <f aca="false">IF(Hotels!G16="Booked","Yes",IF(Hotels!G16="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N16" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
+      </c>
+      <c r="O16" s="30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2996,10 +3054,10 @@
         <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D17" s="29" t="n">
         <v>5</v>
@@ -3026,19 +3084,22 @@
         <v>200</v>
       </c>
       <c r="K17" s="12" t="n">
-        <f aca="false">G17+H17+I17+J17</f>
-        <v>465</v>
+        <f aca="false">G17+H17+I17+J17+O17</f>
+        <v>490</v>
       </c>
       <c r="L17" s="12" t="n">
         <f aca="false">IF(D17=0,0,K17/D17)</f>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="M17" s="9" t="str">
         <f aca="false">IF(Hotels!G17="Booked","Yes",IF(Hotels!G17="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N17" s="31" t="s">
-        <v>102</v>
+        <v>104</v>
+      </c>
+      <c r="O17" s="30" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3046,10 +3107,10 @@
         <v>21</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D18" s="29" t="n">
         <v>6</v>
@@ -3076,19 +3137,22 @@
         <v>270</v>
       </c>
       <c r="K18" s="12" t="n">
-        <f aca="false">G18+H18+I18+J18</f>
-        <v>890</v>
+        <f aca="false">G18+H18+I18+J18+O18</f>
+        <v>920</v>
       </c>
       <c r="L18" s="12" t="n">
         <f aca="false">IF(D18=0,0,K18/D18)</f>
-        <v>148.333333333333</v>
+        <v>153.333333333333</v>
       </c>
       <c r="M18" s="9" t="str">
         <f aca="false">IF(Hotels!G18="Booked","Yes",IF(Hotels!G18="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>105</v>
+        <v>107</v>
+      </c>
+      <c r="O18" s="30" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3096,10 +3160,10 @@
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D19" s="29" t="n">
         <v>4</v>
@@ -3126,19 +3190,22 @@
         <v>80</v>
       </c>
       <c r="K19" s="12" t="n">
-        <f aca="false">G19+H19+I19+J19</f>
-        <v>305</v>
+        <f aca="false">G19+H19+I19+J19+O19</f>
+        <v>325</v>
       </c>
       <c r="L19" s="12" t="n">
         <f aca="false">IF(D19=0,0,K19/D19)</f>
-        <v>76.25</v>
+        <v>81.25</v>
       </c>
       <c r="M19" s="9" t="str">
         <f aca="false">IF(Hotels!G19="Booked","Yes",IF(Hotels!G19="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N19" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
+      </c>
+      <c r="O19" s="30" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3146,7 +3213,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>23</v>
@@ -3176,19 +3243,22 @@
         <v>760</v>
       </c>
       <c r="K20" s="12" t="n">
-        <f aca="false">G20+H20+I20+J20</f>
-        <v>1040</v>
+        <f aca="false">G20+H20+I20+J20+O20</f>
+        <v>1140</v>
       </c>
       <c r="L20" s="12" t="n">
         <f aca="false">IF(D20=0,0,K20/D20)</f>
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M20" s="9" t="str">
         <f aca="false">IF(Hotels!G20="Booked","Yes",IF(Hotels!G20="Staying with friends","N/A – host","No"))</f>
         <v>N/A – host</v>
       </c>
       <c r="N20" s="31" t="s">
-        <v>110</v>
+        <v>112</v>
+      </c>
+      <c r="O20" s="30" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3196,10 +3266,10 @@
         <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D21" s="29" t="n">
         <v>8</v>
@@ -3226,19 +3296,22 @@
         <v>384</v>
       </c>
       <c r="K21" s="12" t="n">
-        <f aca="false">G21+H21+I21+J21</f>
-        <v>994</v>
+        <f aca="false">G21+H21+I21+J21+O21</f>
+        <v>1034</v>
       </c>
       <c r="L21" s="12" t="n">
         <f aca="false">IF(D21=0,0,K21/D21)</f>
-        <v>124.25</v>
+        <v>129.25</v>
       </c>
       <c r="M21" s="9" t="str">
         <f aca="false">IF(Hotels!G21="Booked","Yes",IF(Hotels!G21="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N21" s="31" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="O21" s="30" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3246,10 +3319,10 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D22" s="29" t="n">
         <v>2</v>
@@ -3276,19 +3349,22 @@
         <v>40</v>
       </c>
       <c r="K22" s="12" t="n">
-        <f aca="false">G22+H22+I22+J22</f>
-        <v>350</v>
+        <f aca="false">G22+H22+I22+J22+O22</f>
+        <v>360</v>
       </c>
       <c r="L22" s="12" t="n">
         <f aca="false">IF(D22=0,0,K22/D22)</f>
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M22" s="9" t="str">
         <f aca="false">IF(Hotels!G22="Booked","Yes",IF(Hotels!G22="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N22" s="31" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="O22" s="30" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3296,10 +3372,10 @@
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D23" s="29" t="n">
         <v>3</v>
@@ -3326,19 +3402,22 @@
         <v>114</v>
       </c>
       <c r="K23" s="12" t="n">
-        <f aca="false">G23+H23+I23+J23</f>
-        <v>339</v>
+        <f aca="false">G23+H23+I23+J23+O23</f>
+        <v>354</v>
       </c>
       <c r="L23" s="12" t="n">
         <f aca="false">IF(D23=0,0,K23/D23)</f>
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M23" s="9" t="str">
         <f aca="false">IF(Hotels!G23="Booked","Yes",IF(Hotels!G23="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N23" s="31" t="s">
-        <v>119</v>
+        <v>121</v>
+      </c>
+      <c r="O23" s="30" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3346,10 +3425,10 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D24" s="29" t="n">
         <v>2</v>
@@ -3376,19 +3455,22 @@
         <v>76</v>
       </c>
       <c r="K24" s="12" t="n">
-        <f aca="false">G24+H24+I24+J24</f>
-        <v>396</v>
+        <f aca="false">G24+H24+I24+J24+O24</f>
+        <v>406</v>
       </c>
       <c r="L24" s="12" t="n">
         <f aca="false">IF(D24=0,0,K24/D24)</f>
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="M24" s="9" t="str">
         <f aca="false">IF(Hotels!G24="Booked","Yes",IF(Hotels!G24="Staying with friends","N/A – host","No"))</f>
         <v>No</v>
       </c>
       <c r="N24" s="31" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="O24" s="30" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3421,14 +3503,18 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">SUM(K5:K24)</f>
-        <v>9192.02</v>
+        <v>9647.02</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">IF(D25=0,0,K25/D25)</f>
-        <v>101.011208791209</v>
+        <v>106.011208791209</v>
       </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
+      <c r="O25" s="16" t="n">
+        <f aca="false">SUM(O5:O24)</f>
+        <v>455</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3467,12 +3553,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3480,43 +3566,43 @@
         <v>4</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N4" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3540,10 +3626,10 @@
         <v>46315</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H5" s="39" t="n">
         <v>36</v>
@@ -3553,17 +3639,17 @@
         <v>36</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="37"/>
       <c r="L5" s="37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N5" s="41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3588,10 +3674,10 @@
         <v>46317</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H6" s="39" t="n">
         <v>0</v>
@@ -3601,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K6" s="37"/>
       <c r="L6" s="37"/>
       <c r="M6" s="37"/>
       <c r="N6" s="41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3632,10 +3718,10 @@
         <v>46320</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H7" s="39" t="n">
         <f aca="false">(52.24+239.55)/3</f>
@@ -3646,13 +3732,13 @@
         <v>291.79</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K7" s="37"/>
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
       <c r="N7" s="41" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3677,10 +3763,10 @@
         <v>46323</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H8" s="39" t="n">
         <f aca="false">(137.26+66.78)/3</f>
@@ -3691,13 +3777,13 @@
         <v>204.04</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" s="37"/>
       <c r="L8" s="37"/>
       <c r="M8" s="37"/>
       <c r="N8" s="41" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3722,10 +3808,10 @@
         <v>46328</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H9" s="39" t="n">
         <f aca="false">338.05/5</f>
@@ -3736,13 +3822,13 @@
         <v>338.05</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K9" s="37"/>
       <c r="L9" s="37"/>
       <c r="M9" s="37"/>
       <c r="N9" s="41" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3767,10 +3853,10 @@
         <v>46331</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H10" s="39" t="n">
         <f aca="false">226.17/3</f>
@@ -3781,13 +3867,13 @@
         <v>226.17</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K10" s="37"/>
       <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="N10" s="41" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3812,10 +3898,10 @@
         <v>46337</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H11" s="39" t="n">
         <f aca="false">300.97/6</f>
@@ -3826,13 +3912,13 @@
         <v>300.97</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K11" s="37"/>
       <c r="L11" s="37"/>
       <c r="M11" s="37"/>
       <c r="N11" s="41" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3858,7 +3944,7 @@
       </c>
       <c r="F12" s="37"/>
       <c r="G12" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H12" s="39" t="n">
         <v>20</v>
@@ -3872,7 +3958,7 @@
       <c r="L12" s="37"/>
       <c r="M12" s="37"/>
       <c r="N12" s="41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3898,7 +3984,7 @@
       </c>
       <c r="F13" s="37"/>
       <c r="G13" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H13" s="39" t="n">
         <v>25</v>
@@ -3912,7 +3998,7 @@
       <c r="L13" s="37"/>
       <c r="M13" s="37"/>
       <c r="N13" s="41" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3938,7 +4024,7 @@
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H14" s="39" t="n">
         <v>45</v>
@@ -3976,7 +4062,7 @@
       </c>
       <c r="F15" s="37"/>
       <c r="G15" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H15" s="39" t="n">
         <v>35</v>
@@ -4014,7 +4100,7 @@
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H16" s="39" t="n">
         <v>35</v>
@@ -4052,7 +4138,7 @@
       </c>
       <c r="F17" s="37"/>
       <c r="G17" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H17" s="39" t="n">
         <v>25</v>
@@ -4066,7 +4152,7 @@
       <c r="L17" s="37"/>
       <c r="M17" s="37"/>
       <c r="N17" s="41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4092,7 +4178,7 @@
       </c>
       <c r="F18" s="37"/>
       <c r="G18" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H18" s="39" t="n">
         <v>90</v>
@@ -4106,7 +4192,7 @@
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
       <c r="N18" s="41" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4132,7 +4218,7 @@
       </c>
       <c r="F19" s="37"/>
       <c r="G19" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H19" s="39" t="n">
         <v>35</v>
@@ -4169,10 +4255,10 @@
         <v>46390</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H20" s="39" t="n">
         <v>0</v>
@@ -4182,13 +4268,13 @@
         <v>0</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K20" s="37"/>
       <c r="L20" s="37"/>
       <c r="M20" s="37"/>
       <c r="N20" s="41" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4214,7 +4300,7 @@
       </c>
       <c r="F21" s="37"/>
       <c r="G21" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H21" s="39" t="n">
         <v>55</v>
@@ -4228,7 +4314,7 @@
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
       <c r="N21" s="41" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4254,7 +4340,7 @@
       </c>
       <c r="F22" s="37"/>
       <c r="G22" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H22" s="39" t="n">
         <v>130</v>
@@ -4268,7 +4354,7 @@
       <c r="L22" s="37"/>
       <c r="M22" s="37"/>
       <c r="N22" s="41" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4294,7 +4380,7 @@
       </c>
       <c r="F23" s="37"/>
       <c r="G23" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H23" s="39" t="n">
         <v>55</v>
@@ -4332,7 +4418,7 @@
       </c>
       <c r="F24" s="37"/>
       <c r="G24" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H24" s="39" t="n">
         <v>80</v>
@@ -4346,7 +4432,7 @@
       <c r="L24" s="37"/>
       <c r="M24" s="37"/>
       <c r="N24" s="41" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4379,7 +4465,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C27" s="44" t="str">
         <f aca="false">COUNTIF(G5:G24,"Booked")&amp;" of "&amp;(COUNTA(G5:G24)-COUNTIF(G5:G24,"Staying with friends"))</f>
@@ -4388,7 +4474,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C28" s="45" t="n">
         <f aca="false">SUMIF(G5:G24,"Booked",I5:I24)</f>
@@ -4397,7 +4483,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C29" s="45" t="n">
         <f aca="false">SUMIF(G5:G24,"To book",I5:I24)+SUMIF(G5:G24,"Shortlisted",I5:I24)</f>
@@ -4452,53 +4538,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4509,33 +4595,33 @@
         <v>46313</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G5" s="38"/>
       <c r="H5" s="38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I5" s="47" t="n">
         <v>667.6</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L5" s="38"/>
       <c r="M5" s="41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4546,35 +4632,35 @@
         <v>46314</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I6" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L6" s="38"/>
       <c r="M6" s="41" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4585,35 +4671,35 @@
         <v>46317</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I7" s="47" t="n">
         <v>87.7</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L7" s="38"/>
       <c r="M7" s="41" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4624,35 +4710,35 @@
         <v>46337</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I8" s="47" t="n">
         <v>211.52</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L8" s="38"/>
       <c r="M8" s="41" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4663,29 +4749,29 @@
         <v>46345</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
       <c r="H9" s="38" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I9" s="47" t="n">
         <v>130</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L9" s="38"/>
       <c r="M9" s="41" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4696,29 +4782,29 @@
         <v>46352</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I10" s="47" t="n">
         <v>130</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L10" s="38"/>
       <c r="M10" s="41" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4729,29 +4815,29 @@
         <v>46360</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E11" s="38"/>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I11" s="47" t="n">
         <v>80</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L11" s="38"/>
       <c r="M11" s="41" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4762,29 +4848,29 @@
         <v>46366</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E12" s="38"/>
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
       <c r="H12" s="38" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I12" s="47" t="n">
         <v>70</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L12" s="38"/>
       <c r="M12" s="41" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4795,29 +4881,29 @@
         <v>46370</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
       <c r="G13" s="38"/>
       <c r="H13" s="38" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I13" s="47" t="n">
         <v>180</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L13" s="38"/>
       <c r="M13" s="41" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4828,29 +4914,29 @@
         <v>46390</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
       <c r="G14" s="38"/>
       <c r="H14" s="38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I14" s="47" t="n">
         <v>150</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L14" s="38"/>
       <c r="M14" s="41" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4861,31 +4947,31 @@
         <v>46405</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I15" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L15" s="38"/>
       <c r="M15" s="41"/>
@@ -4898,35 +4984,35 @@
         <v>46405</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I16" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L16" s="38"/>
       <c r="M16" s="41" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4951,7 +5037,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I18" s="49" t="n">
         <f aca="false">SUMIF(J5:J16,"Booked",I5:I16)</f>
@@ -4960,7 +5046,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I19" s="49" t="n">
         <f aca="false">I17-I18</f>
@@ -4969,7 +5055,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -5010,82 +5096,82 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B5" s="28" t="n">
         <v>281.62</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>62.4</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B7" s="28" t="n">
         <v>13.64</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5101,225 +5187,225 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="31"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C14" s="29"/>
       <c r="D14" s="31"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C15" s="29"/>
       <c r="D15" s="31" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C17" s="29"/>
       <c r="D17" s="31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="31"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C20" s="29"/>
       <c r="D20" s="31" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C22" s="29"/>
       <c r="D22" s="31"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C23" s="29"/>
       <c r="D23" s="31"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C24" s="29"/>
       <c r="D24" s="31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C26" s="29"/>
       <c r="D26" s="31"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="31"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="31"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C29" s="29"/>
       <c r="D29" s="31"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="31"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C31" s="29"/>
       <c r="D31" s="31"/>
@@ -5377,17 +5463,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>4</v>
@@ -5396,46 +5482,46 @@
         <v>30</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2788.23</v>
+        <v>2766.01</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="51" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E5" s="52" t="n">
         <v>667.6</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I5" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Booked – pay later")</f>
@@ -5444,34 +5530,34 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E6" s="52" t="n">
         <v>281.62</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2788.23</v>
+        <v>2766.01</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="51" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B7" s="51" t="s">
         <v>11</v>
@@ -5480,65 +5566,65 @@
         <v>34</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E7" s="52" t="n">
         <v>36</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7211.77</v>
+        <v>7233.99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E8" s="52" t="n">
         <v>19</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="51" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E9" s="52" t="n">
         <v>87.7</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>13</v>
@@ -5547,18 +5633,18 @@
         <v>34</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E10" s="52" t="n">
         <v>239.55</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="51" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>13</v>
@@ -5567,38 +5653,38 @@
         <v>34</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E11" s="52" t="n">
         <v>52.24</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="51" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C12" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E12" s="52" t="n">
         <v>211.52</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="51" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B13" s="51" t="s">
         <v>13</v>
@@ -5607,18 +5693,18 @@
         <v>34</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E13" s="52" t="n">
         <v>137.26</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>13</v>
@@ -5627,18 +5713,18 @@
         <v>34</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E14" s="52" t="n">
         <v>338.05</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B15" s="51" t="s">
         <v>13</v>
@@ -5647,18 +5733,18 @@
         <v>34</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E15" s="52" t="n">
         <v>66.78</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>13</v>
@@ -5667,18 +5753,18 @@
         <v>34</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E16" s="52" t="n">
         <v>300.97</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>13</v>
@@ -5687,78 +5773,81 @@
         <v>34</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E17" s="52" t="n">
         <v>226.17</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="51" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E18" s="52" t="n">
         <v>13.64</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="51" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E19" s="52" t="n">
         <v>32.4</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="51" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B20" s="51" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E20" s="52" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="51" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B21" s="51" t="s">
         <v>11</v>
@@ -5767,41 +5856,44 @@
         <v>35</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E21" s="52" t="n">
-        <v>14.91</v>
+        <v>3.05</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="51" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B22" s="51" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>320</v>
+        <v>35</v>
       </c>
       <c r="E22" s="52" t="n">
-        <v>2.95</v>
+        <v>14.91</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="51" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B23" s="51" t="s">
         <v>11</v>
@@ -5810,21 +5902,21 @@
         <v>35</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E23" s="52" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="51" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B24" s="51" t="s">
         <v>11</v>
@@ -5833,44 +5925,44 @@
         <v>35</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>35</v>
+        <v>328</v>
       </c>
       <c r="E24" s="52" t="n">
-        <v>14.91</v>
+        <v>2.55</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="51" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B25" s="51" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E25" s="52" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B26" s="51" t="s">
         <v>11</v>
@@ -5879,67 +5971,67 @@
         <v>35</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E26" s="52" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="51" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="E27" s="52" t="n">
-        <v>5.9</v>
+        <v>8.87</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="51" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E28" s="52" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="51" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B29" s="51" t="s">
         <v>11</v>
@@ -5948,86 +6040,41 @@
         <v>35</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E29" s="52" t="n">
-        <v>8.87</v>
+        <v>1.98</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="B30" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="51" t="s">
-        <v>334</v>
-      </c>
-      <c r="E30" s="52" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F30" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="A30" s="51"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="B31" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="E31" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>337</v>
-      </c>
+      <c r="A31" s="51"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="51"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="51" t="s">
-        <v>339</v>
-      </c>
-      <c r="E32" s="52" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="F32" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>340</v>
-      </c>
+      <c r="A32" s="51"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="51"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="51"/>
@@ -13757,22 +13804,8 @@
       <c r="E998" s="52"/>
       <c r="F998" s="51"/>
     </row>
-    <row r="999" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A999" s="51"/>
-      <c r="B999" s="51"/>
-      <c r="C999" s="51"/>
-      <c r="D999" s="51"/>
-      <c r="E999" s="52"/>
-      <c r="F999" s="51"/>
-    </row>
-    <row r="1000" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1000" s="51"/>
-      <c r="B1000" s="51"/>
-      <c r="C1000" s="51"/>
-      <c r="D1000" s="51"/>
-      <c r="E1000" s="52"/>
-      <c r="F1000" s="51"/>
-    </row>
+    <row r="999" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B1000" type="list">
@@ -13780,7 +13813,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C1000" type="list">
-      <formula1>"Flights,Accommodation,Food,Local transport,Activities,Insurance &amp; admin,Other"</formula1>
+      <formula1>"Flights,Accommodation,Food,Local transport,Activities,Shopping &amp; misc,Insurance &amp; admin,Other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F1000" type="list">

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="345">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1042,6 +1042,24 @@
   </si>
   <si>
     <t xml:space="preserve">mvgm1pq2sx7l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvha28vt2umu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narita Express</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvhbcrzpy1g5</t>
   </si>
 </sst>
 </file>
@@ -1797,11 +1815,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>91.51</v>
+        <v>95.77</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1244.49</v>
+        <v>1240.23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1825,11 +1843,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1361.02</v>
+        <v>1384.27</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3659</v>
+        <v>3635.75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2091,11 +2109,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>43.26</v>
+        <v>47.52</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3346.74</v>
+        <v>3342.48</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2112,11 +2130,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>8.85</v>
+        <v>32.1</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>961.15</v>
+        <v>937.9</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
@@ -2217,11 +2235,11 @@
       </c>
       <c r="C28" s="24" t="n">
         <f aca="false">SUM(C20:C27)</f>
-        <v>2766.01</v>
+        <v>2793.52</v>
       </c>
       <c r="D28" s="24" t="n">
         <f aca="false">SUM(D20:D27)</f>
-        <v>7233.99</v>
+        <v>7206.48</v>
       </c>
       <c r="E28" s="25" t="n">
         <f aca="false">SUM(E20:E27)</f>
@@ -2246,7 +2264,7 @@
       </c>
       <c r="B32" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2766.01</v>
+        <v>2793.52</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2264,7 +2282,7 @@
       </c>
       <c r="B34" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7233.99</v>
+        <v>7206.48</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2293,7 +2311,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2766.01</v>
+        <v>2793.52</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2302,7 +2320,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">B39-B40</f>
-        <v>5268.26</v>
+        <v>5240.75</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5495,7 +5513,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2766.01</v>
+        <v>2793.52</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>293</v>
@@ -5552,7 +5570,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2766.01</v>
+        <v>2793.52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5579,7 +5597,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7233.99</v>
+        <v>7206.48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6053,20 +6071,50 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="51"/>
+      <c r="A30" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>340</v>
+      </c>
+      <c r="E30" s="52" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="51"/>
+      <c r="A31" s="51" t="s">
+        <v>342</v>
+      </c>
+      <c r="B31" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>343</v>
+      </c>
+      <c r="E31" s="52" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -327,7 +327,7 @@
     <t xml:space="preserve">Kuala Lumpur</t>
   </si>
   <si>
-    <t xml:space="preserve">26 – 29 Nov</t>
+    <t xml:space="preserve">26 – 30 Nov</t>
   </si>
   <si>
     <t xml:space="preserve">See friend 27 Nov</t>
@@ -336,7 +336,7 @@
     <t xml:space="preserve">Johor + Singapore day trips</t>
   </si>
   <si>
-    <t xml:space="preserve">29 Nov – 4 Dec</t>
+    <t xml:space="preserve">30 Nov – 4 Dec</t>
   </si>
   <si>
     <t xml:space="preserve">Food incl. £90 Singapore treat. SG Arrival Card each crossing</t>
@@ -831,7 +831,7 @@
     <t xml:space="preserve">Proof of leaving Taiwan</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirm Johor friend dates (29 Nov–4 Dec)</t>
+    <t xml:space="preserve">Confirm Johor friend dates (30 Nov–4 Dec)</t>
   </si>
   <si>
     <t xml:space="preserve">Soon</t>
@@ -1066,13 +1066,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\£#,##0;&quot;(£&quot;#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="ddd\ d\ mmm\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="ddd\ d\ mmm\ yyyy"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -1299,7 +1298,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1331,7 +1330,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1339,15 +1342,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1355,7 +1358,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1363,19 +1366,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1403,11 +1402,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1451,19 +1450,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1471,7 +1470,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1564,34 +1563,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1737,7 +1736,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
@@ -1919,11 +1918,11 @@
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">SUM(Itinerary!K16:K17)</f>
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">IF(C11=0,0,D11/C11)</f>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1931,7 +1930,7 @@
       </c>
       <c r="G11" s="12" t="n">
         <f aca="false">D11-F11</f>
-        <v>736</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1970,11 +1969,11 @@
         <v>23</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">SUM(Itinerary!D20:D20)</f>
+        <f aca="false">SUM(Itinerary!D20)</f>
         <v>20</v>
       </c>
       <c r="D13" s="10" t="n">
-        <f aca="false">SUM(Itinerary!K20:K20)</f>
+        <f aca="false">SUM(Itinerary!K20)</f>
         <v>1140</v>
       </c>
       <c r="E13" s="11" t="n">
@@ -2021,11 +2020,11 @@
       </c>
       <c r="D15" s="16" t="n">
         <f aca="false">SUM(D7:D14)</f>
-        <v>9647.02</v>
+        <v>9639.02</v>
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">IF(C15=0,0,D15/C15)</f>
-        <v>106.011208791209</v>
+        <v>105.923296703297</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -2084,7 +2083,7 @@
       </c>
       <c r="B21" s="17" t="n">
         <f aca="false">Itinerary!I25</f>
-        <v>3802.02</v>
+        <v>3812.02</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A21)</f>
@@ -2092,11 +2091,11 @@
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">B21-C21</f>
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B21/$B$3)</f>
-        <v>0.380202</v>
+        <v>0.381202</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2105,7 +2104,7 @@
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">Itinerary!J25</f>
-        <v>3390</v>
+        <v>3372</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
@@ -2113,11 +2112,11 @@
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3342.48</v>
+        <v>3324.48</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
-        <v>0.339</v>
+        <v>0.3372</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2210,7 +2209,7 @@
       </c>
       <c r="B27" s="21" t="n">
         <f aca="false">$B$3-SUM(B20:B26)</f>
-        <v>-1811.5</v>
+        <v>-1803.5</v>
       </c>
       <c r="C27" s="22" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,"Other")</f>
@@ -2218,11 +2217,11 @@
       </c>
       <c r="D27" s="22" t="n">
         <f aca="false">B27-C27</f>
-        <v>-1811.5</v>
+        <v>-1803.5</v>
       </c>
       <c r="E27" s="23" t="n">
         <f aca="false">IF($B$3=0,0,B27/$B$3)</f>
-        <v>-0.18115</v>
+        <v>-0.18035</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2249,7 +2248,7 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="str">
         <f aca="false">IF(B27&lt;0,"⚠ Plan is over budget by "&amp;TEXT(-B27,"£#,##0"),IF(B27&lt;200,"⚠ Buffer below £200","✓ Plan fits the budget with a buffer"))</f>
-        <v>⚠ Plan is over budget by £1,812</v>
+        <v>⚠ Plan is over budget by £1,804</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2338,7 +2337,7 @@
       </c>
       <c r="B43" s="27" t="n">
         <f aca="false">MAX(0,SUM(B20:B26)-B39)</f>
-        <v>3777.23</v>
+        <v>3769.23</v>
       </c>
     </row>
   </sheetData>
@@ -2358,7 +2357,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -3025,7 +3024,7 @@
         <v>100</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">Hotels!H16</f>
@@ -3042,19 +3041,19 @@
       </c>
       <c r="I16" s="12" t="n">
         <f aca="false">D16*E16</f>
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="J16" s="12" t="n">
         <f aca="false">D16*F16</f>
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="K16" s="12" t="n">
         <f aca="false">G16+H16+I16+J16+O16</f>
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="L16" s="12" t="n">
         <f aca="false">IF(D16=0,0,K16/D16)</f>
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="M16" s="9" t="str">
         <f aca="false">IF(Hotels!G16="Booked","Yes",IF(Hotels!G16="Staying with friends","N/A – host","No"))</f>
@@ -3064,7 +3063,7 @@
         <v>101</v>
       </c>
       <c r="O16" s="30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3078,7 +3077,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">Hotels!H17</f>
@@ -3095,19 +3094,19 @@
       </c>
       <c r="I17" s="12" t="n">
         <f aca="false">D17*E17</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J17" s="12" t="n">
         <f aca="false">D17*F17</f>
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="K17" s="12" t="n">
         <f aca="false">G17+H17+I17+J17+O17</f>
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="L17" s="12" t="n">
         <f aca="false">IF(D17=0,0,K17/D17)</f>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="M17" s="9" t="str">
         <f aca="false">IF(Hotels!G17="Booked","Yes",IF(Hotels!G17="Staying with friends","N/A – host","No"))</f>
@@ -3117,7 +3116,7 @@
         <v>104</v>
       </c>
       <c r="O17" s="30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3513,19 +3512,19 @@
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">SUM(I5:I24)</f>
-        <v>3802.02</v>
+        <v>3812.02</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">SUM(J5:J24)</f>
-        <v>3390</v>
+        <v>3372</v>
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">SUM(K5:K24)</f>
-        <v>9647.02</v>
+        <v>9639.02</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">IF(D25=0,0,K25/D25)</f>
-        <v>106.011208791209</v>
+        <v>105.923296703297</v>
       </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -3551,7 +3550,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -4110,11 +4109,11 @@
       </c>
       <c r="D16" s="34" t="n">
         <f aca="false">Itinerary!D16</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="36" t="n">
         <f aca="false">C16+D16</f>
-        <v>46355</v>
+        <v>46356</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="38" t="s">
@@ -4125,7 +4124,7 @@
       </c>
       <c r="I16" s="40" t="n">
         <f aca="false">D16*H16</f>
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="J16" s="38"/>
       <c r="K16" s="37"/>
@@ -4144,11 +4143,11 @@
       </c>
       <c r="C17" s="36" t="n">
         <f aca="false">E16</f>
-        <v>46355</v>
+        <v>46356</v>
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">Itinerary!D17</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">C17+D17</f>
@@ -4163,7 +4162,7 @@
       </c>
       <c r="I17" s="40" t="n">
         <f aca="false">D17*H17</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J17" s="38"/>
       <c r="K17" s="37"/>
@@ -4469,7 +4468,7 @@
       <c r="H25" s="42"/>
       <c r="I25" s="43" t="n">
         <f aca="false">SUM(I5:I24)</f>
-        <v>3802.02</v>
+        <v>3812.02</v>
       </c>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
@@ -4505,7 +4504,7 @@
       </c>
       <c r="C29" s="45" t="n">
         <f aca="false">SUMIF(G5:G24,"To book",I5:I24)+SUMIF(G5:G24,"Shortlisted",I5:I24)</f>
-        <v>2405</v>
+        <v>2415</v>
       </c>
     </row>
   </sheetData>
@@ -4540,7 +4539,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
@@ -5104,7 +5103,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
@@ -5465,7 +5464,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J1000"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -75,25 +75,25 @@
     <t xml:space="preserve">Vietnam</t>
   </si>
   <si>
-    <t xml:space="preserve">11 – 19 Nov</t>
+    <t xml:space="preserve">11 – 18 Nov</t>
   </si>
   <si>
     <t xml:space="preserve">Taiwan</t>
   </si>
   <si>
-    <t xml:space="preserve">19 – 26 Nov</t>
+    <t xml:space="preserve">18 – 26 Nov</t>
   </si>
   <si>
     <t xml:space="preserve">Malaysia &amp; Singapore</t>
   </si>
   <si>
-    <t xml:space="preserve">26 Nov – 4 Dec</t>
+    <t xml:space="preserve">26 Nov – 5 Dec</t>
   </si>
   <si>
     <t xml:space="preserve">Thailand</t>
   </si>
   <si>
-    <t xml:space="preserve">4 – 14 Dec</t>
+    <t xml:space="preserve">5 – 14 Dec</t>
   </si>
   <si>
     <t xml:space="preserve">14 Dec – 3 Jan</t>
@@ -300,7 +300,7 @@
     <t xml:space="preserve">Hanoi</t>
   </si>
   <si>
-    <t xml:space="preserve">14 – 19 Nov</t>
+    <t xml:space="preserve">14 – 18 Nov</t>
   </si>
   <si>
     <t xml:space="preserve">Food incl. £45 tasting-menu treat. Optional Ha Long Bay day trip (~£50). ~45 min to airport</t>
@@ -309,7 +309,7 @@
     <t xml:space="preserve">Taipei</t>
   </si>
   <si>
-    <t xml:space="preserve">19 – 23 Nov</t>
+    <t xml:space="preserve">18 – 23 Nov</t>
   </si>
   <si>
     <t xml:space="preserve">Food incl. £90 tasting-menu treat. Jiufen, Beitou hot springs</t>
@@ -336,7 +336,7 @@
     <t xml:space="preserve">Johor + Singapore day trips</t>
   </si>
   <si>
-    <t xml:space="preserve">30 Nov – 4 Dec</t>
+    <t xml:space="preserve">30 Nov – 5 Dec</t>
   </si>
   <si>
     <t xml:space="preserve">Food incl. £90 Singapore treat. SG Arrival Card each crossing</t>
@@ -345,7 +345,7 @@
     <t xml:space="preserve">Beach resort – Andaman coast</t>
   </si>
   <si>
-    <t xml:space="preserve">4 – 10 Dec</t>
+    <t xml:space="preserve">5 – 10 Dec</t>
   </si>
   <si>
     <t xml:space="preserve">Peak dry season. Food incl. £60 seafood treat. Khao Lak / Phuket / Krabi</t>
@@ -822,7 +822,7 @@
     <t xml:space="preserve">Book Tam Coc resort + airport pickup, and Hanoi hotel</t>
   </si>
   <si>
-    <t xml:space="preserve">Book Hanoi → Taipei (19 Nov)</t>
+    <t xml:space="preserve">Book Hanoi → Taipei (18 Nov)</t>
   </si>
   <si>
     <t xml:space="preserve">Book Kaohsiung → KL (26 Nov)</t>
@@ -831,7 +831,7 @@
     <t xml:space="preserve">Proof of leaving Taiwan</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirm Johor friend dates (30 Nov–4 Dec)</t>
+    <t xml:space="preserve">Confirm Johor friend dates (30 Nov–5 Dec)</t>
   </si>
   <si>
     <t xml:space="preserve">Soon</t>
@@ -846,7 +846,7 @@
     <t xml:space="preserve">Book KL + Johor stays</t>
   </si>
   <si>
-    <t xml:space="preserve">Choose Thailand resort (4–10 Dec) + Chiang Mai (10–14 Dec)</t>
+    <t xml:space="preserve">Choose Thailand resort (5–10 Dec) + Chiang Mai (10–14 Dec)</t>
   </si>
   <si>
     <t xml:space="preserve">Peak season – book ahead</t>
@@ -876,7 +876,7 @@
     <t xml:space="preserve">Taiwan online arrival card</t>
   </si>
   <si>
-    <t xml:space="preserve">Before 19 Nov</t>
+    <t xml:space="preserve">Before 18 Nov</t>
   </si>
   <si>
     <t xml:space="preserve">Malaysia Digital Arrival Card (MDAC)</t>
@@ -1858,15 +1858,15 @@
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">SUM(Itinerary!D12:D13)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">SUM(Itinerary!K12:K13)</f>
-        <v>575</v>
+        <v>518</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">IF(C9=0,0,D9/C9)</f>
-        <v>71.875</v>
+        <v>74</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Vietnam")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Vietnam",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Vietnam",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="G9" s="12" t="n">
         <f aca="false">D9-F9</f>
-        <v>575</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1886,15 +1886,15 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(Itinerary!D14:D15)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">SUM(Itinerary!K14:K15)</f>
-        <v>735</v>
+        <v>832.5</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">IF(C10=0,0,D10/C10)</f>
-        <v>105</v>
+        <v>104.0625</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Taiwan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Taiwan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Taiwan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="G10" s="12" t="n">
         <f aca="false">D10-F10</f>
-        <v>735</v>
+        <v>832.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1914,15 +1914,15 @@
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">SUM(Itinerary!D16:D17)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">SUM(Itinerary!K16:K17)</f>
-        <v>728</v>
+        <v>798</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">IF(C11=0,0,D11/C11)</f>
-        <v>91</v>
+        <v>88.6666666666667</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Malaysia &amp; Singapore",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="G11" s="12" t="n">
         <f aca="false">D11-F11</f>
-        <v>728</v>
+        <v>798</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1942,15 +1942,15 @@
       </c>
       <c r="C12" s="9" t="n">
         <f aca="false">SUM(Itinerary!D18:D19)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">SUM(Itinerary!K18:K19)</f>
-        <v>1245</v>
+        <v>1105</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">IF(C12=0,0,D12/C12)</f>
-        <v>124.5</v>
+        <v>122.777777777778</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Thailand")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Thailand",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Thailand",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="G12" s="12" t="n">
         <f aca="false">D12-F12</f>
-        <v>1245</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2020,11 +2020,11 @@
       </c>
       <c r="D15" s="16" t="n">
         <f aca="false">SUM(D7:D14)</f>
-        <v>9639.02</v>
+        <v>9609.52</v>
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">IF(C15=0,0,D15/C15)</f>
-        <v>105.923296703297</v>
+        <v>105.599120879121</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B21" s="17" t="n">
         <f aca="false">Itinerary!I25</f>
-        <v>3812.02</v>
+        <v>3767.02</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A21)</f>
@@ -2091,11 +2091,11 @@
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">B21-C21</f>
-        <v>2415</v>
+        <v>2370</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B21/$B$3)</f>
-        <v>0.381202</v>
+        <v>0.376702</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">Itinerary!J25</f>
-        <v>3372</v>
+        <v>3387.5</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
@@ -2112,11 +2112,11 @@
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3324.48</v>
+        <v>3339.98</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
-        <v>0.3372</v>
+        <v>0.33875</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="B27" s="21" t="n">
         <f aca="false">$B$3-SUM(B20:B26)</f>
-        <v>-1803.5</v>
+        <v>-1774</v>
       </c>
       <c r="C27" s="22" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,"Other")</f>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="D27" s="22" t="n">
         <f aca="false">B27-C27</f>
-        <v>-1803.5</v>
+        <v>-1774</v>
       </c>
       <c r="E27" s="23" t="n">
         <f aca="false">IF($B$3=0,0,B27/$B$3)</f>
-        <v>-0.18035</v>
+        <v>-0.1774</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2248,7 +2248,7 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="str">
         <f aca="false">IF(B27&lt;0,"⚠ Plan is over budget by "&amp;TEXT(-B27,"£#,##0"),IF(B27&lt;200,"⚠ Buffer below £200","✓ Plan fits the budget with a buffer"))</f>
-        <v>⚠ Plan is over budget by £1,804</v>
+        <v>⚠ Plan is over budget by £1,774</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B43" s="27" t="n">
         <f aca="false">MAX(0,SUM(B20:B26)-B39)</f>
-        <v>3769.23</v>
+        <v>3739.73</v>
       </c>
     </row>
   </sheetData>
@@ -2865,7 +2865,7 @@
         <v>91</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="10" t="n">
         <f aca="false">Hotels!H13</f>
@@ -2882,19 +2882,19 @@
       </c>
       <c r="I13" s="12" t="n">
         <f aca="false">D13*E13</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J13" s="12" t="n">
         <f aca="false">D13*F13</f>
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="K13" s="12" t="n">
         <f aca="false">G13+H13+I13+J13+O13</f>
-        <v>370</v>
+        <v>313</v>
       </c>
       <c r="L13" s="12" t="n">
         <f aca="false">IF(D13=0,0,K13/D13)</f>
-        <v>74</v>
+        <v>78.25</v>
       </c>
       <c r="M13" s="9" t="str">
         <f aca="false">IF(Hotels!G13="Booked","Yes",IF(Hotels!G13="Staying with friends","N/A – host","No"))</f>
@@ -2904,7 +2904,7 @@
         <v>92</v>
       </c>
       <c r="O13" s="30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2918,7 +2918,7 @@
         <v>94</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">Hotels!H14</f>
@@ -2935,19 +2935,19 @@
       </c>
       <c r="I14" s="12" t="n">
         <f aca="false">D14*E14</f>
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="J14" s="12" t="n">
         <f aca="false">D14*F14</f>
-        <v>190</v>
+        <v>237.5</v>
       </c>
       <c r="K14" s="12" t="n">
         <f aca="false">G14+H14+I14+J14+O14</f>
-        <v>460</v>
+        <v>557.5</v>
       </c>
       <c r="L14" s="12" t="n">
         <f aca="false">IF(D14=0,0,K14/D14)</f>
-        <v>115</v>
+        <v>111.5</v>
       </c>
       <c r="M14" s="9" t="str">
         <f aca="false">IF(Hotels!G14="Booked","Yes",IF(Hotels!G14="Staying with friends","N/A – host","No"))</f>
@@ -2957,7 +2957,7 @@
         <v>95</v>
       </c>
       <c r="O14" s="30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3077,7 +3077,7 @@
         <v>103</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">Hotels!H17</f>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="I17" s="12" t="n">
         <f aca="false">D17*E17</f>
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="J17" s="12" t="n">
         <f aca="false">D17*F17</f>
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K17" s="12" t="n">
         <f aca="false">G17+H17+I17+J17+O17</f>
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="L17" s="12" t="n">
         <f aca="false">IF(D17=0,0,K17/D17)</f>
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="M17" s="9" t="str">
         <f aca="false">IF(Hotels!G17="Booked","Yes",IF(Hotels!G17="Staying with friends","N/A – host","No"))</f>
@@ -3116,7 +3116,7 @@
         <v>104</v>
       </c>
       <c r="O17" s="30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3130,7 +3130,7 @@
         <v>106</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">Hotels!H18</f>
@@ -3147,19 +3147,19 @@
       </c>
       <c r="I18" s="12" t="n">
         <f aca="false">D18*E18</f>
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="J18" s="12" t="n">
         <f aca="false">D18*F18</f>
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="K18" s="12" t="n">
         <f aca="false">G18+H18+I18+J18+O18</f>
-        <v>920</v>
+        <v>780</v>
       </c>
       <c r="L18" s="12" t="n">
         <f aca="false">IF(D18=0,0,K18/D18)</f>
-        <v>153.333333333333</v>
+        <v>156</v>
       </c>
       <c r="M18" s="9" t="str">
         <f aca="false">IF(Hotels!G18="Booked","Yes",IF(Hotels!G18="Staying with friends","N/A – host","No"))</f>
@@ -3169,7 +3169,7 @@
         <v>107</v>
       </c>
       <c r="O18" s="30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3512,19 +3512,19 @@
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">SUM(I5:I24)</f>
-        <v>3812.02</v>
+        <v>3767.02</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">SUM(J5:J24)</f>
-        <v>3372</v>
+        <v>3387.5</v>
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">SUM(K5:K24)</f>
-        <v>9639.02</v>
+        <v>9609.52</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">IF(D25=0,0,K25/D25)</f>
-        <v>105.923296703297</v>
+        <v>105.599120879121</v>
       </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="D13" s="34" t="n">
         <f aca="false">Itinerary!D13</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="36" t="n">
         <f aca="false">C13+D13</f>
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="F13" s="37"/>
       <c r="G13" s="38" t="s">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="I13" s="40" t="n">
         <f aca="false">D13*H13</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J13" s="38"/>
       <c r="K13" s="37"/>
@@ -4029,11 +4029,11 @@
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">E13</f>
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="D14" s="34" t="n">
         <f aca="false">Itinerary!D14</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="36" t="n">
         <f aca="false">C14+D14</f>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="I14" s="40" t="n">
         <f aca="false">D14*H14</f>
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="J14" s="38"/>
       <c r="K14" s="37"/>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="D17" s="34" t="n">
         <f aca="false">Itinerary!D17</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">C17+D17</f>
-        <v>46360</v>
+        <v>46361</v>
       </c>
       <c r="F17" s="37"/>
       <c r="G17" s="38" t="s">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I17" s="40" t="n">
         <f aca="false">D17*H17</f>
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="J17" s="38"/>
       <c r="K17" s="37"/>
@@ -4183,11 +4183,11 @@
       </c>
       <c r="C18" s="36" t="n">
         <f aca="false">E17</f>
-        <v>46360</v>
+        <v>46361</v>
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">Itinerary!D18</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="36" t="n">
         <f aca="false">C18+D18</f>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I18" s="40" t="n">
         <f aca="false">D18*H18</f>
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="J18" s="38"/>
       <c r="K18" s="37"/>
@@ -4468,7 +4468,7 @@
       <c r="H25" s="42"/>
       <c r="I25" s="43" t="n">
         <f aca="false">SUM(I5:I24)</f>
-        <v>3812.02</v>
+        <v>3767.02</v>
       </c>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C29" s="45" t="n">
         <f aca="false">SUMIF(G5:G24,"To book",I5:I24)+SUMIF(G5:G24,"Shortlisted",I5:I24)</f>
-        <v>2415</v>
+        <v>2370</v>
       </c>
     </row>
   </sheetData>
@@ -4763,7 +4763,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="35" t="n">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>204</v>
@@ -4829,7 +4829,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="35" t="n">
-        <v>46360</v>
+        <v>46361</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>213</v>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="347">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1060,18 +1060,25 @@
   </si>
   <si>
     <t xml:space="preserve">mvhbcrzpy1g5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvhn4eivoe6v</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\£#,##0;&quot;(£&quot;#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="ddd\ d\ mmm\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="ddd\ d\ mmm\ yyyy"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -1298,7 +1305,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1330,11 +1337,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1342,15 +1345,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1358,7 +1361,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1366,15 +1369,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1402,11 +1409,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1450,19 +1457,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1470,7 +1477,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1563,34 +1570,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1736,7 +1743,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
@@ -1814,11 +1821,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>95.77</v>
+        <v>102.53</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1240.23</v>
+        <v>1233.47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2108,11 +2115,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>47.52</v>
+        <v>54.28</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3339.98</v>
+        <v>3333.22</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2234,11 +2241,11 @@
       </c>
       <c r="C28" s="24" t="n">
         <f aca="false">SUM(C20:C27)</f>
-        <v>2793.52</v>
+        <v>2800.28</v>
       </c>
       <c r="D28" s="24" t="n">
         <f aca="false">SUM(D20:D27)</f>
-        <v>7206.48</v>
+        <v>7199.72</v>
       </c>
       <c r="E28" s="25" t="n">
         <f aca="false">SUM(E20:E27)</f>
@@ -2263,7 +2270,7 @@
       </c>
       <c r="B32" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2793.52</v>
+        <v>2800.28</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2281,7 +2288,7 @@
       </c>
       <c r="B34" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7206.48</v>
+        <v>7199.72</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2310,7 +2317,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2793.52</v>
+        <v>2800.28</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2319,7 +2326,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">B39-B40</f>
-        <v>5240.75</v>
+        <v>5233.99</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2357,7 +2364,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -3550,7 +3557,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -4539,7 +4546,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
@@ -5103,7 +5110,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
@@ -5464,7 +5471,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J1000"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
@@ -5512,7 +5519,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2793.52</v>
+        <v>2800.28</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>293</v>
@@ -5569,7 +5576,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2793.52</v>
+        <v>2800.28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5596,7 +5603,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7206.48</v>
+        <v>7199.72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6116,12 +6123,27 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="51"/>
+      <c r="A32" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>345</v>
+      </c>
+      <c r="E32" s="52" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="348">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1066,6 +1066,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvhn4eivoe6v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvhoyq93mkft</t>
   </si>
 </sst>
 </file>
@@ -1821,11 +1824,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>102.53</v>
+        <v>104.52</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1233.47</v>
+        <v>1231.48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2115,11 +2118,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>54.28</v>
+        <v>56.27</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3333.22</v>
+        <v>3331.23</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2241,11 +2244,11 @@
       </c>
       <c r="C28" s="24" t="n">
         <f aca="false">SUM(C20:C27)</f>
-        <v>2800.28</v>
+        <v>2802.27</v>
       </c>
       <c r="D28" s="24" t="n">
         <f aca="false">SUM(D20:D27)</f>
-        <v>7199.72</v>
+        <v>7197.73</v>
       </c>
       <c r="E28" s="25" t="n">
         <f aca="false">SUM(E20:E27)</f>
@@ -2270,7 +2273,7 @@
       </c>
       <c r="B32" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2800.28</v>
+        <v>2802.27</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2288,7 +2291,7 @@
       </c>
       <c r="B34" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7199.72</v>
+        <v>7197.73</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2317,7 +2320,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2800.28</v>
+        <v>2802.27</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2326,7 +2329,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">B39-B40</f>
-        <v>5233.99</v>
+        <v>5232</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5519,7 +5522,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2800.28</v>
+        <v>2802.27</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>293</v>
@@ -5576,7 +5579,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2800.28</v>
+        <v>2802.27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5603,7 +5606,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7199.72</v>
+        <v>7197.73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6146,12 +6149,27 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="51"/>
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="51"/>
+      <c r="A33" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="B33" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>337</v>
+      </c>
+      <c r="E33" s="52" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="350">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1069,6 +1069,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvhoyq93mkft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waffle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvhozxevm8t8</t>
   </si>
 </sst>
 </file>
@@ -1824,11 +1830,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>104.52</v>
+        <v>107.3</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1231.48</v>
+        <v>1228.7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2118,11 +2124,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>56.27</v>
+        <v>59.05</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3331.23</v>
+        <v>3328.45</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2244,11 +2250,11 @@
       </c>
       <c r="C28" s="24" t="n">
         <f aca="false">SUM(C20:C27)</f>
-        <v>2802.27</v>
+        <v>2805.05</v>
       </c>
       <c r="D28" s="24" t="n">
         <f aca="false">SUM(D20:D27)</f>
-        <v>7197.73</v>
+        <v>7194.95</v>
       </c>
       <c r="E28" s="25" t="n">
         <f aca="false">SUM(E20:E27)</f>
@@ -2273,7 +2279,7 @@
       </c>
       <c r="B32" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2802.27</v>
+        <v>2805.05</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2291,7 +2297,7 @@
       </c>
       <c r="B34" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7197.73</v>
+        <v>7194.95</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2320,7 +2326,7 @@
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2802.27</v>
+        <v>2805.05</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2329,7 +2335,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">B39-B40</f>
-        <v>5232</v>
+        <v>5229.22</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5522,7 +5528,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2802.27</v>
+        <v>2805.05</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>293</v>
@@ -5579,7 +5585,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2802.27</v>
+        <v>2805.05</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5606,7 +5612,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7197.73</v>
+        <v>7194.95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6172,12 +6178,27 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="51"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="51"/>
+      <c r="A34" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>348</v>
+      </c>
+      <c r="E34" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="352">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Ground costs only (accommodation, food, local transport, activities, shopping &amp; misc). Korea &amp; Japan appear twice – spend is combined on their first row.</t>
+    <t xml:space="preserve">Ground costs only (accommodation, food, local transport, trains &amp; intercity, activities, shopping &amp; misc). Korea &amp; Japan appear twice – spend is combined on their first row.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Budget by category</t>
@@ -138,6 +138,9 @@
     <t xml:space="preserve">Local transport</t>
   </si>
   <si>
+    <t xml:space="preserve">Trains &amp; intercity</t>
+  </si>
+  <si>
     <t xml:space="preserve">Activities</t>
   </si>
   <si>
@@ -225,6 +228,9 @@
     <t xml:space="preserve">Shopping &amp; misc (£)</t>
   </si>
   <si>
+    <t xml:space="preserve">Trains &amp; intercity (£)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Incheon – Incheon Airport Hotel Seattle</t>
   </si>
   <si>
@@ -249,7 +255,7 @@
     <t xml:space="preserve">22 – 25 Oct</t>
   </si>
   <si>
-    <t xml:space="preserve">MARATHON 25 Oct. Arrive Narita 15:30 on 22 Oct – Narita Express / limousine bus (~90 min)</t>
+    <t xml:space="preserve">MARATHON 25 Oct. Arrive Narita 15:30 on 22 Oct. Trains: Narita Express to Yokohama (~£23).</t>
   </si>
   <si>
     <t xml:space="preserve">Shizuoka</t>
@@ -267,7 +273,7 @@
     <t xml:space="preserve">28 Oct – 2 Nov</t>
   </si>
   <si>
-    <t xml:space="preserve">Day-trip base: Magome–Tsumago walk, Inuyama, Gujo Hachiman, Ise. Transport incl. Shizuoka → Nagoya</t>
+    <t xml:space="preserve">Day-trip base: Magome–Tsumago walk, Inuyama, Gujo Hachiman, Ise. Trains: Shizuoka → Nagoya shinkansen (~£26).</t>
   </si>
   <si>
     <t xml:space="preserve">Takayama</t>
@@ -276,7 +282,7 @@
     <t xml:space="preserve">2 – 5 Nov</t>
   </si>
   <si>
-    <t xml:space="preserve">Peak autumn colour + Culture Day 3 Nov. Shirakawa-go day trip. Transport incl. Nagoya → Takayama</t>
+    <t xml:space="preserve">Peak autumn colour + Culture Day 3 Nov. Shirakawa-go day trip. Trains: Nagoya → Takayama limited express (~£31).</t>
   </si>
   <si>
     <t xml:space="preserve">Osaka (stay in Namba)</t>
@@ -321,7 +327,7 @@
     <t xml:space="preserve">23 – 26 Nov</t>
   </si>
   <si>
-    <t xml:space="preserve">Food capital. Transport incl. HSR from Taipei + Kaohsiung airport for 26 Nov flight</t>
+    <t xml:space="preserve">Food capital. Local transport incl. getting to Kaohsiung airport for the 26 Nov flight. Trains: Taipei → Tainan high-speed rail (~£33).</t>
   </si>
   <si>
     <t xml:space="preserve">Kuala Lumpur</t>
@@ -399,7 +405,7 @@
     <t xml:space="preserve">16 – 18 Jan</t>
   </si>
   <si>
-    <t xml:space="preserve">Transport incl. Hakodate → Tokyo shinkansen. Flight home 08:30 on 18 Jan</t>
+    <t xml:space="preserve">Flight home 08:30 on 18 Jan. Trains: Hakodate → Tokyo shinkansen (~£118).</t>
   </si>
   <si>
     <t xml:space="preserve">Hotels &amp; stays – one row per stop</t>
@@ -1081,13 +1087,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\£#,##0;&quot;(£&quot;#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="ddd\ d\ mmm\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="ddd\ d\ mmm\ yyyy"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -1314,7 +1319,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1346,7 +1351,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1354,15 +1363,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1370,7 +1379,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1378,19 +1387,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1418,11 +1423,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1466,19 +1471,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1486,7 +1491,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1579,34 +1584,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1751,8 +1756,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
@@ -2141,19 +2146,19 @@
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">Itinerary!G25</f>
-        <v>970</v>
+        <v>739</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>32.1</v>
+        <v>8.85</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>937.9</v>
+        <v>730.15</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
-        <v>0.097</v>
+        <v>0.0739</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2161,20 +2166,20 @@
         <v>37</v>
       </c>
       <c r="B24" s="17" t="n">
-        <f aca="false">Itinerary!H25</f>
-        <v>1030</v>
+        <f aca="false">Itinerary!P25</f>
+        <v>231</v>
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A24)</f>
-        <v>0</v>
+        <v>23.25</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">B24-C24</f>
-        <v>1030</v>
+        <v>207.75</v>
       </c>
       <c r="E24" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B24/$B$3)</f>
-        <v>0.103</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2182,20 +2187,20 @@
         <v>38</v>
       </c>
       <c r="B25" s="17" t="n">
-        <f aca="false">Itinerary!O25</f>
-        <v>455</v>
+        <f aca="false">Itinerary!H25</f>
+        <v>1030</v>
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A25)</f>
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="D25" s="18" t="n">
         <f aca="false">B25-C25</f>
-        <v>451.6</v>
+        <v>1030</v>
       </c>
       <c r="E25" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B25/$B$3)</f>
-        <v>0.0455</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2203,130 +2208,142 @@
         <v>39</v>
       </c>
       <c r="B26" s="17" t="n">
+        <f aca="false">Itinerary!O25</f>
+        <v>455</v>
+      </c>
+      <c r="C26" s="18" t="n">
+        <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
+        <v>3.4</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <f aca="false">B26-C26</f>
+        <v>451.6</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
+        <v>0.0455</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="17" t="n">
         <f aca="false">'Admin &amp; checklist'!B9</f>
         <v>457.66</v>
       </c>
-      <c r="C26" s="18" t="n">
-        <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
+      <c r="C27" s="18" t="n">
+        <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A27)</f>
         <v>346.66</v>
       </c>
-      <c r="D26" s="18" t="n">
-        <f aca="false">B26-C26</f>
+      <c r="D27" s="18" t="n">
+        <f aca="false">B27-C27</f>
         <v>111</v>
       </c>
-      <c r="E26" s="19" t="n">
-        <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
+      <c r="E27" s="19" t="n">
+        <f aca="false">IF($B$3=0,0,B27/$B$3)</f>
         <v>0.045766</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="21" t="n">
-        <f aca="false">$B$3-SUM(B20:B26)</f>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="21" t="n">
+        <f aca="false">$B$3-SUM(B20:B27)</f>
         <v>-1774</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C28" s="22" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,"Other")</f>
         <v>0</v>
       </c>
-      <c r="D27" s="22" t="n">
-        <f aca="false">B27-C27</f>
+      <c r="D28" s="22" t="n">
+        <f aca="false">B28-C28</f>
         <v>-1774</v>
       </c>
-      <c r="E27" s="23" t="n">
-        <f aca="false">IF($B$3=0,0,B27/$B$3)</f>
+      <c r="E28" s="23" t="n">
+        <f aca="false">IF($B$3=0,0,B28/$B$3)</f>
         <v>-0.1774</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="24" t="n">
-        <f aca="false">SUM(B20:B27)</f>
+      <c r="B29" s="24" t="n">
+        <f aca="false">SUM(B20:B28)</f>
         <v>10000</v>
       </c>
-      <c r="C28" s="24" t="n">
-        <f aca="false">SUM(C20:C27)</f>
+      <c r="C29" s="24" t="n">
+        <f aca="false">SUM(C20:C28)</f>
         <v>2805.05</v>
       </c>
-      <c r="D28" s="24" t="n">
-        <f aca="false">SUM(D20:D27)</f>
+      <c r="D29" s="24" t="n">
+        <f aca="false">SUM(D20:D28)</f>
         <v>7194.95</v>
       </c>
-      <c r="E28" s="25" t="n">
-        <f aca="false">SUM(E20:E27)</f>
+      <c r="E29" s="25" t="n">
+        <f aca="false">SUM(E20:E28)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="str">
-        <f aca="false">IF(B27&lt;0,"⚠ Plan is over budget by "&amp;TEXT(-B27,"£#,##0"),IF(B27&lt;200,"⚠ Buffer below £200","✓ Plan fits the budget with a buffer"))</f>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="str">
+        <f aca="false">IF(B28&lt;0,"⚠ Plan is over budget by "&amp;TEXT(-B28,"£#,##0"),IF(B28&lt;200,"⚠ Buffer below £200","✓ Plan fits the budget with a buffer"))</f>
         <v>⚠ Plan is over budget by £1,774</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="B32" s="27" t="n">
-        <f aca="false">Tracker!I4</f>
-        <v>2805.05</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="22" t="n">
-        <f aca="false">Tracker!I5</f>
-        <v>0</v>
+      <c r="B33" s="27" t="n">
+        <f aca="false">Tracker!I4</f>
+        <v>2805.05</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="27" t="n">
+      <c r="B34" s="22" t="n">
+        <f aca="false">Tracker!I5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
         <v>7194.95</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
     </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B39" s="28" t="n">
-        <v>8034.27</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="27" t="n">
-        <f aca="false">Tracker!I4</f>
-        <v>2805.05</v>
+      <c r="B40" s="28" t="n">
+        <v>8034.27</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2334,8 +2351,8 @@
         <v>49</v>
       </c>
       <c r="B41" s="27" t="n">
-        <f aca="false">B39-B40</f>
-        <v>5229.22</v>
+        <f aca="false">Tracker!I4</f>
+        <v>2805.05</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2343,8 +2360,8 @@
         <v>50</v>
       </c>
       <c r="B42" s="27" t="n">
-        <f aca="false">MAX(0,B3-B39)</f>
-        <v>1965.73</v>
+        <f aca="false">B40-B41</f>
+        <v>5229.22</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2352,7 +2369,16 @@
         <v>51</v>
       </c>
       <c r="B43" s="27" t="n">
-        <f aca="false">MAX(0,SUM(B20:B26)-B39)</f>
+        <f aca="false">MAX(0,B3-B40)</f>
+        <v>1965.73</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="27" t="n">
+        <f aca="false">MAX(0,SUM(B20:B27)-B40)</f>
         <v>3739.73</v>
       </c>
     </row>
@@ -2372,8 +2398,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -2386,17 +2412,17 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2404,7 +2430,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>5</v>
@@ -2413,37 +2439,40 @@
         <v>6</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2451,10 +2480,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" s="29" t="n">
         <v>1</v>
@@ -2481,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="K5" s="12" t="n">
-        <f aca="false">G5+H5+I5+J5+O5</f>
+        <f aca="false">G5+H5+I5+J5+O5+P5</f>
         <v>71</v>
       </c>
       <c r="L5" s="12" t="n">
@@ -2493,10 +2522,13 @@
         <v>Yes</v>
       </c>
       <c r="N5" s="31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O5" s="30" t="n">
         <v>5</v>
+      </c>
+      <c r="P5" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2504,10 +2536,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D6" s="29" t="n">
         <v>2</v>
@@ -2534,7 +2566,7 @@
         <v>60</v>
       </c>
       <c r="K6" s="12" t="n">
-        <f aca="false">G6+H6+I6+J6+O6</f>
+        <f aca="false">G6+H6+I6+J6+O6+P6</f>
         <v>125</v>
       </c>
       <c r="L6" s="12" t="n">
@@ -2546,10 +2578,13 @@
         <v>N/A – host</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O6" s="30" t="n">
         <v>10</v>
+      </c>
+      <c r="P6" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2557,10 +2592,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="29" t="n">
         <v>3</v>
@@ -2573,7 +2608,7 @@
         <v>38</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H7" s="30" t="n">
         <v>30</v>
@@ -2587,7 +2622,7 @@
         <v>114</v>
       </c>
       <c r="K7" s="12" t="n">
-        <f aca="false">G7+H7+I7+J7+O7</f>
+        <f aca="false">G7+H7+I7+J7+O7+P7</f>
         <v>490.79</v>
       </c>
       <c r="L7" s="12" t="n">
@@ -2599,10 +2634,13 @@
         <v>Yes</v>
       </c>
       <c r="N7" s="31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O7" s="30" t="n">
         <v>15</v>
+      </c>
+      <c r="P7" s="30" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2610,10 +2648,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" s="29" t="n">
         <v>3</v>
@@ -2640,7 +2678,7 @@
         <v>114</v>
       </c>
       <c r="K8" s="12" t="n">
-        <f aca="false">G8+H8+I8+J8+O8</f>
+        <f aca="false">G8+H8+I8+J8+O8+P8</f>
         <v>428.04</v>
       </c>
       <c r="L8" s="12" t="n">
@@ -2652,10 +2690,13 @@
         <v>Yes</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O8" s="30" t="n">
         <v>15</v>
+      </c>
+      <c r="P8" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2663,10 +2704,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" s="29" t="n">
         <v>5</v>
@@ -2679,7 +2720,7 @@
         <v>38</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="H9" s="30" t="n">
         <v>60</v>
@@ -2693,7 +2734,7 @@
         <v>190</v>
       </c>
       <c r="K9" s="12" t="n">
-        <f aca="false">G9+H9+I9+J9+O9</f>
+        <f aca="false">G9+H9+I9+J9+O9+P9</f>
         <v>688.05</v>
       </c>
       <c r="L9" s="12" t="n">
@@ -2705,10 +2746,13 @@
         <v>Yes</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O9" s="30" t="n">
         <v>25</v>
+      </c>
+      <c r="P9" s="30" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2716,10 +2760,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" s="29" t="n">
         <v>3</v>
@@ -2732,7 +2776,7 @@
         <v>38</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H10" s="30" t="n">
         <v>40</v>
@@ -2746,7 +2790,7 @@
         <v>114</v>
       </c>
       <c r="K10" s="12" t="n">
-        <f aca="false">G10+H10+I10+J10+O10</f>
+        <f aca="false">G10+H10+I10+J10+O10+P10</f>
         <v>440.17</v>
       </c>
       <c r="L10" s="12" t="n">
@@ -2758,10 +2802,13 @@
         <v>Yes</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O10" s="30" t="n">
         <v>15</v>
+      </c>
+      <c r="P10" s="30" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2769,10 +2816,10 @@
         <v>13</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="29" t="n">
         <v>6</v>
@@ -2799,7 +2846,7 @@
         <v>348</v>
       </c>
       <c r="K11" s="12" t="n">
-        <f aca="false">G11+H11+I11+J11+O11</f>
+        <f aca="false">G11+H11+I11+J11+O11+P11</f>
         <v>818.97</v>
       </c>
       <c r="L11" s="12" t="n">
@@ -2811,10 +2858,13 @@
         <v>Yes</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O11" s="30" t="n">
         <v>30</v>
+      </c>
+      <c r="P11" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2822,10 +2872,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D12" s="29" t="n">
         <v>3</v>
@@ -2852,7 +2902,7 @@
         <v>45</v>
       </c>
       <c r="K12" s="12" t="n">
-        <f aca="false">G12+H12+I12+J12+O12</f>
+        <f aca="false">G12+H12+I12+J12+O12+P12</f>
         <v>205</v>
       </c>
       <c r="L12" s="12" t="n">
@@ -2864,10 +2914,13 @@
         <v>No</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O12" s="30" t="n">
         <v>15</v>
+      </c>
+      <c r="P12" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2875,10 +2928,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D13" s="29" t="n">
         <v>4</v>
@@ -2905,7 +2958,7 @@
         <v>108</v>
       </c>
       <c r="K13" s="12" t="n">
-        <f aca="false">G13+H13+I13+J13+O13</f>
+        <f aca="false">G13+H13+I13+J13+O13+P13</f>
         <v>313</v>
       </c>
       <c r="L13" s="12" t="n">
@@ -2917,10 +2970,13 @@
         <v>No</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O13" s="30" t="n">
         <v>20</v>
+      </c>
+      <c r="P13" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2928,10 +2984,10 @@
         <v>17</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D14" s="29" t="n">
         <v>5</v>
@@ -2958,7 +3014,7 @@
         <v>237.5</v>
       </c>
       <c r="K14" s="12" t="n">
-        <f aca="false">G14+H14+I14+J14+O14</f>
+        <f aca="false">G14+H14+I14+J14+O14+P14</f>
         <v>557.5</v>
       </c>
       <c r="L14" s="12" t="n">
@@ -2970,10 +3026,13 @@
         <v>No</v>
       </c>
       <c r="N14" s="31" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O14" s="30" t="n">
         <v>25</v>
+      </c>
+      <c r="P14" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2981,10 +3040,10 @@
         <v>17</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D15" s="29" t="n">
         <v>3</v>
@@ -2997,7 +3056,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="H15" s="30" t="n">
         <v>30</v>
@@ -3011,7 +3070,7 @@
         <v>75</v>
       </c>
       <c r="K15" s="12" t="n">
-        <f aca="false">G15+H15+I15+J15+O15</f>
+        <f aca="false">G15+H15+I15+J15+O15+P15</f>
         <v>275</v>
       </c>
       <c r="L15" s="12" t="n">
@@ -3023,10 +3082,13 @@
         <v>No</v>
       </c>
       <c r="N15" s="31" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O15" s="30" t="n">
         <v>15</v>
+      </c>
+      <c r="P15" s="30" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3034,10 +3096,10 @@
         <v>19</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D16" s="29" t="n">
         <v>4</v>
@@ -3064,7 +3126,7 @@
         <v>88</v>
       </c>
       <c r="K16" s="12" t="n">
-        <f aca="false">G16+H16+I16+J16+O16</f>
+        <f aca="false">G16+H16+I16+J16+O16+P16</f>
         <v>308</v>
       </c>
       <c r="L16" s="12" t="n">
@@ -3076,10 +3138,13 @@
         <v>No</v>
       </c>
       <c r="N16" s="31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O16" s="30" t="n">
         <v>20</v>
+      </c>
+      <c r="P16" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3087,10 +3152,10 @@
         <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D17" s="29" t="n">
         <v>5</v>
@@ -3117,7 +3182,7 @@
         <v>200</v>
       </c>
       <c r="K17" s="12" t="n">
-        <f aca="false">G17+H17+I17+J17+O17</f>
+        <f aca="false">G17+H17+I17+J17+O17+P17</f>
         <v>490</v>
       </c>
       <c r="L17" s="12" t="n">
@@ -3129,10 +3194,13 @@
         <v>No</v>
       </c>
       <c r="N17" s="31" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O17" s="30" t="n">
         <v>25</v>
+      </c>
+      <c r="P17" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3140,10 +3208,10 @@
         <v>21</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D18" s="29" t="n">
         <v>5</v>
@@ -3170,7 +3238,7 @@
         <v>225</v>
       </c>
       <c r="K18" s="12" t="n">
-        <f aca="false">G18+H18+I18+J18+O18</f>
+        <f aca="false">G18+H18+I18+J18+O18+P18</f>
         <v>780</v>
       </c>
       <c r="L18" s="12" t="n">
@@ -3182,10 +3250,13 @@
         <v>No</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O18" s="30" t="n">
         <v>25</v>
+      </c>
+      <c r="P18" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3193,10 +3264,10 @@
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D19" s="29" t="n">
         <v>4</v>
@@ -3223,7 +3294,7 @@
         <v>80</v>
       </c>
       <c r="K19" s="12" t="n">
-        <f aca="false">G19+H19+I19+J19+O19</f>
+        <f aca="false">G19+H19+I19+J19+O19+P19</f>
         <v>325</v>
       </c>
       <c r="L19" s="12" t="n">
@@ -3235,10 +3306,13 @@
         <v>No</v>
       </c>
       <c r="N19" s="31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O19" s="30" t="n">
         <v>20</v>
+      </c>
+      <c r="P19" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3246,7 +3320,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>23</v>
@@ -3276,7 +3350,7 @@
         <v>760</v>
       </c>
       <c r="K20" s="12" t="n">
-        <f aca="false">G20+H20+I20+J20+O20</f>
+        <f aca="false">G20+H20+I20+J20+O20+P20</f>
         <v>1140</v>
       </c>
       <c r="L20" s="12" t="n">
@@ -3288,10 +3362,13 @@
         <v>N/A – host</v>
       </c>
       <c r="N20" s="31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O20" s="30" t="n">
         <v>100</v>
+      </c>
+      <c r="P20" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3299,10 +3376,10 @@
         <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D21" s="29" t="n">
         <v>8</v>
@@ -3329,7 +3406,7 @@
         <v>384</v>
       </c>
       <c r="K21" s="12" t="n">
-        <f aca="false">G21+H21+I21+J21+O21</f>
+        <f aca="false">G21+H21+I21+J21+O21+P21</f>
         <v>1034</v>
       </c>
       <c r="L21" s="12" t="n">
@@ -3341,10 +3418,13 @@
         <v>No</v>
       </c>
       <c r="N21" s="31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O21" s="30" t="n">
         <v>40</v>
+      </c>
+      <c r="P21" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3352,10 +3432,10 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D22" s="29" t="n">
         <v>2</v>
@@ -3382,7 +3462,7 @@
         <v>40</v>
       </c>
       <c r="K22" s="12" t="n">
-        <f aca="false">G22+H22+I22+J22+O22</f>
+        <f aca="false">G22+H22+I22+J22+O22+P22</f>
         <v>360</v>
       </c>
       <c r="L22" s="12" t="n">
@@ -3394,10 +3474,13 @@
         <v>No</v>
       </c>
       <c r="N22" s="31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O22" s="30" t="n">
         <v>10</v>
+      </c>
+      <c r="P22" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3405,10 +3488,10 @@
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D23" s="29" t="n">
         <v>3</v>
@@ -3435,7 +3518,7 @@
         <v>114</v>
       </c>
       <c r="K23" s="12" t="n">
-        <f aca="false">G23+H23+I23+J23+O23</f>
+        <f aca="false">G23+H23+I23+J23+O23+P23</f>
         <v>354</v>
       </c>
       <c r="L23" s="12" t="n">
@@ -3447,10 +3530,13 @@
         <v>No</v>
       </c>
       <c r="N23" s="31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O23" s="30" t="n">
         <v>15</v>
+      </c>
+      <c r="P23" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3458,10 +3544,10 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D24" s="29" t="n">
         <v>2</v>
@@ -3474,7 +3560,7 @@
         <v>38</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="H24" s="30" t="n">
         <v>30</v>
@@ -3488,7 +3574,7 @@
         <v>76</v>
       </c>
       <c r="K24" s="12" t="n">
-        <f aca="false">G24+H24+I24+J24+O24</f>
+        <f aca="false">G24+H24+I24+J24+O24+P24</f>
         <v>406</v>
       </c>
       <c r="L24" s="12" t="n">
@@ -3500,10 +3586,13 @@
         <v>No</v>
       </c>
       <c r="N24" s="31" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O24" s="30" t="n">
         <v>10</v>
+      </c>
+      <c r="P24" s="30" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3520,7 +3609,7 @@
       <c r="F25" s="15"/>
       <c r="G25" s="16" t="n">
         <f aca="false">SUM(G5:G24)</f>
-        <v>970</v>
+        <v>739</v>
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">SUM(H5:H24)</f>
@@ -3547,6 +3636,10 @@
       <c r="O25" s="16" t="n">
         <f aca="false">SUM(O5:O24)</f>
         <v>455</v>
+      </c>
+      <c r="P25" s="16" t="n">
+        <f aca="false">SUM(P5:P24)</f>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -3566,7 +3659,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -3586,12 +3679,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3599,43 +3692,43 @@
         <v>4</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N4" s="33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3659,10 +3752,10 @@
         <v>46315</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H5" s="39" t="n">
         <v>36</v>
@@ -3672,17 +3765,17 @@
         <v>36</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="37"/>
       <c r="L5" s="37" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N5" s="41" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3707,10 +3800,10 @@
         <v>46317</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H6" s="39" t="n">
         <v>0</v>
@@ -3720,13 +3813,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K6" s="37"/>
       <c r="L6" s="37"/>
       <c r="M6" s="37"/>
       <c r="N6" s="41" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3751,10 +3844,10 @@
         <v>46320</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H7" s="39" t="n">
         <f aca="false">(52.24+239.55)/3</f>
@@ -3765,13 +3858,13 @@
         <v>291.79</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7" s="37"/>
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
       <c r="N7" s="41" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3796,10 +3889,10 @@
         <v>46323</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H8" s="39" t="n">
         <f aca="false">(137.26+66.78)/3</f>
@@ -3810,13 +3903,13 @@
         <v>204.04</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K8" s="37"/>
       <c r="L8" s="37"/>
       <c r="M8" s="37"/>
       <c r="N8" s="41" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3841,10 +3934,10 @@
         <v>46328</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H9" s="39" t="n">
         <f aca="false">338.05/5</f>
@@ -3855,13 +3948,13 @@
         <v>338.05</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K9" s="37"/>
       <c r="L9" s="37"/>
       <c r="M9" s="37"/>
       <c r="N9" s="41" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3886,10 +3979,10 @@
         <v>46331</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H10" s="39" t="n">
         <f aca="false">226.17/3</f>
@@ -3900,13 +3993,13 @@
         <v>226.17</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" s="37"/>
       <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="N10" s="41" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3931,10 +4024,10 @@
         <v>46337</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H11" s="39" t="n">
         <f aca="false">300.97/6</f>
@@ -3945,13 +4038,13 @@
         <v>300.97</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K11" s="37"/>
       <c r="L11" s="37"/>
       <c r="M11" s="37"/>
       <c r="N11" s="41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3977,7 +4070,7 @@
       </c>
       <c r="F12" s="37"/>
       <c r="G12" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H12" s="39" t="n">
         <v>20</v>
@@ -3991,7 +4084,7 @@
       <c r="L12" s="37"/>
       <c r="M12" s="37"/>
       <c r="N12" s="41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4017,7 +4110,7 @@
       </c>
       <c r="F13" s="37"/>
       <c r="G13" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H13" s="39" t="n">
         <v>25</v>
@@ -4031,7 +4124,7 @@
       <c r="L13" s="37"/>
       <c r="M13" s="37"/>
       <c r="N13" s="41" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4057,7 +4150,7 @@
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H14" s="39" t="n">
         <v>45</v>
@@ -4095,7 +4188,7 @@
       </c>
       <c r="F15" s="37"/>
       <c r="G15" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H15" s="39" t="n">
         <v>35</v>
@@ -4133,7 +4226,7 @@
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H16" s="39" t="n">
         <v>35</v>
@@ -4171,7 +4264,7 @@
       </c>
       <c r="F17" s="37"/>
       <c r="G17" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H17" s="39" t="n">
         <v>25</v>
@@ -4185,7 +4278,7 @@
       <c r="L17" s="37"/>
       <c r="M17" s="37"/>
       <c r="N17" s="41" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4211,7 +4304,7 @@
       </c>
       <c r="F18" s="37"/>
       <c r="G18" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H18" s="39" t="n">
         <v>90</v>
@@ -4225,7 +4318,7 @@
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
       <c r="N18" s="41" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4251,7 +4344,7 @@
       </c>
       <c r="F19" s="37"/>
       <c r="G19" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H19" s="39" t="n">
         <v>35</v>
@@ -4288,10 +4381,10 @@
         <v>46390</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H20" s="39" t="n">
         <v>0</v>
@@ -4301,13 +4394,13 @@
         <v>0</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K20" s="37"/>
       <c r="L20" s="37"/>
       <c r="M20" s="37"/>
       <c r="N20" s="41" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4333,7 +4426,7 @@
       </c>
       <c r="F21" s="37"/>
       <c r="G21" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H21" s="39" t="n">
         <v>55</v>
@@ -4347,7 +4440,7 @@
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
       <c r="N21" s="41" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4373,7 +4466,7 @@
       </c>
       <c r="F22" s="37"/>
       <c r="G22" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H22" s="39" t="n">
         <v>130</v>
@@ -4387,7 +4480,7 @@
       <c r="L22" s="37"/>
       <c r="M22" s="37"/>
       <c r="N22" s="41" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4413,7 +4506,7 @@
       </c>
       <c r="F23" s="37"/>
       <c r="G23" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H23" s="39" t="n">
         <v>55</v>
@@ -4451,7 +4544,7 @@
       </c>
       <c r="F24" s="37"/>
       <c r="G24" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H24" s="39" t="n">
         <v>80</v>
@@ -4465,7 +4558,7 @@
       <c r="L24" s="37"/>
       <c r="M24" s="37"/>
       <c r="N24" s="41" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4498,7 +4591,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C27" s="44" t="str">
         <f aca="false">COUNTIF(G5:G24,"Booked")&amp;" of "&amp;(COUNTA(G5:G24)-COUNTIF(G5:G24,"Staying with friends"))</f>
@@ -4507,7 +4600,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C28" s="45" t="n">
         <f aca="false">SUMIF(G5:G24,"Booked",I5:I24)</f>
@@ -4516,7 +4609,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C29" s="45" t="n">
         <f aca="false">SUMIF(G5:G24,"To book",I5:I24)+SUMIF(G5:G24,"Shortlisted",I5:I24)</f>
@@ -4555,7 +4648,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
@@ -4571,53 +4664,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4628,33 +4721,33 @@
         <v>46313</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G5" s="38"/>
       <c r="H5" s="38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I5" s="47" t="n">
         <v>667.6</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L5" s="38"/>
       <c r="M5" s="41" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4665,35 +4758,35 @@
         <v>46314</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I6" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L6" s="38"/>
       <c r="M6" s="41" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4704,35 +4797,35 @@
         <v>46317</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I7" s="47" t="n">
         <v>87.7</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L7" s="38"/>
       <c r="M7" s="41" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4743,35 +4836,35 @@
         <v>46337</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I8" s="47" t="n">
         <v>211.52</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L8" s="38"/>
       <c r="M8" s="41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4782,29 +4875,29 @@
         <v>46344</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
       <c r="H9" s="38" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I9" s="47" t="n">
         <v>130</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L9" s="38"/>
       <c r="M9" s="41" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4815,29 +4908,29 @@
         <v>46352</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I10" s="47" t="n">
         <v>130</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L10" s="38"/>
       <c r="M10" s="41" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4848,29 +4941,29 @@
         <v>46361</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E11" s="38"/>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I11" s="47" t="n">
         <v>80</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L11" s="38"/>
       <c r="M11" s="41" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4881,29 +4974,29 @@
         <v>46366</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E12" s="38"/>
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
       <c r="H12" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I12" s="47" t="n">
         <v>70</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L12" s="38"/>
       <c r="M12" s="41" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4914,29 +5007,29 @@
         <v>46370</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
       <c r="G13" s="38"/>
       <c r="H13" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I13" s="47" t="n">
         <v>180</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L13" s="38"/>
       <c r="M13" s="41" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4947,29 +5040,29 @@
         <v>46390</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
       <c r="G14" s="38"/>
       <c r="H14" s="38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I14" s="47" t="n">
         <v>150</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L14" s="38"/>
       <c r="M14" s="41" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4980,31 +5073,31 @@
         <v>46405</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I15" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L15" s="38"/>
       <c r="M15" s="41"/>
@@ -5017,35 +5110,35 @@
         <v>46405</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I16" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L16" s="38"/>
       <c r="M16" s="41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5070,7 +5163,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I18" s="49" t="n">
         <f aca="false">SUMIF(J5:J16,"Booked",I5:I16)</f>
@@ -5079,7 +5172,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I19" s="49" t="n">
         <f aca="false">I17-I18</f>
@@ -5088,7 +5181,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -5119,7 +5212,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
@@ -5129,82 +5222,82 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B5" s="28" t="n">
         <v>281.62</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>62.4</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B7" s="28" t="n">
         <v>13.64</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5220,225 +5313,225 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="31"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C14" s="29"/>
       <c r="D14" s="31"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C15" s="29"/>
       <c r="D15" s="31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C17" s="29"/>
       <c r="D17" s="31" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="31"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="31" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C20" s="29"/>
       <c r="D20" s="31" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C22" s="29"/>
       <c r="D22" s="31"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C23" s="29"/>
       <c r="D23" s="31"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C24" s="29"/>
       <c r="D24" s="31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C26" s="29"/>
       <c r="D26" s="31"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="31"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="31"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C29" s="29"/>
       <c r="D29" s="31"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="31"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C31" s="29"/>
       <c r="D31" s="31"/>
@@ -5480,7 +5573,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J1000"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
@@ -5496,17 +5589,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>4</v>
@@ -5515,46 +5608,46 @@
         <v>30</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
         <v>2805.05</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="51" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E5" s="52" t="n">
         <v>667.6</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I5" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Booked – pay later")</f>
@@ -5563,25 +5656,25 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E6" s="52" t="n">
         <v>281.62</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
@@ -5590,7 +5683,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="51" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B7" s="51" t="s">
         <v>11</v>
@@ -5599,16 +5692,16 @@
         <v>34</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E7" s="52" t="n">
         <v>36</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
@@ -5617,47 +5710,47 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E8" s="52" t="n">
         <v>19</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="51" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E9" s="52" t="n">
         <v>87.7</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>13</v>
@@ -5666,18 +5759,18 @@
         <v>34</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E10" s="52" t="n">
         <v>239.55</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="51" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>13</v>
@@ -5686,38 +5779,38 @@
         <v>34</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E11" s="52" t="n">
         <v>52.24</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="51" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C12" s="51" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E12" s="52" t="n">
         <v>211.52</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="51" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B13" s="51" t="s">
         <v>13</v>
@@ -5726,18 +5819,18 @@
         <v>34</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E13" s="52" t="n">
         <v>137.26</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>13</v>
@@ -5746,18 +5839,18 @@
         <v>34</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E14" s="52" t="n">
         <v>338.05</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B15" s="51" t="s">
         <v>13</v>
@@ -5766,18 +5859,18 @@
         <v>34</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E15" s="52" t="n">
         <v>66.78</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>13</v>
@@ -5786,18 +5879,18 @@
         <v>34</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E16" s="52" t="n">
         <v>300.97</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>13</v>
@@ -5806,58 +5899,58 @@
         <v>34</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E17" s="52" t="n">
         <v>226.17</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="51" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E18" s="52" t="n">
         <v>13.64</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E19" s="52" t="n">
         <v>32.4</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B20" s="51" t="s">
         <v>11</v>
@@ -5866,21 +5959,21 @@
         <v>36</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E20" s="52" t="n">
         <v>2.95</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B21" s="51" t="s">
         <v>11</v>
@@ -5889,21 +5982,21 @@
         <v>35</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E21" s="52" t="n">
         <v>3.05</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B22" s="51" t="s">
         <v>11</v>
@@ -5918,15 +6011,15 @@
         <v>14.91</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="51" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B23" s="51" t="s">
         <v>11</v>
@@ -5935,21 +6028,21 @@
         <v>35</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E23" s="52" t="n">
         <v>3.4</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="51" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B24" s="51" t="s">
         <v>11</v>
@@ -5958,21 +6051,21 @@
         <v>35</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E24" s="52" t="n">
         <v>2.55</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="51" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B25" s="51" t="s">
         <v>11</v>
@@ -5981,21 +6074,21 @@
         <v>36</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E25" s="52" t="n">
         <v>5.9</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B26" s="51" t="s">
         <v>11</v>
@@ -6004,21 +6097,21 @@
         <v>35</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E26" s="52" t="n">
         <v>8.5</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="51" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>11</v>
@@ -6027,44 +6120,44 @@
         <v>35</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E27" s="52" t="n">
         <v>8.87</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="51" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E28" s="52" t="n">
         <v>3.4</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="51" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B29" s="51" t="s">
         <v>11</v>
@@ -6073,21 +6166,21 @@
         <v>35</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E29" s="52" t="n">
         <v>1.98</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="51" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>11</v>
@@ -6096,44 +6189,44 @@
         <v>35</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E30" s="52" t="n">
         <v>4.26</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="51" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B31" s="51" t="s">
         <v>13</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E31" s="52" t="n">
         <v>23.25</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="51" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B32" s="51" t="s">
         <v>11</v>
@@ -6142,21 +6235,21 @@
         <v>35</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E32" s="52" t="n">
         <v>6.76</v>
       </c>
       <c r="F32" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="51" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B33" s="51" t="s">
         <v>11</v>
@@ -6165,21 +6258,21 @@
         <v>35</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E33" s="52" t="n">
         <v>1.99</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="51" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B34" s="51" t="s">
         <v>11</v>
@@ -6188,16 +6281,16 @@
         <v>35</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E34" s="52" t="n">
         <v>2.78</v>
       </c>
       <c r="F34" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13921,7 +14014,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C1000" type="list">
-      <formula1>"Flights,Accommodation,Food,Local transport,Activities,Shopping &amp; misc,Insurance &amp; admin,Other"</formula1>
+      <formula1>"Flights,Accommodation,Food,Local transport,Trains &amp; intercity,Activities,Shopping &amp; misc,Insurance &amp; admin,Other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F1000" type="list">

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="354">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1081,18 +1081,25 @@
   </si>
   <si>
     <t xml:space="preserve">mvhozxevm8t8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KBBQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvi0daz6hy5w</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\£#,##0;&quot;(£&quot;#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="ddd\ d\ mmm\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="ddd\ d\ mmm\ yyyy"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -1319,7 +1326,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1351,11 +1358,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1363,15 +1366,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1379,7 +1382,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1387,15 +1390,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1423,11 +1430,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1471,19 +1478,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1491,7 +1498,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1584,34 +1591,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1757,7 +1764,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
@@ -1835,11 +1842,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>107.3</v>
+        <v>143.93</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1228.7</v>
+        <v>1192.07</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2129,11 +2136,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>59.05</v>
+        <v>95.68</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3328.45</v>
+        <v>3291.82</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2276,11 +2283,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2805.05</v>
+        <v>2841.68</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7194.95</v>
+        <v>7158.32</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2305,7 +2312,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2805.05</v>
+        <v>2841.68</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2323,7 +2330,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7194.95</v>
+        <v>7158.32</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2352,7 +2359,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2805.05</v>
+        <v>2841.68</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2361,7 +2368,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5229.22</v>
+        <v>5192.59</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2399,7 +2406,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -3659,7 +3666,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
@@ -4648,7 +4655,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
@@ -5212,7 +5219,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
@@ -5573,7 +5580,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J1000"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
@@ -5621,7 +5628,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2805.05</v>
+        <v>2841.68</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5678,7 +5685,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2805.05</v>
+        <v>2841.68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5705,7 +5712,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7194.95</v>
+        <v>7158.32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6294,12 +6301,27 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="51"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="51"/>
+      <c r="A35" s="51" t="s">
+        <v>341</v>
+      </c>
+      <c r="B35" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>352</v>
+      </c>
+      <c r="E35" s="52" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="356">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1087,6 +1087,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvi0daz6hy5w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olive Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvi46m3ysf73</t>
   </si>
 </sst>
 </file>
@@ -1842,11 +1848,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>143.93</v>
+        <v>157.5</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1192.07</v>
+        <v>1178.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2220,11 +2226,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>3.4</v>
+        <v>16.97</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>451.6</v>
+        <v>438.03</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2283,11 +2289,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2841.68</v>
+        <v>2855.25</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7158.32</v>
+        <v>7144.75</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2312,7 +2318,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2841.68</v>
+        <v>2855.25</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2330,7 +2336,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7158.32</v>
+        <v>7144.75</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2359,7 +2365,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2841.68</v>
+        <v>2855.25</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2368,7 +2374,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5192.59</v>
+        <v>5179.02</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5628,7 +5634,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2841.68</v>
+        <v>2855.25</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5685,7 +5691,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2841.68</v>
+        <v>2855.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5712,7 +5718,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7158.32</v>
+        <v>7144.75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6324,12 +6330,27 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="51"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="51"/>
+      <c r="A36" s="51" t="s">
+        <v>341</v>
+      </c>
+      <c r="B36" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>354</v>
+      </c>
+      <c r="E36" s="52" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -1848,11 +1848,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>157.5</v>
+        <v>161.28</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1178.5</v>
+        <v>1174.72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2226,11 +2226,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>16.97</v>
+        <v>20.75</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>438.03</v>
+        <v>434.25</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2289,11 +2289,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2855.25</v>
+        <v>2859.03</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7144.75</v>
+        <v>7140.97</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2855.25</v>
+        <v>2859.03</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7144.75</v>
+        <v>7140.97</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2855.25</v>
+        <v>2859.03</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5179.02</v>
+        <v>5175.24</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2855.25</v>
+        <v>2859.03</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2855.25</v>
+        <v>2859.03</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7144.75</v>
+        <v>7140.97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6343,7 +6343,7 @@
         <v>354</v>
       </c>
       <c r="E36" s="52" t="n">
-        <v>13.57</v>
+        <v>17.35</v>
       </c>
       <c r="F36" s="51" t="s">
         <v>43</v>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="358">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1093,6 +1093,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvi46m3ysf73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running Flask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvi48fnuf6v2</t>
   </si>
 </sst>
 </file>
@@ -1848,11 +1854,11 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Korea",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>161.28</v>
+        <v>174.85</v>
       </c>
       <c r="G7" s="12" t="n">
         <f aca="false">D7+D13-F7</f>
-        <v>1174.72</v>
+        <v>1161.15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2205,11 +2211,11 @@
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A25)</f>
-        <v>0</v>
+        <v>13.57</v>
       </c>
       <c r="D25" s="18" t="n">
         <f aca="false">B25-C25</f>
-        <v>1030</v>
+        <v>1016.43</v>
       </c>
       <c r="E25" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B25/$B$3)</f>
@@ -2289,11 +2295,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2859.03</v>
+        <v>2872.6</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7140.97</v>
+        <v>7127.4</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2318,7 +2324,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2859.03</v>
+        <v>2872.6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2336,7 +2342,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7140.97</v>
+        <v>7127.4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2365,7 +2371,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2859.03</v>
+        <v>2872.6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2374,7 +2380,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5175.24</v>
+        <v>5161.67</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5634,7 +5640,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2859.03</v>
+        <v>2872.6</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5691,7 +5697,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2859.03</v>
+        <v>2872.6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5718,7 +5724,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7140.97</v>
+        <v>7127.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6353,12 +6359,27 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="51"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="51"/>
+      <c r="A37" s="51" t="s">
+        <v>341</v>
+      </c>
+      <c r="B37" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>356</v>
+      </c>
+      <c r="E37" s="52" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="359">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1099,6 +1099,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvi48fnuf6v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mviqqaspbcyd</t>
   </si>
 </sst>
 </file>
@@ -1882,11 +1885,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1384.27</v>
+        <v>1387.23</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3635.75</v>
+        <v>3632.79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2169,11 +2172,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>8.85</v>
+        <v>11.81</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>730.15</v>
+        <v>727.19</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
@@ -2295,11 +2298,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2872.6</v>
+        <v>2875.56</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7127.4</v>
+        <v>7124.44</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2324,7 +2327,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2872.6</v>
+        <v>2875.56</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2342,7 +2345,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7127.4</v>
+        <v>7124.44</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2371,7 +2374,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2872.6</v>
+        <v>2875.56</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2380,7 +2383,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5161.67</v>
+        <v>5158.71</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5640,7 +5643,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2872.6</v>
+        <v>2875.56</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5697,7 +5700,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2872.6</v>
+        <v>2875.56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5724,7 +5727,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7127.4</v>
+        <v>7124.44</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6382,12 +6385,27 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="51"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="51"/>
+      <c r="A38" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="B38" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="E38" s="52" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="361">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1102,6 +1102,12 @@
   </si>
   <si>
     <t xml:space="preserve">mviqqaspbcyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airport Lounge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mviuu7x13v7m</t>
   </si>
 </sst>
 </file>
@@ -1885,11 +1891,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1387.23</v>
+        <v>1407.78</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3632.79</v>
+        <v>3612.24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2235,11 +2241,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>20.75</v>
+        <v>41.3</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>434.25</v>
+        <v>413.7</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2298,11 +2304,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2875.56</v>
+        <v>2896.11</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7124.44</v>
+        <v>7103.89</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2327,7 +2333,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2875.56</v>
+        <v>2896.11</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2345,7 +2351,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7124.44</v>
+        <v>7103.89</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2374,7 +2380,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2875.56</v>
+        <v>2896.11</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2383,7 +2389,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5158.71</v>
+        <v>5138.16</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5643,7 +5649,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2875.56</v>
+        <v>2896.11</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5700,7 +5706,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2875.56</v>
+        <v>2896.11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5727,7 +5733,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7124.44</v>
+        <v>7103.89</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6408,12 +6414,27 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="51"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="51"/>
+      <c r="A39" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="E39" s="52" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="363">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1108,6 +1108,12 @@
   </si>
   <si>
     <t xml:space="preserve">mviuu7x13v7m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suica card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvj80u63qq2m</t>
   </si>
 </sst>
 </file>
@@ -1891,11 +1897,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1407.78</v>
+        <v>1412.52</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3612.24</v>
+        <v>3607.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2178,11 +2184,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>11.81</v>
+        <v>16.55</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>727.19</v>
+        <v>722.45</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
@@ -2304,11 +2310,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2896.11</v>
+        <v>2900.85</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7103.89</v>
+        <v>7099.15</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2333,7 +2339,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2896.11</v>
+        <v>2900.85</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2351,7 +2357,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7103.89</v>
+        <v>7099.15</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2380,7 +2386,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2896.11</v>
+        <v>2900.85</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2389,7 +2395,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5138.16</v>
+        <v>5133.42</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5649,7 +5655,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2896.11</v>
+        <v>2900.85</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5706,7 +5712,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2896.11</v>
+        <v>2900.85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5733,7 +5739,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7103.89</v>
+        <v>7099.15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6437,12 +6443,27 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="51"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="51"/>
+      <c r="A40" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>361</v>
+      </c>
+      <c r="E40" s="52" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="365">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1114,6 +1114,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvj80u63qq2m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvjfm4dvwhv5</t>
   </si>
 </sst>
 </file>
@@ -1897,11 +1903,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1412.52</v>
+        <v>1421.06</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3607.5</v>
+        <v>3598.96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2163,11 +2169,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>95.68</v>
+        <v>104.22</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3291.82</v>
+        <v>3283.28</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2310,11 +2316,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2900.85</v>
+        <v>2909.39</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7099.15</v>
+        <v>7090.61</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2339,7 +2345,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2900.85</v>
+        <v>2909.39</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2357,7 +2363,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7099.15</v>
+        <v>7090.61</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2386,7 +2392,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2900.85</v>
+        <v>2909.39</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2395,7 +2401,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5133.42</v>
+        <v>5124.88</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5655,7 +5661,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2900.85</v>
+        <v>2909.39</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5712,7 +5718,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2900.85</v>
+        <v>2909.39</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5739,7 +5745,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7099.15</v>
+        <v>7090.61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6466,12 +6472,27 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="51"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="51"/>
+      <c r="A41" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>363</v>
+      </c>
+      <c r="E41" s="52" t="n">
+        <v>8.54</v>
+      </c>
+      <c r="F41" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="367">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1120,6 +1120,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvjfm4dvwhv5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fruit sando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvjgkqsnzjqx</t>
   </si>
 </sst>
 </file>
@@ -1903,11 +1909,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1421.06</v>
+        <v>1425.33</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3598.96</v>
+        <v>3594.69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2169,11 +2175,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>104.22</v>
+        <v>108.49</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3283.28</v>
+        <v>3279.01</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2316,11 +2322,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2909.39</v>
+        <v>2913.66</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7090.61</v>
+        <v>7086.34</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2345,7 +2351,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2909.39</v>
+        <v>2913.66</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2363,7 +2369,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7090.61</v>
+        <v>7086.34</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2392,7 +2398,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2909.39</v>
+        <v>2913.66</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2401,7 +2407,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5124.88</v>
+        <v>5120.61</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5661,7 +5667,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2909.39</v>
+        <v>2913.66</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5718,7 +5724,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2909.39</v>
+        <v>2913.66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5745,7 +5751,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7090.61</v>
+        <v>7086.34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6495,12 +6501,27 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="51"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="51"/>
+      <c r="A42" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="B42" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="E42" s="52" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="369">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1126,6 +1126,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvjgkqsnzjqx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family Mart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvjgs4ix5h8f</t>
   </si>
 </sst>
 </file>
@@ -1909,11 +1915,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1425.33</v>
+        <v>1428.65</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3594.69</v>
+        <v>3591.37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2259,11 +2265,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>41.3</v>
+        <v>44.62</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>413.7</v>
+        <v>410.38</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2322,11 +2328,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2913.66</v>
+        <v>2916.98</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7086.34</v>
+        <v>7083.02</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2351,7 +2357,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2913.66</v>
+        <v>2916.98</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2369,7 +2375,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7086.34</v>
+        <v>7083.02</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2398,7 +2404,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2913.66</v>
+        <v>2916.98</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2407,7 +2413,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5120.61</v>
+        <v>5117.29</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5667,7 +5673,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2913.66</v>
+        <v>2916.98</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5724,7 +5730,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2913.66</v>
+        <v>2916.98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5751,7 +5757,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7086.34</v>
+        <v>7083.02</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6524,12 +6530,27 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="51"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="51"/>
+      <c r="A43" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="B43" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="E43" s="52" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="372">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1132,6 +1132,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvjgs4ix5h8f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minato Coffee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvk5bhfpd7p3</t>
   </si>
 </sst>
 </file>
@@ -1915,11 +1924,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1428.65</v>
+        <v>1431.52</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3591.37</v>
+        <v>3588.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2181,11 +2190,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>108.49</v>
+        <v>111.36</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3279.01</v>
+        <v>3276.14</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2328,11 +2337,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2916.98</v>
+        <v>2919.85</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7083.02</v>
+        <v>7080.15</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2357,7 +2366,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2916.98</v>
+        <v>2919.85</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2375,7 +2384,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7083.02</v>
+        <v>7080.15</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2404,7 +2413,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2916.98</v>
+        <v>2919.85</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2413,7 +2422,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5117.29</v>
+        <v>5114.42</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5673,7 +5682,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2916.98</v>
+        <v>2919.85</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5730,7 +5739,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2916.98</v>
+        <v>2919.85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5757,7 +5766,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7083.02</v>
+        <v>7080.15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6553,12 +6562,27 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="51"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="51"/>
+      <c r="A44" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B44" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="51" t="s">
+        <v>370</v>
+      </c>
+      <c r="E44" s="52" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="F44" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="374">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1141,6 +1141,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvk5bhfpd7p3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkac1o05k6k</t>
   </si>
 </sst>
 </file>
@@ -1924,11 +1930,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1431.52</v>
+        <v>1434.65</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3588.5</v>
+        <v>3585.37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2190,11 +2196,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>111.36</v>
+        <v>114.49</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3276.14</v>
+        <v>3273.01</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2337,11 +2343,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2919.85</v>
+        <v>2922.98</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7080.15</v>
+        <v>7077.02</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2366,7 +2372,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2919.85</v>
+        <v>2922.98</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2384,7 +2390,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7080.15</v>
+        <v>7077.02</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2413,7 +2419,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2919.85</v>
+        <v>2922.98</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2422,7 +2428,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5114.42</v>
+        <v>5111.29</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5682,7 +5688,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2919.85</v>
+        <v>2922.98</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5739,7 +5745,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2919.85</v>
+        <v>2922.98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5766,7 +5772,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7080.15</v>
+        <v>7077.02</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6585,12 +6591,27 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="51"/>
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="51"/>
+      <c r="A45" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B45" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="E45" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="F45" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="376">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1147,6 +1147,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkac1o05k6k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FamilyMart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkad59n1l9o</t>
   </si>
 </sst>
 </file>
@@ -1930,11 +1936,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1434.65</v>
+        <v>1437.54</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3585.37</v>
+        <v>3582.48</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2196,11 +2202,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>114.49</v>
+        <v>117.38</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3273.01</v>
+        <v>3270.12</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2343,11 +2349,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2922.98</v>
+        <v>2925.87</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7077.02</v>
+        <v>7074.13</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2372,7 +2378,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2922.98</v>
+        <v>2925.87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2390,7 +2396,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7077.02</v>
+        <v>7074.13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2419,7 +2425,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2922.98</v>
+        <v>2925.87</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2428,7 +2434,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5111.29</v>
+        <v>5108.4</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5688,7 +5694,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2922.98</v>
+        <v>2925.87</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5745,7 +5751,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2922.98</v>
+        <v>2925.87</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5772,7 +5778,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7077.02</v>
+        <v>7074.13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6614,12 +6620,27 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="51"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="51"/>
+      <c r="A46" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B46" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="E46" s="52" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F46" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="378">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1153,6 +1153,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkad59n1l9o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBottle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkegcwdgs40</t>
   </si>
 </sst>
 </file>
@@ -1936,11 +1942,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1437.54</v>
+        <v>1440.84</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3582.48</v>
+        <v>3579.18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2202,11 +2208,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>117.38</v>
+        <v>120.68</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3270.12</v>
+        <v>3266.82</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2349,11 +2355,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2925.87</v>
+        <v>2929.17</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7074.13</v>
+        <v>7070.83</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2378,7 +2384,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2925.87</v>
+        <v>2929.17</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2396,7 +2402,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7074.13</v>
+        <v>7070.83</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2425,7 +2431,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2925.87</v>
+        <v>2929.17</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2434,7 +2440,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5108.4</v>
+        <v>5105.1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5694,7 +5700,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2925.87</v>
+        <v>2929.17</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5751,7 +5757,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2925.87</v>
+        <v>2929.17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5778,7 +5784,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7074.13</v>
+        <v>7070.83</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6643,12 +6649,27 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="51"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="51"/>
+      <c r="A47" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B47" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="51" t="s">
+        <v>376</v>
+      </c>
+      <c r="E47" s="52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F47" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="380">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1159,6 +1159,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkegcwdgs40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold Medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkeguj2z73p</t>
   </si>
 </sst>
 </file>
@@ -1942,11 +1948,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1440.84</v>
+        <v>1451.25</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3579.18</v>
+        <v>3568.77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2292,11 +2298,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>44.62</v>
+        <v>55.03</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>410.38</v>
+        <v>399.97</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2355,11 +2361,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2929.17</v>
+        <v>2939.58</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7070.83</v>
+        <v>7060.42</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2384,7 +2390,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2929.17</v>
+        <v>2939.58</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2402,7 +2408,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7070.83</v>
+        <v>7060.42</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2431,7 +2437,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2929.17</v>
+        <v>2939.58</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2440,7 +2446,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5105.1</v>
+        <v>5094.69</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5700,7 +5706,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2929.17</v>
+        <v>2939.58</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5757,7 +5763,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2929.17</v>
+        <v>2939.58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5784,7 +5790,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7070.83</v>
+        <v>7060.42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6672,12 +6678,27 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="51"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="51"/>
+      <c r="A48" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B48" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="E48" s="52" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="F48" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="382">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1165,6 +1165,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkeguj2z73p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Withdrawral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkj13sckg46</t>
   </si>
 </sst>
 </file>
@@ -1948,11 +1954,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1451.25</v>
+        <v>1499.05</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3568.77</v>
+        <v>3520.97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2298,11 +2304,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>55.03</v>
+        <v>102.83</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>399.97</v>
+        <v>352.17</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2361,11 +2367,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2939.58</v>
+        <v>2987.38</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7060.42</v>
+        <v>7012.62</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2390,7 +2396,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2939.58</v>
+        <v>2987.38</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2408,7 +2414,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7060.42</v>
+        <v>7012.62</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2437,7 +2443,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2939.58</v>
+        <v>2987.38</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2446,7 +2452,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5094.69</v>
+        <v>5046.89</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5706,7 +5712,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2939.58</v>
+        <v>2987.38</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5763,7 +5769,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2939.58</v>
+        <v>2987.38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5790,7 +5796,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7060.42</v>
+        <v>7012.62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6701,12 +6707,27 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="51"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="51"/>
+      <c r="A49" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B49" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="51" t="s">
+        <v>380</v>
+      </c>
+      <c r="E49" s="52" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F49" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -2220,11 +2220,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>120.68</v>
+        <v>168.48</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3266.82</v>
+        <v>3219.02</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2304,11 +2304,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>102.83</v>
+        <v>55.03</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>352.17</v>
+        <v>399.97</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -6714,7 +6714,7 @@
         <v>13</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D49" s="51" t="s">
         <v>380</v>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="384">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1171,6 +1171,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkj13sckg46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkj2i74n90g</t>
   </si>
 </sst>
 </file>
@@ -1954,11 +1960,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1499.05</v>
+        <v>1509.05</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3520.97</v>
+        <v>3510.97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2220,11 +2226,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>168.48</v>
+        <v>178.48</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3219.02</v>
+        <v>3209.02</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2367,11 +2373,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2987.38</v>
+        <v>2997.38</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7012.62</v>
+        <v>7002.62</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2396,7 +2402,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2987.38</v>
+        <v>2997.38</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2414,7 +2420,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7012.62</v>
+        <v>7002.62</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2443,7 +2449,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2987.38</v>
+        <v>2997.38</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2452,7 +2458,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5046.89</v>
+        <v>5036.89</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5712,7 +5718,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2987.38</v>
+        <v>2997.38</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5769,7 +5775,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2987.38</v>
+        <v>2997.38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5796,7 +5802,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7012.62</v>
+        <v>7002.62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6730,12 +6736,27 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="51"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="51"/>
+      <c r="A50" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B50" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="E50" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="382">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1171,12 +1171,6 @@
   </si>
   <si>
     <t xml:space="preserve">mvkj13sckg46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mvkj2i74n90g</t>
   </si>
 </sst>
 </file>
@@ -1960,11 +1954,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1509.05</v>
+        <v>1499.05</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3510.97</v>
+        <v>3520.97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2226,11 +2220,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>178.48</v>
+        <v>168.48</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3209.02</v>
+        <v>3219.02</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2373,11 +2367,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2997.38</v>
+        <v>2987.38</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7002.62</v>
+        <v>7012.62</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2402,7 +2396,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2997.38</v>
+        <v>2987.38</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2420,7 +2414,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7002.62</v>
+        <v>7012.62</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2449,7 +2443,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2997.38</v>
+        <v>2987.38</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2458,7 +2452,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5036.89</v>
+        <v>5046.89</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5718,7 +5712,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2997.38</v>
+        <v>2987.38</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5775,7 +5769,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2997.38</v>
+        <v>2987.38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5802,7 +5796,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7002.62</v>
+        <v>7012.62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6736,27 +6730,12 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="51" t="s">
-        <v>369</v>
-      </c>
-      <c r="B50" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="D50" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="E50" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="F50" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>383</v>
-      </c>
+      <c r="A50" s="51"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="51"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="384">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1171,6 +1171,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkj13sckg46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkn35eorct4</t>
   </si>
 </sst>
 </file>
@@ -1954,11 +1960,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1499.05</v>
+        <v>1499.77</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3520.97</v>
+        <v>3520.25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2220,11 +2226,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>168.48</v>
+        <v>169.2</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3219.02</v>
+        <v>3218.3</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2367,11 +2373,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2987.38</v>
+        <v>2988.1</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7012.62</v>
+        <v>7011.9</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2396,7 +2402,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2987.38</v>
+        <v>2988.1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2414,7 +2420,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7012.62</v>
+        <v>7011.9</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2443,7 +2449,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2987.38</v>
+        <v>2988.1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2452,7 +2458,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5046.89</v>
+        <v>5046.17</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5712,7 +5718,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2987.38</v>
+        <v>2988.1</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5769,7 +5775,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2987.38</v>
+        <v>2988.1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5796,7 +5802,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7012.62</v>
+        <v>7011.9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6730,12 +6736,27 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="51"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="51"/>
+      <c r="A50" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B50" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="E50" s="52" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F50" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="386">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1177,6 +1177,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkn35eorct4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sparking Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkn4vup9dx4</t>
   </si>
 </sst>
 </file>
@@ -1960,11 +1966,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1499.77</v>
+        <v>1501.08</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3520.25</v>
+        <v>3518.94</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2226,11 +2232,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>169.2</v>
+        <v>170.51</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3218.3</v>
+        <v>3216.99</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2373,11 +2379,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2988.1</v>
+        <v>2989.41</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7011.9</v>
+        <v>7010.59</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2402,7 +2408,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2988.1</v>
+        <v>2989.41</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2420,7 +2426,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7011.9</v>
+        <v>7010.59</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2449,7 +2455,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2988.1</v>
+        <v>2989.41</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2458,7 +2464,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5046.17</v>
+        <v>5044.86</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5718,7 +5724,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2988.1</v>
+        <v>2989.41</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5775,7 +5781,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2988.1</v>
+        <v>2989.41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5802,7 +5808,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7011.9</v>
+        <v>7010.59</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6759,12 +6765,27 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="51"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="51"/>
+      <c r="A51" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B51" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="51" t="s">
+        <v>384</v>
+      </c>
+      <c r="E51" s="52" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F51" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="388">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1183,6 +1183,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkn4vup9dx4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel Room Upgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvkn5xy6zbhd</t>
   </si>
 </sst>
 </file>
@@ -1966,11 +1972,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1501.08</v>
+        <v>1515.42</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3518.94</v>
+        <v>3504.6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2211,11 +2217,11 @@
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A21)</f>
-        <v>1397.02</v>
+        <v>1411.36</v>
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">B21-C21</f>
-        <v>2370</v>
+        <v>2355.66</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B21/$B$3)</f>
@@ -2379,11 +2385,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>2989.41</v>
+        <v>3003.75</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>7010.59</v>
+        <v>6996.25</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2408,7 +2414,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2989.41</v>
+        <v>3003.75</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2426,7 +2432,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>7010.59</v>
+        <v>6996.25</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2455,7 +2461,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>2989.41</v>
+        <v>3003.75</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2464,7 +2470,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5044.86</v>
+        <v>5030.52</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5724,7 +5730,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>2989.41</v>
+        <v>3003.75</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5781,7 +5787,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>2989.41</v>
+        <v>3003.75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5808,7 +5814,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>7010.59</v>
+        <v>6996.25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6788,12 +6794,27 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="51"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="51"/>
+      <c r="A52" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B52" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="51" t="s">
+        <v>386</v>
+      </c>
+      <c r="E52" s="52" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="F52" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="390">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1189,6 +1189,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvkn5xy6zbhd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FruitSando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvl0v5eoak5a</t>
   </si>
 </sst>
 </file>
@@ -1972,11 +1978,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1515.42</v>
+        <v>1520.2</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3504.6</v>
+        <v>3499.82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2238,11 +2244,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>170.51</v>
+        <v>175.29</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3216.99</v>
+        <v>3212.21</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2385,11 +2391,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3003.75</v>
+        <v>3008.53</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6996.25</v>
+        <v>6991.47</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2414,7 +2420,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3003.75</v>
+        <v>3008.53</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2432,7 +2438,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6996.25</v>
+        <v>6991.47</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2461,7 +2467,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3003.75</v>
+        <v>3008.53</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2470,7 +2476,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5030.52</v>
+        <v>5025.74</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5730,7 +5736,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3003.75</v>
+        <v>3008.53</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5787,7 +5793,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3003.75</v>
+        <v>3008.53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5814,7 +5820,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6996.25</v>
+        <v>6991.47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6817,12 +6823,27 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="51"/>
-      <c r="B53" s="51"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="51"/>
+      <c r="A53" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="B53" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="51" t="s">
+        <v>388</v>
+      </c>
+      <c r="E53" s="52" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F53" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="393">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1195,6 +1195,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvl0v5eoak5a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7Eleven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvlvo9wf8yrp</t>
   </si>
 </sst>
 </file>
@@ -1978,11 +1987,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1520.2</v>
+        <v>1523.86</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3499.82</v>
+        <v>3496.16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2244,11 +2253,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>175.29</v>
+        <v>178.95</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3212.21</v>
+        <v>3208.55</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2391,11 +2400,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3008.53</v>
+        <v>3012.19</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6991.47</v>
+        <v>6987.81</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2420,7 +2429,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3008.53</v>
+        <v>3012.19</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2438,7 +2447,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6991.47</v>
+        <v>6987.81</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2467,7 +2476,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3008.53</v>
+        <v>3012.19</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2476,7 +2485,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5025.74</v>
+        <v>5022.08</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5736,7 +5745,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3008.53</v>
+        <v>3012.19</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5793,7 +5802,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3008.53</v>
+        <v>3012.19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5820,7 +5829,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6991.47</v>
+        <v>6987.81</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6846,12 +6855,27 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="51"/>
-      <c r="B54" s="51"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="51"/>
+      <c r="A54" s="51" t="s">
+        <v>390</v>
+      </c>
+      <c r="B54" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D54" s="51" t="s">
+        <v>391</v>
+      </c>
+      <c r="E54" s="52" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="F54" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="394">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1204,6 +1204,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvlvo9wf8yrp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvlvp23ue9yu</t>
   </si>
 </sst>
 </file>
@@ -1987,11 +1990,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1523.86</v>
+        <v>1554.72</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3496.16</v>
+        <v>3465.3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2253,11 +2256,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>178.95</v>
+        <v>209.81</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3208.55</v>
+        <v>3177.69</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2400,11 +2403,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3012.19</v>
+        <v>3043.05</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6987.81</v>
+        <v>6956.95</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2429,7 +2432,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3012.19</v>
+        <v>3043.05</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2447,7 +2450,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6987.81</v>
+        <v>6956.95</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2476,7 +2479,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3012.19</v>
+        <v>3043.05</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2485,7 +2488,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>5022.08</v>
+        <v>4991.22</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5745,7 +5748,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3012.19</v>
+        <v>3043.05</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5802,7 +5805,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3012.19</v>
+        <v>3043.05</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5829,7 +5832,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6987.81</v>
+        <v>6956.95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6878,12 +6881,27 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="51"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="51"/>
+      <c r="A55" s="51" t="s">
+        <v>390</v>
+      </c>
+      <c r="B55" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="51" t="s">
+        <v>347</v>
+      </c>
+      <c r="E55" s="52" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="F55" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="396">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1207,6 +1207,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvlvp23ue9yu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UniCoffee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvm8dbcgf81u</t>
   </si>
 </sst>
 </file>
@@ -1990,11 +1996,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1554.72</v>
+        <v>1557.65</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3465.3</v>
+        <v>3462.37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2256,11 +2262,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>209.81</v>
+        <v>212.74</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3177.69</v>
+        <v>3174.76</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2403,11 +2409,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3043.05</v>
+        <v>3045.98</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6956.95</v>
+        <v>6954.02</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2432,7 +2438,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3043.05</v>
+        <v>3045.98</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2450,7 +2456,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6956.95</v>
+        <v>6954.02</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2479,7 +2485,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3043.05</v>
+        <v>3045.98</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2488,7 +2494,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4991.22</v>
+        <v>4988.29</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5748,7 +5754,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3043.05</v>
+        <v>3045.98</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5805,7 +5811,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3043.05</v>
+        <v>3045.98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5832,7 +5838,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6956.95</v>
+        <v>6954.02</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6904,12 +6910,27 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="51"/>
-      <c r="B56" s="51"/>
-      <c r="C56" s="51"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="51"/>
+      <c r="A56" s="51" t="s">
+        <v>390</v>
+      </c>
+      <c r="B56" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="51" t="s">
+        <v>394</v>
+      </c>
+      <c r="E56" s="52" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F56" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="398">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1213,6 +1213,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvm8dbcgf81u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvobotwjc34i</t>
   </si>
 </sst>
 </file>
@@ -1996,11 +2002,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1557.65</v>
+        <v>1565.67</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3462.37</v>
+        <v>3454.35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2262,11 +2268,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>212.74</v>
+        <v>220.76</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3174.76</v>
+        <v>3166.74</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2409,11 +2415,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3045.98</v>
+        <v>3054</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6954.02</v>
+        <v>6946</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2438,7 +2444,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3045.98</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2456,7 +2462,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6954.02</v>
+        <v>6946</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2485,7 +2491,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3045.98</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2494,7 +2500,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4988.29</v>
+        <v>4980.27</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5754,7 +5760,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3045.98</v>
+        <v>3054</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5811,7 +5817,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3045.98</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5838,7 +5844,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6954.02</v>
+        <v>6946</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6933,12 +6939,27 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="51"/>
-      <c r="B57" s="51"/>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="52"/>
-      <c r="F57" s="51"/>
+      <c r="A57" s="51" t="s">
+        <v>396</v>
+      </c>
+      <c r="B57" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="E57" s="52" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="F57" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="399">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1219,6 +1219,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvobotwjc34i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvobrx1nu2md</t>
   </si>
 </sst>
 </file>
@@ -2002,11 +2005,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1565.67</v>
+        <v>1569.47</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3454.35</v>
+        <v>3450.55</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2268,11 +2271,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>220.76</v>
+        <v>224.56</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3166.74</v>
+        <v>3162.94</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2415,11 +2418,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3054</v>
+        <v>3057.8</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6946</v>
+        <v>6942.2</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2444,7 +2447,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3054</v>
+        <v>3057.8</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2462,7 +2465,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6946</v>
+        <v>6942.2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2491,7 +2494,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3054</v>
+        <v>3057.8</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2500,7 +2503,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4980.27</v>
+        <v>4976.47</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5760,7 +5763,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3054</v>
+        <v>3057.8</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5817,7 +5820,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3054</v>
+        <v>3057.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5844,7 +5847,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6946</v>
+        <v>6942.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6962,12 +6965,27 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="51"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="51"/>
+      <c r="A58" s="51" t="s">
+        <v>396</v>
+      </c>
+      <c r="B58" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="E58" s="52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F58" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="401">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1222,6 +1222,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvobrx1nu2md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvodjqpmi26p</t>
   </si>
 </sst>
 </file>
@@ -2005,11 +2011,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1569.47</v>
+        <v>1573.28</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3450.55</v>
+        <v>3446.74</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2271,11 +2277,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>224.56</v>
+        <v>228.37</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3162.94</v>
+        <v>3159.13</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2418,11 +2424,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3057.8</v>
+        <v>3061.61</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6942.2</v>
+        <v>6938.39</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2447,7 +2453,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3057.8</v>
+        <v>3061.61</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2465,7 +2471,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6942.2</v>
+        <v>6938.39</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2494,7 +2500,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3057.8</v>
+        <v>3061.61</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2503,7 +2509,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4976.47</v>
+        <v>4972.66</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5763,7 +5769,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3057.8</v>
+        <v>3061.61</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5820,7 +5826,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3057.8</v>
+        <v>3061.61</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5847,7 +5853,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6942.2</v>
+        <v>6938.39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6988,12 +6994,27 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="51"/>
-      <c r="B59" s="51"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="51"/>
+      <c r="A59" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B59" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="E59" s="52" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="F59" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="402">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1228,6 +1228,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvodjqpmi26p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvodkt929bhg</t>
   </si>
 </sst>
 </file>
@@ -2011,11 +2014,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1573.28</v>
+        <v>1574.85</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3446.74</v>
+        <v>3445.17</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2277,11 +2280,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>228.37</v>
+        <v>229.94</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3159.13</v>
+        <v>3157.56</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2424,11 +2427,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3061.61</v>
+        <v>3063.18</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6938.39</v>
+        <v>6936.82</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2453,7 +2456,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3061.61</v>
+        <v>3063.18</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2471,7 +2474,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6938.39</v>
+        <v>6936.82</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2500,7 +2503,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3061.61</v>
+        <v>3063.18</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2509,7 +2512,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4972.66</v>
+        <v>4971.09</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5769,7 +5772,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3061.61</v>
+        <v>3063.18</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5826,7 +5829,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3061.61</v>
+        <v>3063.18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5853,7 +5856,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6938.39</v>
+        <v>6936.82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7017,12 +7020,27 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="51"/>
-      <c r="B60" s="51"/>
-      <c r="C60" s="51"/>
-      <c r="D60" s="51"/>
-      <c r="E60" s="52"/>
-      <c r="F60" s="51"/>
+      <c r="A60" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B60" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="E60" s="52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F60" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="403">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1231,6 +1231,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvodkt929bhg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvofp4vww61s</t>
   </si>
 </sst>
 </file>
@@ -2014,11 +2017,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1574.85</v>
+        <v>1577.22</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3445.17</v>
+        <v>3442.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2280,11 +2283,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>229.94</v>
+        <v>232.31</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3157.56</v>
+        <v>3155.19</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2427,11 +2430,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3063.18</v>
+        <v>3065.55</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6936.82</v>
+        <v>6934.45</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2456,7 +2459,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3063.18</v>
+        <v>3065.55</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2474,7 +2477,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6936.82</v>
+        <v>6934.45</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2503,7 +2506,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3063.18</v>
+        <v>3065.55</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2512,7 +2515,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4971.09</v>
+        <v>4968.72</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5772,7 +5775,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3063.18</v>
+        <v>3065.55</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5829,7 +5832,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3063.18</v>
+        <v>3065.55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5856,7 +5859,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6936.82</v>
+        <v>6934.45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7043,12 +7046,27 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="51"/>
-      <c r="B61" s="51"/>
-      <c r="C61" s="51"/>
-      <c r="D61" s="51"/>
-      <c r="E61" s="52"/>
-      <c r="F61" s="51"/>
+      <c r="A61" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B61" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="E61" s="52" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F61" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="405">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1234,6 +1234,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvofp4vww61s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvomuuhyk5fd</t>
   </si>
 </sst>
 </file>
@@ -2017,11 +2023,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1577.22</v>
+        <v>1582.02</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3442.8</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2304,11 +2310,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>16.55</v>
+        <v>21.35</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>722.45</v>
+        <v>717.65</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
@@ -2430,11 +2436,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3065.55</v>
+        <v>3070.35</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6934.45</v>
+        <v>6929.65</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2459,7 +2465,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3065.55</v>
+        <v>3070.35</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2477,7 +2483,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6934.45</v>
+        <v>6929.65</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2506,7 +2512,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3065.55</v>
+        <v>3070.35</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2515,7 +2521,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4968.72</v>
+        <v>4963.92</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5775,7 +5781,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3065.55</v>
+        <v>3070.35</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5832,7 +5838,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3065.55</v>
+        <v>3070.35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5859,7 +5865,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6934.45</v>
+        <v>6929.65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7069,12 +7075,27 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="51"/>
-      <c r="B62" s="51"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="51"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="51"/>
+      <c r="A62" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B62" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" s="51" t="s">
+        <v>403</v>
+      </c>
+      <c r="E62" s="52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F62" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="407">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1240,6 +1240,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvomuuhyk5fd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PepperLunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvorfo8ev68o</t>
   </si>
 </sst>
 </file>
@@ -2023,11 +2029,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1582.02</v>
+        <v>1589.84</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3438</v>
+        <v>3430.18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2289,11 +2295,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>232.31</v>
+        <v>240.13</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3155.19</v>
+        <v>3147.37</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2436,11 +2442,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3070.35</v>
+        <v>3078.17</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6929.65</v>
+        <v>6921.83</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2465,7 +2471,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3070.35</v>
+        <v>3078.17</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2483,7 +2489,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6929.65</v>
+        <v>6921.83</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2512,7 +2518,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3070.35</v>
+        <v>3078.17</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2521,7 +2527,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4963.92</v>
+        <v>4956.1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5781,7 +5787,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3070.35</v>
+        <v>3078.17</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5838,7 +5844,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3070.35</v>
+        <v>3078.17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5865,7 +5871,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6929.65</v>
+        <v>6921.83</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7098,12 +7104,27 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="51"/>
-      <c r="B63" s="51"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="51"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="51"/>
+      <c r="A63" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B63" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="E63" s="52" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="F63" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="409">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1246,6 +1246,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvorfo8ev68o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muscle relaxant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvorg9hzr81p</t>
   </si>
 </sst>
 </file>
@@ -2029,11 +2035,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1589.84</v>
+        <v>1592.93</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3430.18</v>
+        <v>3427.09</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2379,11 +2385,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>55.03</v>
+        <v>58.12</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>399.97</v>
+        <v>396.88</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2442,11 +2448,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3078.17</v>
+        <v>3081.26</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6921.83</v>
+        <v>6918.74</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2471,7 +2477,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3078.17</v>
+        <v>3081.26</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2489,7 +2495,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6921.83</v>
+        <v>6918.74</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2518,7 +2524,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3078.17</v>
+        <v>3081.26</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2527,7 +2533,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4956.1</v>
+        <v>4953.01</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5787,7 +5793,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3078.17</v>
+        <v>3081.26</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5844,7 +5850,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3078.17</v>
+        <v>3081.26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5871,7 +5877,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6921.83</v>
+        <v>6918.74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7127,12 +7133,27 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="51"/>
-      <c r="B64" s="51"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="51"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="51"/>
+      <c r="A64" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B64" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" s="51" t="s">
+        <v>407</v>
+      </c>
+      <c r="E64" s="52" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F64" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="411">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1252,6 +1252,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvorg9hzr81p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvorgmpvwsbp</t>
   </si>
 </sst>
 </file>
@@ -2035,11 +2041,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1592.93</v>
+        <v>1593.59</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3427.09</v>
+        <v>3426.43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2301,11 +2307,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>240.13</v>
+        <v>240.79</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3147.37</v>
+        <v>3146.71</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2448,11 +2454,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3081.26</v>
+        <v>3081.92</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6918.74</v>
+        <v>6918.08</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2477,7 +2483,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3081.26</v>
+        <v>3081.92</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2495,7 +2501,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6918.74</v>
+        <v>6918.08</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2524,7 +2530,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3081.26</v>
+        <v>3081.92</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2533,7 +2539,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4953.01</v>
+        <v>4952.35</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5793,7 +5799,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3081.26</v>
+        <v>3081.92</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5850,7 +5856,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3081.26</v>
+        <v>3081.92</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5877,7 +5883,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6918.74</v>
+        <v>6918.08</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7156,12 +7162,27 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="51"/>
-      <c r="B65" s="51"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="51"/>
+      <c r="A65" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B65" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" s="51" t="s">
+        <v>409</v>
+      </c>
+      <c r="E65" s="52" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F65" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="413">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1258,6 +1258,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvorgmpvwsbp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groceries &amp; snacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvot5akg57p7</t>
   </si>
 </sst>
 </file>
@@ -2041,11 +2047,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1593.59</v>
+        <v>1609.92</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3426.43</v>
+        <v>3410.1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2307,11 +2313,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>240.79</v>
+        <v>257.12</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3146.71</v>
+        <v>3130.38</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2454,11 +2460,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3081.92</v>
+        <v>3098.25</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6918.08</v>
+        <v>6901.75</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2483,7 +2489,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3081.92</v>
+        <v>3098.25</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2501,7 +2507,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6918.08</v>
+        <v>6901.75</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2530,7 +2536,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3081.92</v>
+        <v>3098.25</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2539,7 +2545,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4952.35</v>
+        <v>4936.02</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5799,7 +5805,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3081.92</v>
+        <v>3098.25</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5856,7 +5862,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3081.92</v>
+        <v>3098.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5883,7 +5889,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6918.08</v>
+        <v>6901.75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7185,12 +7191,27 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="51"/>
-      <c r="B66" s="51"/>
-      <c r="C66" s="51"/>
-      <c r="D66" s="51"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="51"/>
+      <c r="A66" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B66" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="51" t="s">
+        <v>411</v>
+      </c>
+      <c r="E66" s="52" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="F66" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="415">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1264,6 +1264,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvot5akg57p7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvp2jnha09zo</t>
   </si>
 </sst>
 </file>
@@ -2047,11 +2053,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1609.92</v>
+        <v>1631.02</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3410.1</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2376,11 +2382,11 @@
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A25)</f>
-        <v>13.57</v>
+        <v>34.67</v>
       </c>
       <c r="D25" s="18" t="n">
         <f aca="false">B25-C25</f>
-        <v>1016.43</v>
+        <v>995.33</v>
       </c>
       <c r="E25" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B25/$B$3)</f>
@@ -2460,11 +2466,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3098.25</v>
+        <v>3119.35</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6901.75</v>
+        <v>6880.65</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2489,7 +2495,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3098.25</v>
+        <v>3119.35</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2507,7 +2513,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6901.75</v>
+        <v>6880.65</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2536,7 +2542,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3098.25</v>
+        <v>3119.35</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2545,7 +2551,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4936.02</v>
+        <v>4914.92</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5805,7 +5811,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3098.25</v>
+        <v>3119.35</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5862,7 +5868,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3098.25</v>
+        <v>3119.35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5889,7 +5895,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6901.75</v>
+        <v>6880.65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7214,12 +7220,27 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="51"/>
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="51"/>
+      <c r="A67" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B67" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D67" s="51" t="s">
+        <v>413</v>
+      </c>
+      <c r="E67" s="52" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F67" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="416">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1270,6 +1270,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvp2jnha09zo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvp2jx2345u8</t>
   </si>
 </sst>
 </file>
@@ -2053,11 +2056,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1631.02</v>
+        <v>1639.46</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3389</v>
+        <v>3380.56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2319,11 +2322,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>257.12</v>
+        <v>265.56</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3130.38</v>
+        <v>3121.94</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2466,11 +2469,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3119.35</v>
+        <v>3127.79</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6880.65</v>
+        <v>6872.21</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2495,7 +2498,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3119.35</v>
+        <v>3127.79</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2513,7 +2516,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6880.65</v>
+        <v>6872.21</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2542,7 +2545,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3119.35</v>
+        <v>3127.79</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2551,7 +2554,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4914.92</v>
+        <v>4906.48</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5811,7 +5814,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3119.35</v>
+        <v>3127.79</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5868,7 +5871,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3119.35</v>
+        <v>3127.79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5895,7 +5898,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6880.65</v>
+        <v>6872.21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7243,12 +7246,27 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="51"/>
-      <c r="B68" s="51"/>
-      <c r="C68" s="51"/>
-      <c r="D68" s="51"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="51"/>
+      <c r="A68" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B68" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="E68" s="52" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="F68" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="418">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1273,6 +1273,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvp2jx2345u8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvpabin5okfy</t>
   </si>
 </sst>
 </file>
@@ -2056,11 +2062,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1639.46</v>
+        <v>1642.04</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3380.56</v>
+        <v>3377.98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2322,11 +2328,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>265.56</v>
+        <v>268.14</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3121.94</v>
+        <v>3119.36</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2469,11 +2475,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3127.79</v>
+        <v>3130.37</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6872.21</v>
+        <v>6869.63</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2498,7 +2504,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3127.79</v>
+        <v>3130.37</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2516,7 +2522,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6872.21</v>
+        <v>6869.63</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2545,7 +2551,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3127.79</v>
+        <v>3130.37</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2554,7 +2560,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4906.48</v>
+        <v>4903.9</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5814,7 +5820,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3127.79</v>
+        <v>3130.37</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5871,7 +5877,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3127.79</v>
+        <v>3130.37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5898,7 +5904,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6872.21</v>
+        <v>6869.63</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7269,12 +7275,27 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="51"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="51"/>
+      <c r="A69" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B69" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="E69" s="52" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F69" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="421">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1279,6 +1279,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvpabin5okfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family mart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvpzb6cigrdo</t>
   </si>
 </sst>
 </file>
@@ -2062,11 +2071,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1642.04</v>
+        <v>1643.85</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3377.98</v>
+        <v>3376.17</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2328,11 +2337,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>268.14</v>
+        <v>269.95</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3119.36</v>
+        <v>3117.55</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2475,11 +2484,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3130.37</v>
+        <v>3132.18</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6869.63</v>
+        <v>6867.82</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2504,7 +2513,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3130.37</v>
+        <v>3132.18</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2522,7 +2531,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6869.63</v>
+        <v>6867.82</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2551,7 +2560,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3130.37</v>
+        <v>3132.18</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2560,7 +2569,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4903.9</v>
+        <v>4902.09</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5820,7 +5829,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3130.37</v>
+        <v>3132.18</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5877,7 +5886,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3130.37</v>
+        <v>3132.18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5904,7 +5913,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6869.63</v>
+        <v>6867.82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7298,12 +7307,27 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="52"/>
-      <c r="F70" s="51"/>
+      <c r="A70" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B70" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" s="51" t="s">
+        <v>419</v>
+      </c>
+      <c r="E70" s="52" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F70" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="423">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1288,6 +1288,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvpzb6cigrdo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoghurt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvpzbl6dlj7y</t>
   </si>
 </sst>
 </file>
@@ -2071,11 +2077,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1643.85</v>
+        <v>1646.08</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3376.17</v>
+        <v>3373.94</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2337,11 +2343,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>269.95</v>
+        <v>272.18</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3117.55</v>
+        <v>3115.32</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2484,11 +2490,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3132.18</v>
+        <v>3134.41</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6867.82</v>
+        <v>6865.59</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2513,7 +2519,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3132.18</v>
+        <v>3134.41</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2531,7 +2537,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6867.82</v>
+        <v>6865.59</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2560,7 +2566,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3132.18</v>
+        <v>3134.41</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2569,7 +2575,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4902.09</v>
+        <v>4899.86</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5829,7 +5835,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3132.18</v>
+        <v>3134.41</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5886,7 +5892,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3132.18</v>
+        <v>3134.41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5913,7 +5919,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6867.82</v>
+        <v>6865.59</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7330,12 +7336,27 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="52"/>
-      <c r="F71" s="51"/>
+      <c r="A71" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B71" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="E71" s="52" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F71" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="425">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1294,6 +1294,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvpzbl6dlj7y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minato coffee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvq0iakbh5v6</t>
   </si>
 </sst>
 </file>
@@ -2077,11 +2083,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1646.08</v>
+        <v>1652.07</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3373.94</v>
+        <v>3367.95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2343,11 +2349,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>272.18</v>
+        <v>278.17</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3115.32</v>
+        <v>3109.33</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2490,11 +2496,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3134.41</v>
+        <v>3140.4</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6865.59</v>
+        <v>6859.6</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2519,7 +2525,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3134.41</v>
+        <v>3140.4</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2537,7 +2543,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6865.59</v>
+        <v>6859.6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2566,7 +2572,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3134.41</v>
+        <v>3140.4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2575,7 +2581,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4899.86</v>
+        <v>4893.87</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5835,7 +5841,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3134.41</v>
+        <v>3140.4</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5892,7 +5898,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3134.41</v>
+        <v>3140.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5919,7 +5925,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6865.59</v>
+        <v>6859.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7359,12 +7365,27 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="51"/>
-      <c r="B72" s="51"/>
-      <c r="C72" s="51"/>
-      <c r="D72" s="51"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="51"/>
+      <c r="A72" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B72" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="51" t="s">
+        <v>423</v>
+      </c>
+      <c r="E72" s="52" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F72" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="426">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1300,6 +1300,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvq0iakbh5v6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvq58f9gkxdi</t>
   </si>
 </sst>
 </file>
@@ -2083,11 +2086,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1652.07</v>
+        <v>1656.82</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3367.95</v>
+        <v>3363.2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2370,11 +2373,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>21.35</v>
+        <v>26.1</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>717.65</v>
+        <v>712.9</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
@@ -2496,11 +2499,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3140.4</v>
+        <v>3145.15</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6859.6</v>
+        <v>6854.85</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2525,7 +2528,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3140.4</v>
+        <v>3145.15</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2543,7 +2546,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6859.6</v>
+        <v>6854.85</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2572,7 +2575,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3140.4</v>
+        <v>3145.15</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2581,7 +2584,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4893.87</v>
+        <v>4889.12</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5841,7 +5844,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3140.4</v>
+        <v>3145.15</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5898,7 +5901,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3140.4</v>
+        <v>3145.15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5925,7 +5928,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6859.6</v>
+        <v>6854.85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7388,12 +7391,27 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="51"/>
-      <c r="B73" s="51"/>
-      <c r="C73" s="51"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="52"/>
-      <c r="F73" s="51"/>
+      <c r="A73" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B73" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D73" s="51" t="s">
+        <v>403</v>
+      </c>
+      <c r="E73" s="52" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F73" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="428">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1303,6 +1303,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvq58f9gkxdi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sukiyaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvq9pk4z04zk</t>
   </si>
 </sst>
 </file>
@@ -2086,11 +2092,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1656.82</v>
+        <v>1683.17</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3363.2</v>
+        <v>3336.85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2352,11 +2358,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>278.17</v>
+        <v>304.52</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3109.33</v>
+        <v>3082.98</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2499,11 +2505,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3145.15</v>
+        <v>3171.5</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6854.85</v>
+        <v>6828.5</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2528,7 +2534,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3145.15</v>
+        <v>3171.5</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2546,7 +2552,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6854.85</v>
+        <v>6828.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2575,7 +2581,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3145.15</v>
+        <v>3171.5</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2584,7 +2590,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4889.12</v>
+        <v>4862.77</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5844,7 +5850,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3145.15</v>
+        <v>3171.5</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5901,7 +5907,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3145.15</v>
+        <v>3171.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5928,7 +5934,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6854.85</v>
+        <v>6828.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7414,12 +7420,27 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="51"/>
-      <c r="B74" s="51"/>
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="51"/>
+      <c r="A74" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B74" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D74" s="51" t="s">
+        <v>426</v>
+      </c>
+      <c r="E74" s="52" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="F74" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="429">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1309,6 +1309,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvq9pk4z04zk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvqh1hkkl4av</t>
   </si>
 </sst>
 </file>
@@ -2092,11 +2095,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1683.17</v>
+        <v>1701.28</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3336.85</v>
+        <v>3318.74</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2442,11 +2445,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>58.12</v>
+        <v>76.23</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>396.88</v>
+        <v>378.77</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2505,11 +2508,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3171.5</v>
+        <v>3189.61</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6828.5</v>
+        <v>6810.39</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2534,7 +2537,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3171.5</v>
+        <v>3189.61</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2552,7 +2555,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6828.5</v>
+        <v>6810.39</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2581,7 +2584,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3171.5</v>
+        <v>3189.61</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2590,7 +2593,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4862.77</v>
+        <v>4844.66</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5850,7 +5853,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3171.5</v>
+        <v>3189.61</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5907,7 +5910,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3171.5</v>
+        <v>3189.61</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5934,7 +5937,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6828.5</v>
+        <v>6810.39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7443,12 +7446,27 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="51"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="51"/>
+      <c r="A75" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B75" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D75" s="51" t="s">
+        <v>337</v>
+      </c>
+      <c r="E75" s="52" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="F75" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="431">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1312,6 +1312,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvqh1hkkl4av</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train to Nagoya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvqi40fs2t9j</t>
   </si>
 </sst>
 </file>
@@ -2095,11 +2101,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1701.28</v>
+        <v>1751.09</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3318.74</v>
+        <v>3268.93</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2403,11 +2409,11 @@
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A24)</f>
-        <v>23.25</v>
+        <v>73.06</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">B24-C24</f>
-        <v>207.75</v>
+        <v>157.94</v>
       </c>
       <c r="E24" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B24/$B$3)</f>
@@ -2508,11 +2514,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3189.61</v>
+        <v>3239.42</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6810.39</v>
+        <v>6760.58</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2537,7 +2543,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3189.61</v>
+        <v>3239.42</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2555,7 +2561,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6810.39</v>
+        <v>6760.58</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2584,7 +2590,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3189.61</v>
+        <v>3239.42</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2593,7 +2599,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4844.66</v>
+        <v>4794.85</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5853,7 +5859,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3189.61</v>
+        <v>3239.42</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5910,7 +5916,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3189.61</v>
+        <v>3239.42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5937,7 +5943,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6810.39</v>
+        <v>6760.58</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7469,12 +7475,27 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="51"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="51"/>
+      <c r="A76" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B76" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="E76" s="52" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="F76" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="433">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1318,6 +1318,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvqi40fs2t9j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvqm6w73ktqo</t>
   </si>
 </sst>
 </file>
@@ -2101,11 +2107,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1751.09</v>
+        <v>1753.33</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3268.93</v>
+        <v>3266.69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2367,11 +2373,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>304.52</v>
+        <v>306.76</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3082.98</v>
+        <v>3080.74</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2514,11 +2520,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3239.42</v>
+        <v>3241.66</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6760.58</v>
+        <v>6758.34</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2543,7 +2549,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3239.42</v>
+        <v>3241.66</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2561,7 +2567,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6760.58</v>
+        <v>6758.34</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2590,7 +2596,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3239.42</v>
+        <v>3241.66</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2599,7 +2605,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4794.85</v>
+        <v>4792.61</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5859,7 +5865,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3239.42</v>
+        <v>3241.66</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5916,7 +5922,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3239.42</v>
+        <v>3241.66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5943,7 +5949,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6760.58</v>
+        <v>6758.34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7498,12 +7504,27 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="51"/>
-      <c r="B77" s="51"/>
-      <c r="C77" s="51"/>
-      <c r="D77" s="51"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="51"/>
+      <c r="A77" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B77" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="51" t="s">
+        <v>431</v>
+      </c>
+      <c r="E77" s="52" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F77" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="435">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1324,6 +1324,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvqm6w73ktqo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mcdonalds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvqm7c7lny3f</t>
   </si>
 </sst>
 </file>
@@ -2107,11 +2113,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1753.33</v>
+        <v>1766.63</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3266.69</v>
+        <v>3253.39</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2373,11 +2379,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>306.76</v>
+        <v>320.06</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3080.74</v>
+        <v>3067.44</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2520,11 +2526,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3241.66</v>
+        <v>3254.96</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6758.34</v>
+        <v>6745.04</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2549,7 +2555,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3241.66</v>
+        <v>3254.96</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2567,7 +2573,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6758.34</v>
+        <v>6745.04</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2596,7 +2602,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3241.66</v>
+        <v>3254.96</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2605,7 +2611,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4792.61</v>
+        <v>4779.31</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5865,7 +5871,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3241.66</v>
+        <v>3254.96</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5922,7 +5928,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3241.66</v>
+        <v>3254.96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5949,7 +5955,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6758.34</v>
+        <v>6745.04</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7527,12 +7533,27 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="51"/>
-      <c r="B78" s="51"/>
-      <c r="C78" s="51"/>
-      <c r="D78" s="51"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="51"/>
+      <c r="A78" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B78" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" s="51" t="s">
+        <v>433</v>
+      </c>
+      <c r="E78" s="52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F78" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="438">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1330,6 +1330,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvqm7c7lny3f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrojcxp41da</t>
   </si>
 </sst>
 </file>
@@ -2113,11 +2122,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1766.63</v>
+        <v>1773.29</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3253.39</v>
+        <v>3246.73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2379,11 +2388,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>320.06</v>
+        <v>326.72</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3067.44</v>
+        <v>3060.78</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2526,11 +2535,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3254.96</v>
+        <v>3261.62</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6745.04</v>
+        <v>6738.38</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2555,7 +2564,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3254.96</v>
+        <v>3261.62</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2573,7 +2582,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6745.04</v>
+        <v>6738.38</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2602,7 +2611,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3254.96</v>
+        <v>3261.62</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2611,7 +2620,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4779.31</v>
+        <v>4772.65</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5871,7 +5880,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3254.96</v>
+        <v>3261.62</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5928,7 +5937,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3254.96</v>
+        <v>3261.62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5955,7 +5964,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6745.04</v>
+        <v>6738.38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7556,12 +7565,27 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="51"/>
-      <c r="B79" s="51"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="51"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="51"/>
+      <c r="A79" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B79" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D79" s="51" t="s">
+        <v>436</v>
+      </c>
+      <c r="E79" s="52" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="F79" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="441">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1339,6 +1339,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvrojcxp41da</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starbucks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrojtna9xy1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrok5bxmjgs</t>
   </si>
 </sst>
 </file>
@@ -2122,11 +2131,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1773.29</v>
+        <v>1778.48</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3246.73</v>
+        <v>3241.54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2388,11 +2397,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>326.72</v>
+        <v>331.91</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3060.78</v>
+        <v>3055.59</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2535,11 +2544,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3261.62</v>
+        <v>3266.81</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6738.38</v>
+        <v>6733.19</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2564,7 +2573,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3261.62</v>
+        <v>3266.81</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2582,7 +2591,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6738.38</v>
+        <v>6733.19</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2611,7 +2620,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3261.62</v>
+        <v>3266.81</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2620,7 +2629,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4772.65</v>
+        <v>4767.46</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5880,7 +5889,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3261.62</v>
+        <v>3266.81</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5937,7 +5946,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3261.62</v>
+        <v>3266.81</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5964,7 +5973,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6738.38</v>
+        <v>6733.19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7588,20 +7597,50 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="51"/>
-      <c r="B80" s="51"/>
-      <c r="C80" s="51"/>
-      <c r="D80" s="51"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="51"/>
+      <c r="A80" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B80" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" s="51" t="s">
+        <v>438</v>
+      </c>
+      <c r="E80" s="52" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F80" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="51"/>
-      <c r="B81" s="51"/>
-      <c r="C81" s="51"/>
-      <c r="D81" s="51"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="51"/>
+      <c r="A81" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B81" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D81" s="51" t="s">
+        <v>372</v>
+      </c>
+      <c r="E81" s="52" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F81" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="442">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1348,6 +1348,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvrok5bxmjgs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrokey4ia59</t>
   </si>
 </sst>
 </file>
@@ -2131,11 +2134,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1778.48</v>
+        <v>1779.43</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3241.54</v>
+        <v>3240.59</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2397,11 +2400,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>331.91</v>
+        <v>332.86</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3055.59</v>
+        <v>3054.64</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2544,11 +2547,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3266.81</v>
+        <v>3267.76</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6733.19</v>
+        <v>6732.24</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2573,7 +2576,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3266.81</v>
+        <v>3267.76</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2591,7 +2594,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6733.19</v>
+        <v>6732.24</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2620,7 +2623,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3266.81</v>
+        <v>3267.76</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2629,7 +2632,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4767.46</v>
+        <v>4766.51</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5889,7 +5892,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3266.81</v>
+        <v>3267.76</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5946,7 +5949,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3266.81</v>
+        <v>3267.76</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5973,7 +5976,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6733.19</v>
+        <v>6732.24</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7643,12 +7646,27 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="51"/>
-      <c r="B82" s="51"/>
-      <c r="C82" s="51"/>
-      <c r="D82" s="51"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="51"/>
+      <c r="A82" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B82" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D82" s="51" t="s">
+        <v>431</v>
+      </c>
+      <c r="E82" s="52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F82" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="444">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1351,6 +1351,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvrokey4ia59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagoya Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrqlsrej9n4</t>
   </si>
 </sst>
 </file>
@@ -2134,11 +2140,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1779.43</v>
+        <v>1784.21</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3240.59</v>
+        <v>3235.81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2463,11 +2469,11 @@
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A25)</f>
-        <v>34.67</v>
+        <v>39.45</v>
       </c>
       <c r="D25" s="18" t="n">
         <f aca="false">B25-C25</f>
-        <v>995.33</v>
+        <v>990.55</v>
       </c>
       <c r="E25" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B25/$B$3)</f>
@@ -2547,11 +2553,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3267.76</v>
+        <v>3272.54</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6732.24</v>
+        <v>6727.46</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2576,7 +2582,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3267.76</v>
+        <v>3272.54</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2594,7 +2600,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6732.24</v>
+        <v>6727.46</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2623,7 +2629,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3267.76</v>
+        <v>3272.54</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2632,7 +2638,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4766.51</v>
+        <v>4761.73</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5892,7 +5898,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3267.76</v>
+        <v>3272.54</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5949,7 +5955,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3267.76</v>
+        <v>3272.54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5976,7 +5982,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6732.24</v>
+        <v>6727.46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7669,12 +7675,27 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="51"/>
-      <c r="B83" s="51"/>
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="51"/>
+      <c r="A83" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B83" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" s="51" t="s">
+        <v>442</v>
+      </c>
+      <c r="E83" s="52" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F83" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="446">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1357,6 +1357,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvrqlsrej9n4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matcha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrruaiq60mu</t>
   </si>
 </sst>
 </file>
@@ -2140,11 +2146,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1784.21</v>
+        <v>1789.94</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3235.81</v>
+        <v>3230.08</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2406,11 +2412,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>332.86</v>
+        <v>338.59</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3054.64</v>
+        <v>3048.91</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2553,11 +2559,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3272.54</v>
+        <v>3278.27</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6727.46</v>
+        <v>6721.73</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2582,7 +2588,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3272.54</v>
+        <v>3278.27</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2600,7 +2606,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6727.46</v>
+        <v>6721.73</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2629,7 +2635,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3272.54</v>
+        <v>3278.27</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2638,7 +2644,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4761.73</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5898,7 +5904,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3272.54</v>
+        <v>3278.27</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5955,7 +5961,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3272.54</v>
+        <v>3278.27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5982,7 +5988,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6727.46</v>
+        <v>6721.73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7698,12 +7704,27 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="51"/>
-      <c r="B84" s="51"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="51"/>
+      <c r="A84" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B84" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84" s="51" t="s">
+        <v>444</v>
+      </c>
+      <c r="E84" s="52" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="F84" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="448">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1363,6 +1363,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvrruaiq60mu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train to Takayama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrxcaeo5hbb</t>
   </si>
 </sst>
 </file>
@@ -2146,11 +2152,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1789.94</v>
+        <v>1822.45</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3230.08</v>
+        <v>3197.57</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2454,11 +2460,11 @@
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A24)</f>
-        <v>73.06</v>
+        <v>105.57</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">B24-C24</f>
-        <v>157.94</v>
+        <v>125.43</v>
       </c>
       <c r="E24" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B24/$B$3)</f>
@@ -2559,11 +2565,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3278.27</v>
+        <v>3310.78</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6721.73</v>
+        <v>6689.22</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2588,7 +2594,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3278.27</v>
+        <v>3310.78</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2606,7 +2612,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6721.73</v>
+        <v>6689.22</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2635,7 +2641,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3278.27</v>
+        <v>3310.78</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2644,7 +2650,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4756</v>
+        <v>4723.49</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5904,7 +5910,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3278.27</v>
+        <v>3310.78</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5961,7 +5967,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3278.27</v>
+        <v>3310.78</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5988,7 +5994,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6721.73</v>
+        <v>6689.22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7727,12 +7733,27 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="51"/>
-      <c r="B85" s="51"/>
-      <c r="C85" s="51"/>
-      <c r="D85" s="51"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="51"/>
+      <c r="A85" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B85" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D85" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="E85" s="52" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="F85" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="450">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1369,6 +1369,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvrxcaeo5hbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gyukatsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrxcu95rxhk</t>
   </si>
 </sst>
 </file>
@@ -2152,11 +2158,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1822.45</v>
+        <v>1841.21</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3197.57</v>
+        <v>3178.81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2418,11 +2424,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>338.59</v>
+        <v>357.35</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3048.91</v>
+        <v>3030.15</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2565,11 +2571,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3310.78</v>
+        <v>3329.54</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6689.22</v>
+        <v>6670.46</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2594,7 +2600,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3310.78</v>
+        <v>3329.54</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2612,7 +2618,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6689.22</v>
+        <v>6670.46</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2641,7 +2647,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3310.78</v>
+        <v>3329.54</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2650,7 +2656,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4723.49</v>
+        <v>4704.73</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5910,7 +5916,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3310.78</v>
+        <v>3329.54</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5967,7 +5973,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3310.78</v>
+        <v>3329.54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5994,7 +6000,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6689.22</v>
+        <v>6670.46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7756,12 +7762,27 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="51"/>
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="51"/>
+      <c r="A86" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B86" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" s="51" t="s">
+        <v>448</v>
+      </c>
+      <c r="E86" s="52" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="F86" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="452">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1375,6 +1375,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvrxcu95rxhk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvrxdicmalfm</t>
   </si>
 </sst>
 </file>
@@ -2158,11 +2164,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1841.21</v>
+        <v>1847.94</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3178.81</v>
+        <v>3172.08</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2508,11 +2514,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>76.23</v>
+        <v>82.96</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>378.77</v>
+        <v>372.04</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2571,11 +2577,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3329.54</v>
+        <v>3336.27</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6670.46</v>
+        <v>6663.73</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2600,7 +2606,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3329.54</v>
+        <v>3336.27</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2618,7 +2624,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6670.46</v>
+        <v>6663.73</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2647,7 +2653,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3329.54</v>
+        <v>3336.27</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2656,7 +2662,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4704.73</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5916,7 +5922,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3329.54</v>
+        <v>3336.27</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5973,7 +5979,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3329.54</v>
+        <v>3336.27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6000,7 +6006,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6670.46</v>
+        <v>6663.73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7785,12 +7791,27 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="51"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="51"/>
+      <c r="A87" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B87" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D87" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="E87" s="52" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="F87" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="453">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1381,6 +1381,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvrxdicmalfm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvs3l53uys9n</t>
   </si>
 </sst>
 </file>
@@ -2164,11 +2167,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1847.94</v>
+        <v>1849.56</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3172.08</v>
+        <v>3170.46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2430,11 +2433,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>357.35</v>
+        <v>358.97</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3030.15</v>
+        <v>3028.53</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2577,11 +2580,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3336.27</v>
+        <v>3337.89</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6663.73</v>
+        <v>6662.11</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2606,7 +2609,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3336.27</v>
+        <v>3337.89</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2624,7 +2627,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6663.73</v>
+        <v>6662.11</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2653,7 +2656,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3336.27</v>
+        <v>3337.89</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2662,7 +2665,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4698</v>
+        <v>4696.38</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5922,7 +5925,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3336.27</v>
+        <v>3337.89</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5979,7 +5982,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3336.27</v>
+        <v>3337.89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6006,7 +6009,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6663.73</v>
+        <v>6662.11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7814,12 +7817,27 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="51"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="51"/>
+      <c r="A88" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B88" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="E88" s="52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F88" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="454">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1384,6 +1384,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvs3l53uys9n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvs3lc6y8bd9</t>
   </si>
 </sst>
 </file>
@@ -2167,11 +2170,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1849.56</v>
+        <v>1852.94</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3170.46</v>
+        <v>3167.08</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2433,11 +2436,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>358.97</v>
+        <v>362.35</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3028.53</v>
+        <v>3025.15</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2580,11 +2583,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3337.89</v>
+        <v>3341.27</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6662.11</v>
+        <v>6658.73</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2609,7 +2612,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3337.89</v>
+        <v>3341.27</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2627,7 +2630,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6662.11</v>
+        <v>6658.73</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2656,7 +2659,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3337.89</v>
+        <v>3341.27</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2665,7 +2668,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4696.38</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5925,7 +5928,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3337.89</v>
+        <v>3341.27</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5982,7 +5985,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3337.89</v>
+        <v>3341.27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6009,7 +6012,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6662.11</v>
+        <v>6658.73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7840,12 +7843,27 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="51"/>
-      <c r="B89" s="51"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="51"/>
-      <c r="E89" s="52"/>
-      <c r="F89" s="51"/>
+      <c r="A89" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B89" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="E89" s="52" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F89" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="456">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1387,6 +1387,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvs3lc6y8bd9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takoyaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvs3wxzfeytn</t>
   </si>
 </sst>
 </file>
@@ -2170,11 +2176,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1852.94</v>
+        <v>1857.3</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3167.08</v>
+        <v>3162.72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2436,11 +2442,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>362.35</v>
+        <v>366.71</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3025.15</v>
+        <v>3020.79</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2583,11 +2589,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3341.27</v>
+        <v>3345.63</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6658.73</v>
+        <v>6654.37</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2612,7 +2618,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3341.27</v>
+        <v>3345.63</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2630,7 +2636,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6658.73</v>
+        <v>6654.37</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2659,7 +2665,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3341.27</v>
+        <v>3345.63</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2668,7 +2674,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4693</v>
+        <v>4688.64</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5928,7 +5934,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3341.27</v>
+        <v>3345.63</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5985,7 +5991,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3341.27</v>
+        <v>3345.63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6012,7 +6018,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6658.73</v>
+        <v>6654.37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7866,12 +7872,27 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="51"/>
-      <c r="B90" s="51"/>
-      <c r="C90" s="51"/>
-      <c r="D90" s="51"/>
-      <c r="E90" s="52"/>
-      <c r="F90" s="51"/>
+      <c r="A90" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B90" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D90" s="51" t="s">
+        <v>454</v>
+      </c>
+      <c r="E90" s="52" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="F90" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="459">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1393,6 +1393,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvs3wxzfeytn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eel!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvsy1oh1vqqa</t>
   </si>
 </sst>
 </file>
@@ -2176,11 +2185,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1857.3</v>
+        <v>1884.26</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3162.72</v>
+        <v>3135.76</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2442,11 +2451,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>366.71</v>
+        <v>393.67</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>3020.79</v>
+        <v>2993.83</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2589,11 +2598,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3345.63</v>
+        <v>3372.59</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6654.37</v>
+        <v>6627.41</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2618,7 +2627,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3345.63</v>
+        <v>3372.59</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2636,7 +2645,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6654.37</v>
+        <v>6627.41</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2665,7 +2674,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3345.63</v>
+        <v>3372.59</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2674,7 +2683,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4688.64</v>
+        <v>4661.68</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5934,7 +5943,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3345.63</v>
+        <v>3372.59</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -5991,7 +6000,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3345.63</v>
+        <v>3372.59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6018,7 +6027,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6654.37</v>
+        <v>6627.41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7895,12 +7904,27 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="51"/>
-      <c r="B91" s="51"/>
-      <c r="C91" s="51"/>
-      <c r="D91" s="51"/>
-      <c r="E91" s="52"/>
-      <c r="F91" s="51"/>
+      <c r="A91" s="51" t="s">
+        <v>456</v>
+      </c>
+      <c r="B91" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D91" s="51" t="s">
+        <v>457</v>
+      </c>
+      <c r="E91" s="52" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="F91" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="461">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1402,6 +1402,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvsy1oh1vqqa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suica topup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvtayw8oya7i</t>
   </si>
 </sst>
 </file>
@@ -2185,11 +2191,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1884.26</v>
+        <v>1893.82</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3135.76</v>
+        <v>3126.2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2472,11 +2478,11 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A23)</f>
-        <v>26.1</v>
+        <v>35.66</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">B23-C23</f>
-        <v>712.9</v>
+        <v>703.34</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B23/$B$3)</f>
@@ -2598,11 +2604,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3372.59</v>
+        <v>3382.15</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6627.41</v>
+        <v>6617.85</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2627,7 +2633,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3372.59</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2645,7 +2651,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6627.41</v>
+        <v>6617.85</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2674,7 +2680,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3372.59</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2683,7 +2689,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4661.68</v>
+        <v>4652.12</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5943,7 +5949,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3372.59</v>
+        <v>3382.15</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6000,7 +6006,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3372.59</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6027,7 +6033,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6627.41</v>
+        <v>6617.85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7927,12 +7933,27 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="51"/>
-      <c r="B92" s="51"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="51"/>
-      <c r="E92" s="52"/>
-      <c r="F92" s="51"/>
+      <c r="A92" s="51" t="s">
+        <v>456</v>
+      </c>
+      <c r="B92" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="E92" s="52" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="F92" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="462">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1408,6 +1408,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvtayw8oya7i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvtaz4m6itj0</t>
   </si>
 </sst>
 </file>
@@ -2191,11 +2194,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1893.82</v>
+        <v>1897.12</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3126.2</v>
+        <v>3122.9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2457,11 +2460,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>393.67</v>
+        <v>396.97</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2993.83</v>
+        <v>2990.53</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2604,11 +2607,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3382.15</v>
+        <v>3385.45</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6617.85</v>
+        <v>6614.55</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2633,7 +2636,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3382.15</v>
+        <v>3385.45</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2651,7 +2654,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6617.85</v>
+        <v>6614.55</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2680,7 +2683,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3382.15</v>
+        <v>3385.45</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2689,7 +2692,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4652.12</v>
+        <v>4648.82</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5949,7 +5952,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3382.15</v>
+        <v>3385.45</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6006,7 +6009,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3382.15</v>
+        <v>3385.45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6033,7 +6036,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6617.85</v>
+        <v>6614.55</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7956,12 +7959,27 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="51"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="51"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="51"/>
+      <c r="A93" s="51" t="s">
+        <v>456</v>
+      </c>
+      <c r="B93" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D93" s="51" t="s">
+        <v>444</v>
+      </c>
+      <c r="E93" s="52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F93" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="463">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1411,6 +1411,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvtaz4m6itj0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvtg7ut0fqi1</t>
   </si>
 </sst>
 </file>
@@ -2194,11 +2197,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1897.12</v>
+        <v>1907.88</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3122.9</v>
+        <v>3112.14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2460,11 +2463,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>396.97</v>
+        <v>407.73</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2990.53</v>
+        <v>2979.77</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2607,11 +2610,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3385.45</v>
+        <v>3396.21</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6614.55</v>
+        <v>6603.79</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2636,7 +2639,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3385.45</v>
+        <v>3396.21</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2654,7 +2657,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6614.55</v>
+        <v>6603.79</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2683,7 +2686,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3385.45</v>
+        <v>3396.21</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2692,7 +2695,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4648.82</v>
+        <v>4638.06</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5952,7 +5955,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3385.45</v>
+        <v>3396.21</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6009,7 +6012,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3385.45</v>
+        <v>3396.21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6036,7 +6039,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6614.55</v>
+        <v>6603.79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7982,12 +7985,27 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="51"/>
-      <c r="B94" s="51"/>
-      <c r="C94" s="51"/>
-      <c r="D94" s="51"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="51"/>
+      <c r="A94" s="51" t="s">
+        <v>456</v>
+      </c>
+      <c r="B94" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D94" s="51" t="s">
+        <v>426</v>
+      </c>
+      <c r="E94" s="52" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="F94" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="465">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1414,6 +1414,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvtg7ut0fqi1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pizza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvtg858egtto</t>
   </si>
 </sst>
 </file>
@@ -2197,11 +2203,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1907.88</v>
+        <v>1916.11</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3112.14</v>
+        <v>3103.91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2463,11 +2469,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>407.73</v>
+        <v>415.96</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2979.77</v>
+        <v>2971.54</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2610,11 +2616,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3396.21</v>
+        <v>3404.44</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6603.79</v>
+        <v>6595.56</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2639,7 +2645,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3396.21</v>
+        <v>3404.44</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2657,7 +2663,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6603.79</v>
+        <v>6595.56</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2686,7 +2692,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3396.21</v>
+        <v>3404.44</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2695,7 +2701,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4638.06</v>
+        <v>4629.83</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5955,7 +5961,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3396.21</v>
+        <v>3404.44</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6012,7 +6018,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3396.21</v>
+        <v>3404.44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6039,7 +6045,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6603.79</v>
+        <v>6595.56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8008,12 +8014,27 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="51"/>
-      <c r="B95" s="51"/>
-      <c r="C95" s="51"/>
-      <c r="D95" s="51"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="51"/>
+      <c r="A95" s="51" t="s">
+        <v>456</v>
+      </c>
+      <c r="B95" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D95" s="51" t="s">
+        <v>463</v>
+      </c>
+      <c r="E95" s="52" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="F95" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="468">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1420,6 +1420,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvtg858egtto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota Museum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvuhhjadqm9g</t>
   </si>
 </sst>
 </file>
@@ -2203,11 +2212,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1916.11</v>
+        <v>1920.89</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3103.91</v>
+        <v>3099.13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2532,11 +2541,11 @@
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A25)</f>
-        <v>39.45</v>
+        <v>44.23</v>
       </c>
       <c r="D25" s="18" t="n">
         <f aca="false">B25-C25</f>
-        <v>990.55</v>
+        <v>985.77</v>
       </c>
       <c r="E25" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B25/$B$3)</f>
@@ -2616,11 +2625,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3404.44</v>
+        <v>3409.22</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6595.56</v>
+        <v>6590.78</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2645,7 +2654,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3404.44</v>
+        <v>3409.22</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2663,7 +2672,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6595.56</v>
+        <v>6590.78</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2692,7 +2701,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3404.44</v>
+        <v>3409.22</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2701,7 +2710,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4629.83</v>
+        <v>4625.05</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5961,7 +5970,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3404.44</v>
+        <v>3409.22</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6018,7 +6027,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3404.44</v>
+        <v>3409.22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6045,7 +6054,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6595.56</v>
+        <v>6590.78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8037,12 +8046,27 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="51"/>
-      <c r="B96" s="51"/>
-      <c r="C96" s="51"/>
-      <c r="D96" s="51"/>
-      <c r="E96" s="52"/>
-      <c r="F96" s="51"/>
+      <c r="A96" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B96" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D96" s="51" t="s">
+        <v>466</v>
+      </c>
+      <c r="E96" s="52" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F96" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="469">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1429,6 +1429,9 @@
   </si>
   <si>
     <t xml:space="preserve">mvuhhjadqm9g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvusrwvdzmlp</t>
   </si>
 </sst>
 </file>
@@ -2212,11 +2215,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1920.89</v>
+        <v>1935.27</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3099.13</v>
+        <v>3084.75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2478,11 +2481,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>415.96</v>
+        <v>430.34</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2971.54</v>
+        <v>2957.16</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2625,11 +2628,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3409.22</v>
+        <v>3423.6</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6590.78</v>
+        <v>6576.4</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2654,7 +2657,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3409.22</v>
+        <v>3423.6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2672,7 +2675,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6590.78</v>
+        <v>6576.4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2701,7 +2704,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3409.22</v>
+        <v>3423.6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2710,7 +2713,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4625.05</v>
+        <v>4610.67</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5970,7 +5973,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3409.22</v>
+        <v>3423.6</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6027,7 +6030,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3409.22</v>
+        <v>3423.6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6054,7 +6057,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6590.78</v>
+        <v>6576.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8069,12 +8072,27 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="51"/>
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
-      <c r="E97" s="52"/>
-      <c r="F97" s="51"/>
+      <c r="A97" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B97" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D97" s="51" t="s">
+        <v>347</v>
+      </c>
+      <c r="E97" s="52" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="F97" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="472">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1432,6 +1432,15 @@
   </si>
   <si>
     <t xml:space="preserve">mvusrwvdzmlp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvuss8a9skf8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umbrella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvussl8v2y7i</t>
   </si>
 </sst>
 </file>
@@ -2215,11 +2224,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1935.27</v>
+        <v>1949.44</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3084.75</v>
+        <v>3070.58</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2481,11 +2490,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>430.34</v>
+        <v>434.11</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2957.16</v>
+        <v>2953.39</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2565,11 +2574,11 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A26)</f>
-        <v>82.96</v>
+        <v>93.36</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">B26-C26</f>
-        <v>372.04</v>
+        <v>361.64</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B26/$B$3)</f>
@@ -2628,11 +2637,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3423.6</v>
+        <v>3437.77</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6576.4</v>
+        <v>6562.23</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2657,7 +2666,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3423.6</v>
+        <v>3437.77</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2675,7 +2684,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6576.4</v>
+        <v>6562.23</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2704,7 +2713,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3423.6</v>
+        <v>3437.77</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2713,7 +2722,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4610.67</v>
+        <v>4596.5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5973,7 +5982,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3423.6</v>
+        <v>3437.77</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6030,7 +6039,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3423.6</v>
+        <v>3437.77</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6057,7 +6066,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6576.4</v>
+        <v>6562.23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8095,20 +8104,50 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="51"/>
-      <c r="B98" s="51"/>
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="51"/>
+      <c r="A98" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B98" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" s="51" t="s">
+        <v>409</v>
+      </c>
+      <c r="E98" s="52" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="F98" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="51"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="51"/>
+      <c r="A99" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B99" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D99" s="51" t="s">
+        <v>470</v>
+      </c>
+      <c r="E99" s="52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F99" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="474">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1441,6 +1441,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvussl8v2y7i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wine bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvuyit13niyl</t>
   </si>
 </sst>
 </file>
@@ -2224,11 +2230,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1949.44</v>
+        <v>1975.19</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3070.58</v>
+        <v>3044.83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2490,11 +2496,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>434.11</v>
+        <v>459.86</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2953.39</v>
+        <v>2927.64</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2637,11 +2643,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3437.77</v>
+        <v>3463.52</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6562.23</v>
+        <v>6536.48</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2666,7 +2672,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3437.77</v>
+        <v>3463.52</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2684,7 +2690,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6562.23</v>
+        <v>6536.48</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2713,7 +2719,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3437.77</v>
+        <v>3463.52</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2722,7 +2728,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4596.5</v>
+        <v>4570.75</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5982,7 +5988,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3437.77</v>
+        <v>3463.52</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6039,7 +6045,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3437.77</v>
+        <v>3463.52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6066,7 +6072,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6562.23</v>
+        <v>6536.48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8150,12 +8156,27 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="51"/>
+      <c r="A100" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B100" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" s="51" t="s">
+        <v>472</v>
+      </c>
+      <c r="E100" s="52" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="F100" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="476">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1447,6 +1447,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvuyit13niyl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvv2ypmxaq7r</t>
   </si>
 </sst>
 </file>
@@ -2230,11 +2236,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1975.19</v>
+        <v>1981.88</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3044.83</v>
+        <v>3038.14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2496,11 +2502,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>459.86</v>
+        <v>466.55</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2927.64</v>
+        <v>2920.95</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2643,11 +2649,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3463.52</v>
+        <v>3470.21</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6536.48</v>
+        <v>6529.79</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2672,7 +2678,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3463.52</v>
+        <v>3470.21</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2690,7 +2696,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6536.48</v>
+        <v>6529.79</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2719,7 +2725,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3463.52</v>
+        <v>3470.21</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2728,7 +2734,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4570.75</v>
+        <v>4564.06</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5988,7 +5994,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3463.52</v>
+        <v>3470.21</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6045,7 +6051,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3463.52</v>
+        <v>3470.21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6072,7 +6078,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6536.48</v>
+        <v>6529.79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8179,12 +8185,27 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="52"/>
-      <c r="F101" s="51"/>
+      <c r="A101" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B101" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D101" s="51" t="s">
+        <v>474</v>
+      </c>
+      <c r="E101" s="52" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="F101" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -2236,11 +2236,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1981.88</v>
+        <v>1981.92</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3038.14</v>
+        <v>3038.1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2502,11 +2502,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>466.55</v>
+        <v>466.59</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2920.95</v>
+        <v>2920.91</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3470.21</v>
+        <v>3470.25</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6529.79</v>
+        <v>6529.75</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3470.21</v>
+        <v>3470.25</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6529.79</v>
+        <v>6529.75</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3470.21</v>
+        <v>3470.25</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4564.06</v>
+        <v>4564.02</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3470.21</v>
+        <v>3470.25</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3470.21</v>
+        <v>3470.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6529.79</v>
+        <v>6529.75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8175,7 +8175,7 @@
         <v>472</v>
       </c>
       <c r="E100" s="52" t="n">
-        <v>25.75</v>
+        <v>25.79</v>
       </c>
       <c r="F100" s="51" t="s">
         <v>43</v>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="478">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1453,6 +1453,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvv2ypmxaq7r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvwd7acgrqmb</t>
   </si>
 </sst>
 </file>
@@ -2236,11 +2242,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1981.92</v>
+        <v>1984.79</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3038.1</v>
+        <v>3035.23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2502,11 +2508,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>466.59</v>
+        <v>469.46</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2920.91</v>
+        <v>2918.04</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2649,11 +2655,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3470.25</v>
+        <v>3473.12</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6529.75</v>
+        <v>6526.88</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2678,7 +2684,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3470.25</v>
+        <v>3473.12</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2696,7 +2702,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6529.75</v>
+        <v>6526.88</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2725,7 +2731,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3470.25</v>
+        <v>3473.12</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2734,7 +2740,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4564.02</v>
+        <v>4561.15</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5994,7 +6000,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3470.25</v>
+        <v>3473.12</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6051,7 +6057,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3470.25</v>
+        <v>3473.12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6078,7 +6084,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6529.75</v>
+        <v>6526.88</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8208,12 +8214,27 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="51"/>
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
-      <c r="D102" s="51"/>
-      <c r="E102" s="52"/>
-      <c r="F102" s="51"/>
+      <c r="A102" s="51" t="s">
+        <v>476</v>
+      </c>
+      <c r="B102" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C102" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D102" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="E102" s="52" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="F102" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="51"/>

--- a/Sabbatical_Plan_and_Budget.xlsx
+++ b/Sabbatical_Plan_and_Budget.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="480">
   <si>
     <t xml:space="preserve">Sabbatical 2026–27: plan &amp; budget</t>
   </si>
@@ -1459,6 +1459,12 @@
   </si>
   <si>
     <t xml:space="preserve">mvwd7acgrqmb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvwd81qp5s3a</t>
   </si>
 </sst>
 </file>
@@ -2242,11 +2248,11 @@
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Flights")-SUMIFS(Tracker!$E$5:$E$1000,Tracker!$B$5:$B$1000,"Japan",Tracker!$C$5:$C$1000,"Insurance &amp; admin")</f>
-        <v>1984.79</v>
+        <v>1993.5</v>
       </c>
       <c r="G8" s="12" t="n">
         <f aca="false">D8+D14-F8</f>
-        <v>3035.23</v>
+        <v>3026.52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2508,11 +2514,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">SUMIFS(Tracker!$E$5:$E$1000,Tracker!$C$5:$C$1000,A22)</f>
-        <v>469.46</v>
+        <v>478.17</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">B22-C22</f>
-        <v>2918.04</v>
+        <v>2909.33</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">IF($B$3=0,0,B22/$B$3)</f>
@@ -2655,11 +2661,11 @@
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">SUM(C20:C28)</f>
-        <v>3473.12</v>
+        <v>3481.83</v>
       </c>
       <c r="D29" s="24" t="n">
         <f aca="false">SUM(D20:D28)</f>
-        <v>6526.88</v>
+        <v>6518.17</v>
       </c>
       <c r="E29" s="25" t="n">
         <f aca="false">SUM(E20:E28)</f>
@@ -2684,7 +2690,7 @@
       </c>
       <c r="B33" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3473.12</v>
+        <v>3481.83</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2702,7 +2708,7 @@
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">Tracker!I7</f>
-        <v>6526.88</v>
+        <v>6518.17</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2731,7 +2737,7 @@
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Tracker!I4</f>
-        <v>3473.12</v>
+        <v>3481.83</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2740,7 +2746,7 @@
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B40-B41</f>
-        <v>4561.15</v>
+        <v>4552.44</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6000,7 +6006,7 @@
       </c>
       <c r="I4" s="50" t="n">
         <f aca="false">SUMIFS(E5:E1000,F5:F1000,"Paid")</f>
-        <v>3473.12</v>
+        <v>3481.83</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>295</v>
@@ -6057,7 +6063,7 @@
       </c>
       <c r="I6" s="24" t="n">
         <f aca="false">I4+I5</f>
-        <v>3473.12</v>
+        <v>3481.83</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6084,7 +6090,7 @@
       </c>
       <c r="I7" s="27" t="n">
         <f aca="false">Overview!B3-I6</f>
-        <v>6526.88</v>
+        <v>6518.17</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8237,12 +8243,27 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="51"/>
-      <c r="B103" s="51"/>
-      <c r="C103" s="51"/>
-      <c r="D103" s="51"/>
-      <c r="E103" s="52"/>
-      <c r="F103" s="51"/>
+      <c r="A103" s="51" t="s">
+        <v>476</v>
+      </c>
+      <c r="B103" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D103" s="51" t="s">
+        <v>478</v>
+      </c>
+      <c r="E103" s="52" t="n">
+        <v>8.71</v>
+      </c>
+      <c r="F103" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="51"/>
